--- a/resources/qualys/Qualys_VulnLab_scan-b.xlsx
+++ b/resources/qualys/Qualys_VulnLab_scan-b.xlsx
@@ -601,13 +601,7 @@
           <t>Content-Security-Policy HTTP Security Header Not Detected</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>The HTTP Content-Security-Policy response header allows web site administrators to control resources the user agent is allowed to load for a given page. This helps guard against cross-site scripting attacks (XSS). 
-QID Detection Logic: 
-This QID detects the absence of the Content-Security-Policy HTTP header by transmitting a GET request.</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -1221,16 +1215,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
+          <t xml:space="preserve">No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
 1) no-referrer 
 2) no-referrer-when-downgrade 
 3) same-origin 
 4) origin 
 5) origin-when-cross-origin 
 6) strict-origin 
-7) strict-origin-when-cross-origin  
-QID Detection Logic(Unauthenticated): 
-If the Referrer Policy header is not found , checks in response body for meta tag containing tag name as "referrer" and one of the above Referrer Policy.</t>
+7) strict-origin-when-cross-origin  </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1494,10 +1486,7 @@
  PHP 7.0 series reached End of Life in its support cycle on 10 Jan 2019.
  Since there are no further bug fixes or security updates for PHP 7.0 series, it's highly recommended to migrate from version 5.6 to newer supported versions.
  Affected Versions: 
-PHP 7.0.x versions
-QID Detection Logic: 
-Unauthenticated : This QID looks for PHP banner to detect affected versions remotely. 
-Authenticated : This QID checks for php.exe version using registry "HKLM\SOFTWARE\PHP " and flag if found vulnerable.</t>
+PHP 7.0.x versions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1545,15 +1534,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
+          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
 CVE-2022-31630: In installed version of PHP, when using imageloadfont() function in gd extension, it is possible to supply a specially crafted font file, such as if the loaded font is used with imagechar() function, the read outside allocated buffer will be used. This can lead to crashes or disclosure of confidential information. 
 CVE-2022-37454: The Keccak XKCP SHA-3 reference implementation before fdc6fef has an integer overflow and resultant buffer overflow that allows attackers to execute arbitrary code or eliminate expected cryptographic properties.  
 Affected Versions: 
 PHP versions before 7.4.33 
 PHP versions 8.0.0 prior to 8.0.25 
-PHP versions 8.1.0 prior to 8.1.12 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP Server header to see if the server is running a vulnerable version of PHP.</t>
+PHP versions 8.1.0 prior to 8.1.12 </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1615,14 +1602,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apache Web Server is an open-source web server. 
+          <t xml:space="preserve">Apache Web Server is an open-source web server. 
 Uninitialized memory reflection in mod_auth_digest leading to leakage of potentially confidential information, and a segfault. 
 Affected Versions: 
 Apache httpd 2.2.x before 2.2.34 
-Apache httpd 2.4.x before 2.4.27 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v".</t>
+Apache httpd 2.4.x before 2.4.27 </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1683,11 +1667,9 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache HTTP Server versions 2.4.53 and earlier  
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions 2.4.53 and earlier  </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1749,16 +1731,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2022-28330: Apache HTTP Server 2.4.53 and earlier on Windows may read beyond bounds when configured to process requests with the mod_isapi module. 
 CVE-2022-28614: The ap_rwrite() function in Apache HTTP Server 2.4.53 and earlier may read unintended memory if an attacker can cause the server to reflect very large input using ap_rwrite() or ap_rputs(), such as with mod_luas r:puts() function. 
 CVE-2022-28615: Apache HTTP Server 2.4.53 and earlier may crash or disclose information due to a read beyond bounds in ap_strcmp_match() when provided with an extremely large input buffer. 
 CVE-2022-29404: In Apache HTTP Server 2.4.53 and earlier, a malicious request to a lua script that calls r:parsebody(0) may cause a denial of service due to no default limit on possible input size. 
 CVE-2022-30556: Apache HTTP Server 2.4.53 and earlier may return lengths to applications calling r:wsread() that point past the end of the storage allocated for the buffer. 
 Affected Versions: 
-Apache HTTP Server versions 2.4.53 and earlier  
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banners to detect if the target is running the vulnerable version of apache httpd.</t>
+Apache HTTP Server versions 2.4.53 and earlier  </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1882,13 +1862,9 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>In Apache HTTP Server 2.4 releases 2.4.17 to 2.4.38, with MPM event, worker or prefork, code executing in less-privileged child processes or threads (including scripts executed by an in-process scripting interpreter) could execute arbitrary code with the privileges of the parent process (usually root) by manipulating the scoreboard. Non-Unix systems are not affected.
+          <t xml:space="preserve">In Apache HTTP Server 2.4 releases 2.4.17 to 2.4.38, with MPM event, worker or prefork, code executing in less-privileged child processes or threads (including scripts executed by an in-process scripting interpreter) could execute arbitrary code with the privileges of the parent process (usually root) by manipulating the scoreboard. Non-Unix systems are not affected.
  Affected Versions: 
-2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.30, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17 
-QID Detection Logic (Unauthenticated): 
-This QID Checks for the vulnerable versions based on the exposed banner information under the HTTP service. 
-QID Detection Logic (Authenticated): 
-This QID Checks for the vulnerable versions of Apache HTTP Server based on version detected from the command.</t>
+2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.30, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17 </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1943,10 +1919,8 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Apache Module mod_mime is used to assign content metadata to the content selected for an HTTP response by mapping patterns in the URI or filenames to the metadata values. 
-In Apache httpd 2.2.x before 2.2.33 and 2.4.x before 2.4.26, mod_mime can read one byte past the end of a buffer when sending a malicious Content-Type response header. 
-QID Detection Logic (Unauthenticated): 
-This QID matches vulnerable versions based on the exposed banner information under the HTTP service.</t>
+          <t xml:space="preserve">The Apache Module mod_mime is used to assign content metadata to the content selected for an HTTP response by mapping patterns in the URI or filenames to the metadata values. 
+In Apache httpd 2.2.x before 2.2.33 and 2.4.x before 2.4.26, mod_mime can read one byte past the end of a buffer when sending a malicious Content-Type response header. </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2002,16 +1976,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
 Apache HTTP Server versions prior to 2.4.46. 
  NOTE:  
 CVE-2021-26691, CVE-2021-26690, CVE-2020-35452, CVE-2020-13938 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6, 2.4.4, 2.4.3, 2.4.2, 2.4.1, 2.4.0. 
 CVE-2019-17567 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6 
 CVE-2021-30641 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39 
-CVE-2020-13950 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+CVE-2020-13950 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41 </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2073,11 +2045,9 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
+          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
 Affected Versions: 
-Apache HTTP Server 2.4.48 and earlier 
-QID Detection Logic:(Unauthenticated)
-This QID sends an HTTP GET request to the default page and checks for a match for a string "(Server:.*)(Apache)"; then checks for vulnerable versions of Apache HTTP.</t>
+Apache HTTP Server 2.4.48 and earlier </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2138,12 +2108,10 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
+          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
 A carefully crafted request body can cause a buffer overflow in the mod_lua multipart parser (r:parsebody() called from Lua scripts). 
 Affected Versions: 
-Apache HTTP Server 2.4.51 and earlier 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for vulnerable Apache Version by grabbing the banner from HTTP response</t>
+Apache HTTP Server 2.4.51 and earlier </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2204,12 +2172,10 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
+          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
 A crafted URI sent to httpd configured as a forward proxy (ProxyRequests on) can cause a crash (NULL pointer dereference) or, for configurations mixing forward and reverse proxy declarations, can allow for requests to be directed to a declared Unix Domain Socket endpoint (Server Side Request Forgery). 
 Affected Versions: 
-Apache HTTP Server 2.4.7 - 2.4.51 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for vulnerable Apache Version by grabbing the banner from HTTP response</t>
+Apache HTTP Server 2.4.7 - 2.4.51 </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2337,12 +2303,10 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Some mod_proxy configurations on Apache HTTP Server versions 2.4.0 through 2.4.55 allow a HTTP Request Smuggling attack. 
+          <t xml:space="preserve">Some mod_proxy configurations on Apache HTTP Server versions 2.4.0 through 2.4.55 allow a HTTP Request Smuggling attack. 
 Configurations are affected when mod_proxy is enabled along with some form of RewriteRule or ProxyPassMatch in which a non-specific pattern matches some portion of the user-supplied request-target (URL) data and is then re-inserted into the proxied request-target using variable substitution.  
 Affected Versions: 
-Apache HTTP Server Versions 2.4.0 through 2.4.55 (including) 
-QID Detection Logic(Unauthenticated):  
-This QID checks for vulnerable version of Apache HTTP Server by sending a GET request to a target and extracting the version from the response header.</t>
+Apache HTTP Server Versions 2.4.0 through 2.4.55 (including) </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2403,13 +2367,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2006-20001: A carefully crafted If: request header can cause a memory read, or write of a single zero byte, in a pool (heap) memory location beyond the header value sent. This could cause the process to crash. 
 CVE-2022-37436: A malicious backend can cause the response headers to be truncated early, resulting in some headers being incorporated into the response body. If the later headers have any security purpose, they will not be interpreted by the client. 
 Affected Versions: 
-Apache HTTP Server versions prior to 2.4.55 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions prior to 2.4.55 </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2471,13 +2433,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2023-31122: Out-of-bounds Read vulnerability in mod_macro of Apache HTTP Server.This issue affects Apache HTTP Server 
 CVE-2023-45802: A client could send new requests and resets, keeping the connection busy and open and causing the memory footprint to keep on growing. On connection close, all resources were reclaimed, but the process might run out of memory before that. 
 Affected Versions: 
-Apache HTTP Server versions prior to 2.4.58 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions prior to 2.4.58 </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2539,12 +2499,10 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2022-36760: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to.  
 Affected Versions: 
-Apache HTTP Server from 2.4 through 2.4.54  
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server from 2.4 through 2.4.54  </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2606,12 +2564,10 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2022-26377: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to. 
 Affected Versions: 
-Apache HTTP Server versions 2.4 to 2.4.53  
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banners to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions 2.4 to 2.4.53  </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2673,7 +2629,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-38472: SSRF in Apache HTTP Server on Windows allows to potentially leak NTML hashes to a malicious server via SSRF and malicious requests or content 
 CVE-2024-38473: Apache HTTP Server proxy encoding problem 
 CVE-2024-38474: Apache HTTP Server weakness with encoded question marks in backreferences 
@@ -2682,10 +2638,7 @@
 CVE-2024-38477: Apache HTTP Server Crash resulting in Denial of Service in mod_proxy via a malicious request 
 CVE-2024-39573: Apache HTTP Server mod_rewrite proxy handler substitution 
 Affected Versions: 
-Apache HTTP Server versions prior to 2.4.60 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banners to detect if the target is running the vulnerable version of apache httpd. 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache HTTP Server versions prior to 2.4.60 </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2747,14 +2700,10 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-47252:  Apache HTTP Server: mod_ssl error log variable escaping 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2816,13 +2765,10 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-29169:  Apache HTTP Server: mod_dav_lock indirect lock crash 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2884,13 +2830,10 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-34059:  Apache HTTP Server: mod_proxy_ajp: Heap Over-Read and memory disclosure in  ajp_parse_data() 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3023,18 +2966,7 @@
           <t>Apache httpd Server ap_get_basic_auth_pw() Authentication Bypass Vulnerability</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Apache Web Server is an open-source web server. 
-The use of the ap_get_basic_auth_pw() by third-party modules outside of the authentication phase may lead to authentication requirements being bypassed in vulnerable Apache httpd versions. 
-Affected Versions: 
-Apache httpd 2.2.x before 2.2.33 
-Apache httpd 2.4.x before 2.4.26 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v".</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>Customers are advised to upgrade to Apache httpd 2.2.33, 2.4.26 (https://httpd.apache.org/download.cgi) or later versions to remediate this vulnerability.
@@ -3087,13 +3019,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application.
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application.
  CVE-2020-1934: In Apache HTTP Server, mod_proxy_ftp may use uninitialized memory when proxying to a malicious FTP server. 
  CVE-2020-1927: In Apache HTTP Server, redirects configured with mod_rewrite that were intended to be self-referential might be fooled by encoded newlines and redirect instead to an an unexpected URL within the request URL. 
  Affected Versions: 
-Apache httpd 2.4.0 to 2.4.41 
- QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache httpd 2.4.0 to 2.4.41 </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3153,29 +3083,9 @@
           <t>PHP Multiple Denial of Service Vulnerabilities</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML.  
-Multiple vulnerabilities have been discovered in PHP : 
-Affected Version: 
-PHP 5.x through 7.1.24 
-QID Detection Logic(Unauth): 
-The QID will try to find the Vulnerable version of the PHP from the Banner.</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Vendor has Released the patch to addressed the vulnerability. Please update to PHP 7.1.25 (https://www.php.net/releases/7_1_25.php)
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Version 7.1.25 (https://www.php.net/releases/7_1_25.php)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>ext/standard/var_unserializer.c in PHP 5.x through 7.1.24 allows attackers to cause a denial of service (application crash) via an unserialize call for the com, dotnet, or variant class.</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>['CVE-2018-19396', 'CVE-2018-19395']</t>
@@ -3221,11 +3131,9 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
+          <t xml:space="preserve">PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
 Affected Versions: 
-PHP versions before 7.2.16 
-QID Detection Logic 
-The qid checks the php version via banner.</t>
+PHP versions before 7.2.16 </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3286,14 +3194,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
+          <t xml:space="preserve">PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
 PHP is affected by multiple vulnerabilities. 
 Affected Versions: 
 PHP versions prior to 7.4.24 
 PHP versions 7.3.x prior to 7.3.31 
-PHP versions 8.0.x prior to 8.0.11 
-QID Detection Logic 
-The qid checks the php version via banner.</t>
+PHP versions 8.0.x prior to 8.0.11 </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3354,16 +3260,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
+          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
 Affected versions of PHP has multiple vulnerabilities: 
 CVE-2022-31628 : The vulnerability exists due to infinite loop within the phar uncompressor code when processing "quines" gzip files. A remote attacker can pass a specially crafted archive to the application, consume all available system resources and cause denial of service conditions. 
 CVE-2022-31629: The vulnerability exists due to the way PHP handles HTTP variable names. A remote attacker can set a standard insecure cookie in the victim's browser which is treated as a '__Host-' or '__Secure-' cookie by PHP applications. 
 Affected Versions: 
 PHP versions before 7.4.31 
 PHP versions 8.0.0 prior to 8.0.24 
-PHP versions 8.1.0 prior to 8.1.11 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP Server header to see if the server is running a vulnerable version of PHP.</t>
+PHP versions 8.1.0 prior to 8.1.11 </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3425,13 +3329,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2023-38709: Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. 
 CVE-2024-24795: HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack.  
 Affected Versions: 
-Apache HTTP Server versions prior to 2.4.59 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions prior to 2.4.59 </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3493,14 +3395,10 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-49812:  Apache HTTP Server: mod_ssl TLS upgrade attack 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3562,14 +3460,8 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-53020:  Apache HTTP Server: HTTP/2 DoS by Memory Increase 
-Affected Versions: 
-Apache httpd 2.4.17 through 2.4.63 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+          <t xml:space="preserve">Affected Versions: 
+Apache httpd 2.4.17 through 2.4.63 </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3581,11 +3473,7 @@
   Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>['CVE-2025-53020']</t>
@@ -3631,14 +3519,10 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-43394:  Apache HTTP Server: SSRF on Windows due to UNC paths 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3700,14 +3584,10 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-42516:  Apache HTTP Server: HTTP response splitting 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3769,14 +3649,10 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-59775:  Apache HTTP Server: NTLM Leakage on Windows through UNC SSRF 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3838,14 +3714,10 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-66200:  Apache HTTP Server: mod_userdir+suexec bypass via AllowOverride FileInfo 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3907,14 +3779,10 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-58098:  Apache HTTP Server: Server Side Includes adds query string to exec cmd=... 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3976,13 +3844,10 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-33006:  Apache HTTP Server: mod_auth_digest timing attack 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4044,13 +3909,10 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-24072:  Apache HTTP Server: mod_rewrite elevation of privileges via ap_expr 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4112,14 +3974,10 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44119:  escalation of privilege through expressions in .htaccess in multiple modules 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4181,14 +4039,10 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44186:  Loop in `proxy_ftp_handler` in mod_proxy_ftp 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4250,14 +4104,10 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-49975:  mod_http2 denial of service 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4319,14 +4169,10 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-34355:  mod_proxy_html buffer overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4388,14 +4234,10 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-43951:  OOB Read in `merge_response_headers` can cause crash 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4457,14 +4299,10 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-42535:  mod_dav_fs protected directory access 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4526,12 +4364,10 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
+          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
 A crafted method sent through HTTP/2 will bypass validation and be forwarded by mod_proxy, which can lead to request splitting or cache poisoning. 
 Affected Versions: 
-Apache HTTP Server 2.4.17 to 2.4.48. 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server 2.4.17 to 2.4.48. </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4592,14 +4428,10 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-43204:  Apache HTTP Server: SSRF with mod_headers setting Content-Type header 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4661,14 +4493,10 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-65082:  Apache HTTP Server: CGI environment variable override 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4730,13 +4558,10 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-34032:  Apache HTTP Server: mod_proxy_ajp: Heap Buffer Over-Read Due to Missing Null-Termination Check (ajp_msg_get_string) 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4798,13 +4623,10 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-33007:  Apache HTTP Server: mod_authn_socache crash 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4866,13 +4688,10 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-33857:  Apache HTTP Server: Off-by-one OOB reads in AJP getter functions 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4934,14 +4753,10 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-33523:  Apache HTTP Server: multiple modules: HTTP response splitting forwarding malicious status line 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5003,14 +4818,10 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-28780:  Apache HTTP Server: buffer overflow in mod_proxy_ajp via  ajp_msg_check_header() 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5072,14 +4883,10 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-29170:  mod_proxy_ftp XSS 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5141,14 +4948,10 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-29167:  mod_ldap per-dir use-after-free 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5210,14 +5013,10 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-42536:  mod_xml2enc heap overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5279,14 +5078,10 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44185:  Stack Buffer Over-Read in mod_ssl OCSP `send_request` 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5348,14 +5143,10 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-34356:  ProxyPassReverseCookieMap buffer overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5417,14 +5208,10 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44631:  Heap Underflow in `ap_regname` via Signed Char Overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5484,11 +5271,7 @@
           <t>PHP Server Detected</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>PHP is a general purpose scripting language that is especially suited for Web development and can be embedded in HTML.</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -5524,11 +5307,7 @@
           <t>Web Server HTTP Protocol Versions</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -5691,19 +5470,7 @@
           <t>Apache HTTP Server Detected</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards. 
-Apache HTTP Server was detected on the target. 
-QID Detection Logic (Authenticated): 
-Operating System: Linux 
-The detection looks for Apache HTTP Server installation path using ps command. The version is extracted from the Apache HTTP Server's binary. 
-Operating System: Windows 
-This QID checks Windows registry to see if Apache HTTP Server is installed. If found, it displays the installed version. 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP response headers if the Apache web server is running on the target system.</t>
-        </is>
-      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -6096,11 +5863,7 @@
           <t>Web Server Version</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>A web server is server software, or hardware dedicated to running this software, that can satisfy client requests on the World Wide Web.</t>
-        </is>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -6241,14 +6004,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
+          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
 Affected Versions: 
 PHP versions from 8.1.0 prior to 8.1.32 
 PHP versions from 8.2.0 prior to 8.2.28 
 PHP versions from 8.3.0 prior to 8.3.19 
-PHP versions from 8.4.0 prior to 8.4.5 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP Server header to see if the server is running a vulnerable version of PHP.</t>
+PHP versions from 8.4.0 prior to 8.4.5 </t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6309,14 +6070,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
+          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
 Affected PHP versions 
 from 8.4.0 before 8.4.10 
 from 8.3.0 before 8.3.23 
 from 8.2.0 before 8.2.29 
-from 8.1.0 before 8.1.33 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP Server header to see if the server is running a vulnerable version of PHP.</t>
+from 8.1.0 before 8.1.33 </t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6377,14 +6136,10 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-47252:  Apache HTTP Server: mod_ssl error log variable escaping 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6446,13 +6201,9 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29169:  Apache HTTP Server: mod_dav_lock indirect lock crash 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6514,13 +6265,9 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34059:  Apache HTTP Server: mod_proxy_ajp: Heap Over-Read and memory disclosure in  ajp_parse_data() 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6657,9 +6404,7 @@
         <is>
           <t>JQuery is prone to a cross-site-scripting vulnerability because it fails to sufficiently sanitize user-supplied input. 
 Affected Versions:  
-jQuery versions greater than or equal to 1.2 and before 3.5.0.
- QID Detection Logic(Unauthenticated):  
-It checks for vulnerable versions of jQuery from default web page.</t>
+jQuery versions greater than or equal to 1.2 and before 3.5.0.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6722,9 +6467,7 @@
         <is>
           <t>JQuery is prone to a cross-site-scripting vulnerability because it fails to sufficiently sanitize user-supplied input. 
 Affected Versions:  
-jQuery versions greater than or equal to 1.0.3 and before 3.5.0.
- QID Detection Logic(Unauthenticated):  
-It checks for vulnerable versions of jQuery from default web page.</t>
+jQuery versions greater than or equal to 1.0.3 and before 3.5.0.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6853,14 +6596,10 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-49812:  Apache HTTP Server: mod_ssl TLS upgrade attack 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6922,14 +6661,10 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-53020:  Apache HTTP Server: HTTP/2 DoS by Memory Increase 
 Affected Versions: 
-Apache httpd 2.4.17 through 2.4.63 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.17 through 2.4.63 </t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6991,14 +6726,10 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-43394:  Apache HTTP Server: SSRF on Windows due to UNC paths 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7060,14 +6791,10 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-23048:  Apache HTTP Server: mod_ssl access control bypass with session resumption 
 Affected Versions: 
-Apache httpd 2.4.35 through 2.4.63 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.35 through 2.4.63 </t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7129,14 +6856,10 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-42516:  Apache HTTP Server: HTTP response splitting 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7198,14 +6921,9 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-59775:  Apache HTTP Server: NTLM Leakage on Windows through UNC SSRF 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7267,14 +6985,9 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-66200:  Apache HTTP Server: mod_userdir+suexec bypass via AllowOverride FileInfo 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7336,14 +7049,9 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-58098:  Apache HTTP Server: Server Side Includes adds query string to exec cmd=... 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7405,13 +7113,9 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33006:  Apache HTTP Server: mod_auth_digest timing attack 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7473,13 +7177,9 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-24072:  Apache HTTP Server: mod_rewrite elevation of privileges via ap_expr 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7541,14 +7241,10 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44119:  escalation of privilege through expressions in .htaccess in multiple modules 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7610,14 +7306,10 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44186:  Loop in `proxy_ftp_handler` in mod_proxy_ftp 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7679,14 +7371,10 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-49975:  mod_http2 denial of service 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7748,14 +7436,10 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-34355:  mod_proxy_html buffer overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7817,14 +7501,10 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-43951:  OOB Read in `merge_response_headers` can cause crash 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7886,14 +7566,10 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-42535:  mod_dav_fs protected directory access 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7955,14 +7631,10 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-43204:  Apache HTTP Server: SSRF with mod_headers setting Content-Type header 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8024,14 +7696,10 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-49630:  Apache HTTP Server: mod_proxy_http2 denial of service 
 Affected Versions: 
-Apache httpd 2.4.26 through 2.4.63 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.26 through 2.4.63 </t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8093,14 +7761,9 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-65082:  Apache HTTP Server: CGI environment variable override 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8162,14 +7825,9 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-55753:  Apache HTTP Server: mod_md (ACME), unintended retry intervals 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8231,13 +7889,9 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34032:  Apache HTTP Server: mod_proxy_ajp: Heap Buffer Over-Read Due to Missing Null-Termination Check (ajp_msg_get_string) 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8299,13 +7953,9 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33007:  Apache HTTP Server: mod_authn_socache crash 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8367,13 +8017,9 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33857:  Apache HTTP Server: Off-by-one OOB reads in AJP getter functions 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8435,14 +8081,9 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33523:  Apache HTTP Server: multiple modules: HTTP response splitting forwarding malicious status line 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8504,14 +8145,9 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-28780:  Apache HTTP Server: buffer overflow in mod_proxy_ajp via  ajp_msg_check_header() 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8573,14 +8209,9 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29168:  Apache HTTP Server: mod_md unrestricted OCSP response 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8642,14 +8273,10 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-29170:  mod_proxy_ftp XSS 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8711,14 +8338,10 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-29167:  mod_ldap per-dir use-after-free 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8780,14 +8403,10 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-42536:  mod_xml2enc heap overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8849,14 +8468,10 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44185:  Stack Buffer Over-Read in mod_ssl OCSP `send_request` 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8918,14 +8533,10 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-48913:  mod_http2 memory corruption when file handles exhausted 
 Affected Versions: 
-Apache httpd 2.4.55 before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.55 before 2.4.68 </t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8987,14 +8598,10 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-34356:  ProxyPassReverseCookieMap buffer overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9056,14 +8663,10 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44631:  Heap Underflow in `ap_regname` via Signed Char Overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9123,13 +8726,7 @@
           <t>Content-Security-Policy HTTP Security Header Not Detected</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>The HTTP Content-Security-Policy response header allows web site administrators to control resources the user agent is allowed to load for a given page. This helps guard against cross-site scripting attacks (XSS). 
-QID Detection Logic: 
-This QID detects the absence of the Content-Security-Policy HTTP header by transmitting a GET request.</t>
-        </is>
-      </c>
+      <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
@@ -9171,11 +8768,7 @@
           <t>PHP Server Detected</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>PHP is a general purpose scripting language that is especially suited for Web development and can be embedded in HTML.</t>
-        </is>
-      </c>
+      <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
@@ -9351,11 +8944,7 @@
           <t>Web Server HTTP Protocol Versions</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.</t>
-        </is>
-      </c>
+      <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
@@ -9439,9 +9028,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Drupal is a free and open source content management framework written in PHP and distributed under the GNU General Public License. 
-QID Detection Logic: 
-This QID checks for default Drupal installation wizard.</t>
+          <t xml:space="preserve">Drupal is a free and open source content management framework written in PHP and distributed under the GNU General Public License. </t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -9562,15 +9149,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards. 
-Apache HTTP Server was detected on the target. 
-QID Detection Logic (Authenticated): 
-Operating System: Linux 
-The detection looks for Apache HTTP Server installation path using ps command. The version is extracted from the Apache HTTP Server's binary. 
-Operating System: Windows 
-This QID checks Windows registry to see if Apache HTTP Server is installed. If found, it displays the installed version. 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP response headers if the Apache web server is running on the target system.</t>
+          <t xml:space="preserve">The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards. </t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -9967,16 +9546,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
+          <t xml:space="preserve">No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
 1) no-referrer 
 2) no-referrer-when-downgrade 
 3) same-origin 
 4) origin 
 5) origin-when-cross-origin 
 6) strict-origin 
-7) strict-origin-when-cross-origin  
-QID Detection Logic(Unauthenticated): 
-If the Referrer Policy header is not found , checks in response body for meta tag containing tag name as "referrer" and one of the above Referrer Policy.</t>
+7) strict-origin-when-cross-origin  </t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10031,11 +9608,7 @@
           <t>Web Server Version</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>A web server is server software, or hardware dedicated to running this software, that can satisfy client requests on the World Wide Web.</t>
-        </is>
-      </c>
+      <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
@@ -10232,14 +9805,7 @@
           <t>Weak SSL/TLS Key Exchange</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>QID Detection Logic:
-For a SSL enabled port, the scanner probes and maintains a list of supported SSL/TLS versions. For each supported version, the scanner does a SSL handshake to get a list of KEX methods supported by the server. It reports all KEX methods that are considered weak and List all server supported ciphers for each weak key exchange method supported by Server.  
-The criteria of a weak KEX method is as follows: 
-The SSL/TLS server supports key exchanges that are cryptographically weaker than recommended. Key exchanges should provide at least 112 bits of security, which translates to a minimum key size of 2048 bits for Diffie Hellman and RSA key exchanges or 224 bits for Elliptic Curve Diffie Hellman key exchanges.</t>
-        </is>
-      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
           <t>Change the SSL/TLS server configuration to only allow strong key exchanges. Key exchanges used on the server should provide at least 112 bits of security, so the minimum key size to not flag this QID should be:
@@ -10399,7 +9965,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TLS is capable of using a multitude of ciphers (algorithms) to create the public and private key pairs. 
+          <t xml:space="preserve">TLS is capable of using a multitude of ciphers (algorithms) to create the public and private key pairs. 
 For example if TLSv1.0 uses either the RC4 stream cipher, or a block cipher in CBC mode. 
 RC4 is known to have biases and the block cipher in CBC mode is vulnerable to the POODLE attack. 
 TLSv1.0, if configured to use the same cipher suites as SSLv3, includes a means by which a TLS implementation can downgrade the connection to SSL v3.0, thus weakening security. 
@@ -10409,9 +9975,7 @@
 PCI: ASV Program Guide v3.1 (page 27) (https://www.pcisecuritystandards.org/documents/ASV_Program_Guide_v3.1.pdf) 
 PCI: Use of SSL Early TLS and ASV Scans (https://www.pcisecuritystandards.org/documents/Use-of-SSL-Early-TLS-and-ASV-Scans.pdf)
 NOTE: On March 31, 2021 Transport Layer Security (TLS) versions 1.0 (RFC 2246) and 1.1 (RFC 4346) are formally deprecated.
-Refer to Deprecating TLS 1.0 and TLS 1.1 (https://tools.ietf.org/html/rfc8996) 
-QID Detection Logic (Unauthenticated): 
-This QID is detected when the server successfully negotiates a TLS 1.0 handshake. Presence of TLS 1.0 alone is sufficient to flag this QID, independent of cipher strength. TLS 1.0 is deprecated (RFC 8996)</t>
+Refer to Deprecating TLS 1.0 and TLS 1.1 (https://tools.ietf.org/html/rfc8996) </t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10470,12 +10034,10 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>The scan target supports version 1.1 of the TLS protocol. That version is in the process of being deprecated and is no longer recommended. Instead the newer versions 1.2 and/or 1.3 should be used. The TLSv1.1 protocol itself does not have any currently exploitable vulnerabilities. However some vendor implementations of TLSv1.1 have weaknesses which may be exploitable. 
+          <t xml:space="preserve">The scan target supports version 1.1 of the TLS protocol. That version is in the process of being deprecated and is no longer recommended. Instead the newer versions 1.2 and/or 1.3 should be used. The TLSv1.1 protocol itself does not have any currently exploitable vulnerabilities. However some vendor implementations of TLSv1.1 have weaknesses which may be exploitable. 
 This QID is posted as potential, when servers require client certificates and we cannot complete the handshake. 
 NOTE: On March 31, 2021 Transport Layer Security (TLS) versions 1.0 (RFC 2246) and 1.1 (RFC 4346) are formally deprecated.
-Refer to Deprecating TLS 1.0 and TLS 1.1 (https://tools.ietf.org/html/rfc8996) 
-QID Detection Logic (Unauthenticated): 
-This QID is detected when the server accepts a TLS 1.1 handshake. Even though TLS 1.1 has no known direct vulnerabilities, it is deprecated and reported when supported or inferred during the handshake. TLS 1.1 is formally deprecated (RFC 8996)</t>
+Refer to Deprecating TLS 1.0 and TLS 1.1 (https://tools.ietf.org/html/rfc8996) </t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10762,7 +10324,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-38472: SSRF in Apache HTTP Server on Windows allows to potentially leak NTML hashes to a malicious server via SSRF and malicious requests or content 
 CVE-2024-38473: Apache HTTP Server proxy encoding problem 
 CVE-2024-38474: Apache HTTP Server weakness with encoded question marks in backreferences 
@@ -10771,10 +10333,7 @@
 CVE-2024-38477: Apache HTTP Server Crash resulting in Denial of Service in mod_proxy via a malicious request 
 CVE-2024-39573: Apache HTTP Server mod_rewrite proxy handler substitution 
 Affected Versions: 
-Apache HTTP Server versions prior to 2.4.60 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banners to detect if the target is running the vulnerable version of apache httpd. 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache HTTP Server versions prior to 2.4.60 </t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10836,14 +10395,10 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-47252:  Apache HTTP Server: mod_ssl error log variable escaping 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10905,13 +10460,9 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29169:  Apache HTTP Server: mod_dav_lock indirect lock crash 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10973,13 +10524,9 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34059:  Apache HTTP Server: mod_proxy_ajp: Heap Over-Read and memory disclosure in  ajp_parse_data() 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11114,13 +10661,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2023-38709: Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. 
 CVE-2024-24795: HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack.  
 Affected Versions: 
-Apache HTTP Server versions prior to 2.4.59 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions prior to 2.4.59 </t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11182,14 +10727,10 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-49812:  Apache HTTP Server: mod_ssl TLS upgrade attack 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11251,14 +10792,10 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-53020:  Apache HTTP Server: HTTP/2 DoS by Memory Increase 
 Affected Versions: 
-Apache httpd 2.4.17 through 2.4.63 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.17 through 2.4.63 </t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11320,14 +10857,10 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-43394:  Apache HTTP Server: SSRF on Windows due to UNC paths 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11389,14 +10922,10 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-23048:  Apache HTTP Server: mod_ssl access control bypass with session resumption 
 Affected Versions: 
-Apache httpd 2.4.35 through 2.4.63 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.35 through 2.4.63 </t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11458,14 +10987,10 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-42516:  Apache HTTP Server: HTTP response splitting 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11527,14 +11052,9 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-59775:  Apache HTTP Server: NTLM Leakage on Windows through UNC SSRF 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11596,14 +11116,9 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-66200:  Apache HTTP Server: mod_userdir+suexec bypass via AllowOverride FileInfo 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11665,14 +11180,9 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-58098:  Apache HTTP Server: Server Side Includes adds query string to exec cmd=... 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11734,13 +11244,9 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33006:  Apache HTTP Server: mod_auth_digest timing attack 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11802,13 +11308,9 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-24072:  Apache HTTP Server: mod_rewrite elevation of privileges via ap_expr 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11870,14 +11372,10 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44119:  escalation of privilege through expressions in .htaccess in multiple modules 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11939,14 +11437,10 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44186:  Loop in `proxy_ftp_handler` in mod_proxy_ftp 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12008,14 +11502,10 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-49975:  mod_http2 denial of service 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12077,14 +11567,10 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-34355:  mod_proxy_html buffer overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12146,14 +11632,10 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-43951:  OOB Read in `merge_response_headers` can cause crash 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12215,14 +11697,10 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-42535:  mod_dav_fs protected directory access 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12284,9 +11762,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>This is the global system user list, which was retrieved during the scan by exploiting one or more vulnerabilities or via authentication provided by user. The Qualys IDs for the vulnerabilities leading to the disclosure of these users are also given in the Result section. Each user will be displayed only once, even though it may be obtained by using different methods. 
-QID Detection Logic: 
-Note: The user information is collected through QIDs 90266, 45027, 45032, 45031, 105234, and 78021. It's important to clarify that no vulnerabilities were exploited to obtain this information in the aforementioned QIDs.</t>
+          <t xml:space="preserve">This is the global system user list, which was retrieved during the scan by exploiting one or more vulnerabilities or via authentication provided by user. The Qualys IDs for the vulnerabilities leading to the disclosure of these users are also given in the Result section. Each user will be displayed only once, even though it may be obtained by using different methods. </t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12393,14 +11869,10 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-43204:  Apache HTTP Server: SSRF with mod_headers setting Content-Type header 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12462,14 +11934,10 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-49630:  Apache HTTP Server: mod_proxy_http2 denial of service 
 Affected Versions: 
-Apache httpd 2.4.26 through 2.4.63 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.26 through 2.4.63 </t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12531,14 +11999,9 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-65082:  Apache HTTP Server: CGI environment variable override 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12600,14 +12063,9 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-55753:  Apache HTTP Server: mod_md (ACME), unintended retry intervals 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12669,13 +12127,9 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34032:  Apache HTTP Server: mod_proxy_ajp: Heap Buffer Over-Read Due to Missing Null-Termination Check (ajp_msg_get_string) 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12737,13 +12191,9 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33007:  Apache HTTP Server: mod_authn_socache crash 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12805,13 +12255,9 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33857:  Apache HTTP Server: Off-by-one OOB reads in AJP getter functions 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12873,14 +12319,9 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33523:  Apache HTTP Server: multiple modules: HTTP response splitting forwarding malicious status line 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12942,14 +12383,9 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-28780:  Apache HTTP Server: buffer overflow in mod_proxy_ajp via  ajp_msg_check_header() 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -13011,14 +12447,9 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29168:  Apache HTTP Server: mod_md unrestricted OCSP response 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13080,14 +12511,10 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-29170:  mod_proxy_ftp XSS 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13149,14 +12576,10 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-29167:  mod_ldap per-dir use-after-free 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13218,14 +12641,10 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-42536:  mod_xml2enc heap overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13287,14 +12706,10 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44185:  Stack Buffer Over-Read in mod_ssl OCSP `send_request` 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13356,14 +12771,10 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-48913:  mod_http2 memory corruption when file handles exhausted 
 Affected Versions: 
-Apache httpd 2.4.55 before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.55 before 2.4.68 </t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13425,14 +12836,10 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-34356:  ProxyPassReverseCookieMap buffer overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13494,14 +12901,10 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44631:  Heap Underflow in `ap_regname` via Signed Char Overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13563,21 +12966,11 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>The Simple Mail Transfer Protocol is a communication protocol for electronic mail transmission. 
-QID Detection Logic: 
-The QID  checks for 220 status code in the banner of the response.</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+          <t xml:space="preserve">The Simple Mail Transfer Protocol is a communication protocol for electronic mail transmission. </t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr">
         <is>
@@ -13784,19 +13177,7 @@
           <t>Apache HTTP Server Detected</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards. 
-Apache HTTP Server was detected on the target. 
-QID Detection Logic (Authenticated): 
-Operating System: Linux 
-The detection looks for Apache HTTP Server installation path using ps command. The version is extracted from the Apache HTTP Server's binary. 
-Operating System: Windows 
-This QID checks Windows registry to see if Apache HTTP Server is installed. If found, it displays the installed version. 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP response headers if the Apache web server is running on the target system.</t>
-        </is>
-      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
@@ -14191,9 +13572,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>cAdvisor (Container Advisor) provides container users an understanding of the resource usage and performance characteristics of their running containers. It is a running daemon that collects, aggregates, processes, and exports information about running containers. 
-QID Detection Logic:(Unauthenticated) 
-This QID sends a GET request to check if the authentication is enabled by querying the following endpoints /api/v1.3/,/api/v2.0/</t>
+          <t xml:space="preserve">cAdvisor (Container Advisor) provides container users an understanding of the resource usage and performance characteristics of their running containers. It is a running daemon that collects, aggregates, processes, and exports information about running containers. </t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -14807,37 +14186,9 @@
           <t>HTTP Security Header Not Detected</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>This QID reports the absence of the following HTTP headers (https://www.owasp.org/index.php/OWASP_Secure_Headers_Projecttab=Headers) according to CWE-693: Protection Mechanism Failure (https://cwe.mitre.org/data/definitions/693.html): 
-X-Content-Type-Options: This HTTP header will prevent the browser from interpreting files as a different MIME type to what is specified in the Content-Type HTTP header.  
-Strict-Transport-Security: The HTTP Strict-Transport-Security response header (HSTS) allows web servers to declare that web browsers (or other complying user agents) should only interact with it using secure HTTPS connections, and never via the insecure HTTP protocol. 
- QID Detection Logic: 
-This unauthenticated QID will send a GET request sent to '/' (default) endpoint and looks for the presence of the following HTTP Headers in the received response: 
-The Valid directives are as belows:
-X-Content-Type-Options: nosniff 
-Strict-Transport-Security: max-age=&lt; [;includeSubDomains]</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Note:  To better debug the results of this QID, it is requested that customers execute commands to simulate the following functionality: curl -lkL --verbose. 
-CWE-693: Protection Mechanism Failure mentions the following - The product does not use or incorrectly uses a protection mechanism that provides sufficient defense against directed attacks against the product. A "missing" protection mechanism occurs when the application does not define any mechanism against a certain class of attack. An "insufficient" protection mechanism might provide some defenses - for example, against the most common attacks - but it does not protect against everything that is intended. Finally, an "ignored" mechanism occurs when a mechanism is available and in active use within the product, but the developer has not applied it in some code path. 
-Customers are advised to set proper X-Content-Type-Options (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/X-Content-Type-Options) and Strict-Transport-Security (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Strict-Transport-Security) HTTP response headers. 
-Depending on their server software, customers can set directives in their site configuration or Web.config files. Few examples are: 
-X-Content-Type-Options: 
-Apache: Header always set X-Content-Type-Options: nosniff 
-HTTP Strict-Transport-Security: 
-Apache: Header always set Strict-Transport-Security "max-age=31536000; includeSubDomains" 
-Nginx: add_header Strict-Transport-Security max-age=31536000; 
- Note: Network devices that include a HTTP/HTTPS console for administrative/management purposes often do not include all/some of the security headers. This is a known issue and it is recommend to contact the vendor for a solution.</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Depending on the vulnerability being exploited, an unauthenticated remote attacker could conduct cross-site scripting, clickjacking or MIME-type sniffing attacks.</t>
-        </is>
-      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
@@ -14877,13 +14228,7 @@
           <t>Content-Security-Policy HTTP Security Header Not Detected</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>The HTTP Content-Security-Policy response header allows web site administrators to control resources the user agent is allowed to load for a given page. This helps guard against cross-site scripting attacks (XSS). 
-QID Detection Logic: 
-This QID detects the absence of the Content-Security-Policy HTTP header by transmitting a GET request.</t>
-        </is>
-      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr"/>
@@ -15451,16 +14796,14 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
+          <t xml:space="preserve">No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
 1) no-referrer 
 2) no-referrer-when-downgrade 
 3) same-origin 
 4) origin 
 5) origin-when-cross-origin 
 6) strict-origin 
-7) strict-origin-when-cross-origin  
-QID Detection Logic(Unauthenticated): 
-If the Referrer Policy header is not found , checks in response body for meta tag containing tag name as "referrer" and one of the above Referrer Policy.</t>
+7) strict-origin-when-cross-origin  </t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16403,11 +15746,9 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Confluent is a fully managed Kafka service and enterprise stream processing platform.
+          <t xml:space="preserve">Confluent is a fully managed Kafka service and enterprise stream processing platform.
 Mapping of Confluent Platform and Apache Kafka can be done using the 
- Mapping Confluent Platform/Apache Kafka  (https://docs.confluent.io/current/installation/versions-interoperability.html) 
- QID Detection Logic:(authenticated) 
-This QID checks for the package Confluent Platform.</t>
+ Mapping Confluent Platform/Apache Kafka  (https://docs.confluent.io/current/installation/versions-interoperability.html) </t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -16622,14 +15963,7 @@
           <t>Apache Zookeeper Common/Default Nodes Accessible Without ACL</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Apache ZooKeeper is essentially a centralized service for distributed systems to a hierarchical key-value store, which is used to provide a distributed configuration service, synchronization service, and naming registry for large distributed systems.   
-Result section of this QID shows the nodes which are accessible without ACLs. 
- QID Detection Logic: (Unauthenticated): 
-This QID checks ACL for default node under root as well as the following common nodes: "/workers", "/config", "/admin", "/brokers","/cluster", "/consumers", "/controller", "/controller_epoch", "/isr_change_notification","/latest_producer_id_block", "/lgo_dir_event_notification", "/sasl_znode", "/datacenter","/datacenter/controlnodes", "/datacenter/controlnodes/cldb", "/nodes", "/servers", "/services","/services_config/nfs", "/services_config/webserver", "/zkmgr", "/kafka", "/kafka/config","/kafka-manager", "/kafka-manager/configs", "/kafka/admin", "/registry", "/mesos", "/hadoop-ha","/ansible", "/orion", "/master", "/hbase/master", "/cloudera", "/hive", "/accumulo"</t>
-        </is>
-      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
           <t>Workaround: Enable ACL on all the nodes</t>
@@ -16681,11 +16015,9 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>ZooKeeper is a centralized service for maintaining configuration information, naming, providing distributed synchronization, and providing group services. 
+          <t xml:space="preserve">ZooKeeper is a centralized service for maintaining configuration information, naming, providing distributed synchronization, and providing group services. 
 Apache ZooKeeper 3.4.x has reached EOL and will be effective from 1st of June, 2020 
-Currently supported versions of Apache ZooKeeper are 3.6.x, 3.7.x and 3.8.x 
-QID Detection Logic (Unauthenticated): 
-This QID checks the banner response to see if the server is running a vulnerable version of Apache ZooKeeper.</t>
+Currently supported versions of Apache ZooKeeper are 3.6.x, 3.7.x and 3.8.x </t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -16739,15 +16071,13 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Apache ZooKeeper is a centralized service for maintaining configuration information, naming, providing distributed synchronization, and providing group services. 
+          <t xml:space="preserve">Apache ZooKeeper is a centralized service for maintaining configuration information, naming, providing distributed synchronization, and providing group services. 
 CVE-2023-44981: Apache ZooKeeper is vulnerable to authorization bypass vulnerability. 
 Affected Versions: 
 Apache ZooKeeper 3.9.0 
 Apache ZooKeeper 3.8.0 through 3.8.2 
 Apache ZooKeeper 3.7.0 through 3.7.1 
-Apache ZooKeeper before 3.7.0 
-QID Detection Logic (Unauthenticated): 
-This QID checks the banner response to see if the server is running a vulnerable version of Apache ZooKeeper.</t>
+Apache ZooKeeper before 3.7.0 </t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -16969,9 +16299,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Apache ZooKeeper is essentially a centralized service for distributed systems to a hierarchical key-value store, which is used to provide a distributed configuration service, synchronization service, and naming registry for large distributed systems.  
- QID Detection Logic:(Unauthenticated) 
-This QID checks the banner to detect if the target is Apache Zookeeper or not.</t>
+          <t xml:space="preserve">Apache ZooKeeper is essentially a centralized service for distributed systems to a hierarchical key-value store, which is used to provide a distributed configuration service, synchronization service, and naming registry for large distributed systems.  </t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -17467,14 +16795,8 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PHP is a general purpose scripting language that is suited for web development and can be embedded in HTML.
- PHP 7.1 series reached End of Life in its support cycle on 1 Dec 2019.
- Since there are no further bug fixes or security updates for PHP 7.1 series, it's highly recommended to migrate from version 5.6 to newer supported versions.
- Affected Versions: 
-PHP 7.1.x versions
-QID Detection Logic: 
-Unauthenticated : This QID looks for PHP banner to detect affected versions remotely. 
-Authenticated : This QID checks for php.exe version using registry "HKLM\SOFTWARE\PHP " and flag if found vulnerable.</t>
+          <t xml:space="preserve"> Affected Versions: 
+PHP 7.1.x versions</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -17482,11 +16804,7 @@
           <t>Customers are advised to upgrade to the latest version of PHP.</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>The system is at high risk of being exposed to security vulnerabilities. Since the vendor no longer provides updates, obsolete software is more vulnerable to viruses and other attacks.</t>
-        </is>
-      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
@@ -17522,15 +16840,13 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
+          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
 CVE-2022-31630: In installed version of PHP, when using imageloadfont() function in gd extension, it is possible to supply a specially crafted font file, such as if the loaded font is used with imagechar() function, the read outside allocated buffer will be used. This can lead to crashes or disclosure of confidential information. 
 CVE-2022-37454: The Keccak XKCP SHA-3 reference implementation before fdc6fef has an integer overflow and resultant buffer overflow that allows attackers to execute arbitrary code or eliminate expected cryptographic properties.  
 Affected Versions: 
 PHP versions before 7.4.33 
 PHP versions 8.0.0 prior to 8.0.25 
-PHP versions 8.1.0 prior to 8.1.12 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP Server header to see if the server is running a vulnerable version of PHP.</t>
+PHP versions 8.1.0 prior to 8.1.12 </t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -17596,10 +16912,7 @@
  PHP 7.1 series reached End of Life in its support cycle on 1 Dec 2019.
  Since there are no further bug fixes or security updates for PHP 7.1 series, it's highly recommended to migrate from version 5.6 to newer supported versions.
  Affected Versions: 
-PHP 7.1.x versions
-QID Detection Logic: 
-Unauthenticated : This QID looks for PHP banner to detect affected versions remotely. 
-Authenticated : This QID checks for php.exe version using registry "HKLM\SOFTWARE\PHP " and flag if found vulnerable.</t>
+PHP 7.1.x versions</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -17653,11 +16966,9 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache HTTP Server versions 2.4.53 and earlier  
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions 2.4.53 and earlier  </t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -17719,16 +17030,14 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2022-28330: Apache HTTP Server 2.4.53 and earlier on Windows may read beyond bounds when configured to process requests with the mod_isapi module. 
 CVE-2022-28614: The ap_rwrite() function in Apache HTTP Server 2.4.53 and earlier may read unintended memory if an attacker can cause the server to reflect very large input using ap_rwrite() or ap_rputs(), such as with mod_luas r:puts() function. 
 CVE-2022-28615: Apache HTTP Server 2.4.53 and earlier may crash or disclose information due to a read beyond bounds in ap_strcmp_match() when provided with an extremely large input buffer. 
 CVE-2022-29404: In Apache HTTP Server 2.4.53 and earlier, a malicious request to a lua script that calls r:parsebody(0) may cause a denial of service due to no default limit on possible input size. 
 CVE-2022-30556: Apache HTTP Server 2.4.53 and earlier may return lengths to applications calling r:wsread() that point past the end of the storage allocated for the buffer. 
 Affected Versions: 
-Apache HTTP Server versions 2.4.53 and earlier  
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banners to detect if the target is running the vulnerable version of apache httpd.</t>
+Apache HTTP Server versions 2.4.53 and earlier  </t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -17790,13 +17099,9 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>In Apache HTTP Server 2.4 releases 2.4.17 to 2.4.38, with MPM event, worker or prefork, code executing in less-privileged child processes or threads (including scripts executed by an in-process scripting interpreter) could execute arbitrary code with the privileges of the parent process (usually root) by manipulating the scoreboard. Non-Unix systems are not affected.
+          <t xml:space="preserve">In Apache HTTP Server 2.4 releases 2.4.17 to 2.4.38, with MPM event, worker or prefork, code executing in less-privileged child processes or threads (including scripts executed by an in-process scripting interpreter) could execute arbitrary code with the privileges of the parent process (usually root) by manipulating the scoreboard. Non-Unix systems are not affected.
  Affected Versions: 
-2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.30, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17 
-QID Detection Logic (Unauthenticated): 
-This QID Checks for the vulnerable versions based on the exposed banner information under the HTTP service. 
-QID Detection Logic (Authenticated): 
-This QID Checks for the vulnerable versions of Apache HTTP Server based on version detected from the command.</t>
+2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.30, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17 </t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -17849,29 +17154,9 @@
           <t>PHP 7 Remote Code Execution Vulnerability</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
-PHP 7 is exposed to a remote code execution vulnerability due to a underflow issue in the 'env_path_info' in PHP-FPM.
-Affected Versions: 
-PHP 7 versions 7.3.x before 7.3.11, 7.2.x before 7.2.24, and 7.1.x before 7.1.33. 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP Server header to see if the server is running a vulnerable version of PHP.</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>Customers are advised to upgrade to the latest version of PHP (http://www.php.net/). For more information please visit the advisories.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  php download (http://php.net/downloads.php)</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>Successful exploitation of this vulnerability allows a remote attacker to execute arbitrary code on vulnerable server.</t>
-        </is>
-      </c>
+      <c r="B305" t="inlineStr"/>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
           <t>['CVE-2019-11043']</t>
@@ -17917,16 +17202,14 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
 Apache HTTP Server versions prior to 2.4.46. 
  NOTE:  
 CVE-2021-26691, CVE-2021-26690, CVE-2020-35452, CVE-2020-13938 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6, 2.4.4, 2.4.3, 2.4.2, 2.4.1, 2.4.0. 
 CVE-2019-17567 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6 
 CVE-2021-30641 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39 
-CVE-2020-13950 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+CVE-2020-13950 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41 </t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17988,11 +17271,9 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
+          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
 Affected Versions: 
-Apache HTTP Server 2.4.48 and earlier 
-QID Detection Logic:(Unauthenticated)
-This QID sends an HTTP GET request to the default page and checks for a match for a string "(Server:.*)(Apache)"; then checks for vulnerable versions of Apache HTTP.</t>
+Apache HTTP Server 2.4.48 and earlier </t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -18051,16 +17332,7 @@
           <t>Apache Hypertext Transfer Protocol (HTTP) Server Buffer Overflow Vulnerability</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-A carefully crafted request body can cause a buffer overflow in the mod_lua multipart parser (r:parsebody() called from Lua scripts). 
-Affected Versions: 
-Apache HTTP Server 2.4.51 and earlier 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for vulnerable Apache Version by grabbing the banner from HTTP response</t>
-        </is>
-      </c>
+      <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr">
         <is>
           <t>Customers are advised to update to Apache HTTP Server 2.4.52 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) 
@@ -18069,11 +17341,7 @@
   Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>Successful exploitation of the vulnerability may allow remote code execution and complete system compromise.&lt;/P&gt;</t>
-        </is>
-      </c>
+      <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
           <t>['CVE-2021-44790']</t>
@@ -18119,12 +17387,10 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
+          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
 A crafted URI sent to httpd configured as a forward proxy (ProxyRequests on) can cause a crash (NULL pointer dereference) or, for configurations mixing forward and reverse proxy declarations, can allow for requests to be directed to a declared Unix Domain Socket endpoint (Server Side Request Forgery). 
 Affected Versions: 
-Apache HTTP Server 2.4.7 - 2.4.51 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for vulnerable Apache Version by grabbing the banner from HTTP response</t>
+Apache HTTP Server 2.4.7 - 2.4.51 </t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -18252,12 +17518,10 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Some mod_proxy configurations on Apache HTTP Server versions 2.4.0 through 2.4.55 allow a HTTP Request Smuggling attack. 
+          <t xml:space="preserve">Some mod_proxy configurations on Apache HTTP Server versions 2.4.0 through 2.4.55 allow a HTTP Request Smuggling attack. 
 Configurations are affected when mod_proxy is enabled along with some form of RewriteRule or ProxyPassMatch in which a non-specific pattern matches some portion of the user-supplied request-target (URL) data and is then re-inserted into the proxied request-target using variable substitution.  
 Affected Versions: 
-Apache HTTP Server Versions 2.4.0 through 2.4.55 (including) 
-QID Detection Logic(Unauthenticated):  
-This QID checks for vulnerable version of Apache HTTP Server by sending a GET request to a target and extracting the version from the response header.</t>
+Apache HTTP Server Versions 2.4.0 through 2.4.55 (including) </t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -18318,13 +17582,9 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2006-20001: A carefully crafted If: request header can cause a memory read, or write of a single zero byte, in a pool (heap) memory location beyond the header value sent. This could cause the process to crash. 
-CVE-2022-37436: A malicious backend can cause the response headers to be truncated early, resulting in some headers being incorporated into the response body. If the later headers have any security purpose, they will not be interpreted by the client. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache HTTP Server versions prior to 2.4.55 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions prior to 2.4.55 </t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -18386,13 +17646,9 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2023-31122: Out-of-bounds Read vulnerability in mod_macro of Apache HTTP Server.This issue affects Apache HTTP Server 
-CVE-2023-45802: A client could send new requests and resets, keeping the connection busy and open and causing the memory footprint to keep on growing. On connection close, all resources were reclaimed, but the process might run out of memory before that. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache HTTP Server versions prior to 2.4.58 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions prior to 2.4.58 </t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -18454,12 +17710,10 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2022-36760: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to.  
 Affected Versions: 
-Apache HTTP Server from 2.4 through 2.4.54  
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server from 2.4 through 2.4.54  </t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -18521,12 +17775,10 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2022-26377: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to. 
 Affected Versions: 
-Apache HTTP Server versions 2.4 to 2.4.53  
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banners to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions 2.4 to 2.4.53  </t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -18588,19 +17840,9 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2024-38472: SSRF in Apache HTTP Server on Windows allows to potentially leak NTML hashes to a malicious server via SSRF and malicious requests or content 
-CVE-2024-38473: Apache HTTP Server proxy encoding problem 
-CVE-2024-38474: Apache HTTP Server weakness with encoded question marks in backreferences 
-CVE-2024-38475: Apache HTTP Server weakness in mod_rewrite when first segment of substitution matches filesystem path. 
-CVE-2024-38476: Apache HTTP Server may use exploitable/malicious backend application output to run local handlers via internal redirect 
-CVE-2024-38477: Apache HTTP Server Crash resulting in Denial of Service in mod_proxy via a malicious request 
-CVE-2024-39573: Apache HTTP Server mod_rewrite proxy handler substitution 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache HTTP Server versions prior to 2.4.60 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banners to detect if the target is running the vulnerable version of apache httpd. 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache HTTP Server versions prior to 2.4.60 </t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -18662,14 +17904,10 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-47252:  Apache HTTP Server: mod_ssl error log variable escaping 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -18731,13 +17969,9 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29169:  Apache HTTP Server: mod_dav_lock indirect lock crash 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -18799,13 +18033,9 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34059:  Apache HTTP Server: mod_proxy_ajp: Heap Over-Read and memory disclosure in  ajp_parse_data() 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -18940,13 +18170,11 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application.
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application.
  CVE-2020-1934: In Apache HTTP Server, mod_proxy_ftp may use uninitialized memory when proxying to a malicious FTP server. 
  CVE-2020-1927: In Apache HTTP Server, redirects configured with mod_rewrite that were intended to be self-referential might be fooled by encoded newlines and redirect instead to an an unexpected URL within the request URL. 
  Affected Versions: 
-Apache httpd 2.4.0 to 2.4.41 
- QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache httpd 2.4.0 to 2.4.41 </t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -19008,11 +18236,9 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
+          <t xml:space="preserve">PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
 Affected Versions: 
-PHP versions before 7.2.16 
-QID Detection Logic 
-The qid checks the php version via banner.</t>
+PHP versions before 7.2.16 </t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -19073,14 +18299,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
+          <t xml:space="preserve">PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
 PHP is affected by multiple vulnerabilities. 
 Affected Versions: 
 PHP versions prior to 7.4.24 
 PHP versions 7.3.x prior to 7.3.31 
-PHP versions 8.0.x prior to 8.0.11 
-QID Detection Logic 
-The qid checks the php version via banner.</t>
+PHP versions 8.0.x prior to 8.0.11 </t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -19141,16 +18365,14 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
+          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
 Affected versions of PHP has multiple vulnerabilities: 
 CVE-2022-31628 : The vulnerability exists due to infinite loop within the phar uncompressor code when processing "quines" gzip files. A remote attacker can pass a specially crafted archive to the application, consume all available system resources and cause denial of service conditions. 
 CVE-2022-31629: The vulnerability exists due to the way PHP handles HTTP variable names. A remote attacker can set a standard insecure cookie in the victim's browser which is treated as a '__Host-' or '__Secure-' cookie by PHP applications. 
 Affected Versions: 
 PHP versions before 7.4.31 
 PHP versions 8.0.0 prior to 8.0.24 
-PHP versions 8.1.0 prior to 8.1.11 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP Server header to see if the server is running a vulnerable version of PHP.</t>
+PHP versions 8.1.0 prior to 8.1.11 </t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -19278,15 +18500,7 @@
           <t>Apache Hypertext Transfer Protocol (HTTP) Server Response Smuggling Vulnerability</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>HTTP Response Smuggling vulnerability in Apache HTTP Server via mod_proxy_uwsgi. Special characters in the origin response header can truncate/split the response forwarded to the client. 
-Affected Versions: 
-This issue affects Apache HTTP Server: from 2.4.30 through 2.4.55 
-QID Detection Logic(Unauthenticated):  
-This QID checks for vulnerable version of Apache HTTP Server by sending a GET request to a target and extracting the version from the response header.</t>
-        </is>
-      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr">
         <is>
           <t>Customers are advised to upgrade to Apache HTTP Server version 2.4.56 or later. For more information please refer to  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56)
@@ -19345,13 +18559,11 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2023-38709: Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. 
 CVE-2024-24795: HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack.  
 Affected Versions: 
-Apache HTTP Server versions prior to 2.4.59 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server versions prior to 2.4.59 </t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -19413,14 +18625,10 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-49812:  Apache HTTP Server: mod_ssl TLS upgrade attack 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -19482,14 +18690,10 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-53020:  Apache HTTP Server: HTTP/2 DoS by Memory Increase 
 Affected Versions: 
-Apache httpd 2.4.17 through 2.4.63 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.17 through 2.4.63 </t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -19551,14 +18755,10 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2024-43394:  Apache HTTP Server: SSRF on Windows due to UNC paths 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -19620,14 +18820,10 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-23048:  Apache HTTP Server: mod_ssl access control bypass with session resumption 
 Affected Versions: 
-Apache httpd 2.4.35 through 2.4.63 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.35 through 2.4.63 </t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -19689,14 +18885,9 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2024-42516:  Apache HTTP Server: HTTP response splitting 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -19758,14 +18949,9 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-59775:  Apache HTTP Server: NTLM Leakage on Windows through UNC SSRF 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -19827,14 +19013,9 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-66200:  Apache HTTP Server: mod_userdir+suexec bypass via AllowOverride FileInfo 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -19896,14 +19077,9 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-58098:  Apache HTTP Server: Server Side Includes adds query string to exec cmd=... 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -19965,13 +19141,9 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33006:  Apache HTTP Server: mod_auth_digest timing attack 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20033,13 +19205,9 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-24072:  Apache HTTP Server: mod_rewrite elevation of privileges via ap_expr 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -20101,14 +19269,10 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44119:  escalation of privilege through expressions in .htaccess in multiple modules 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -20170,14 +19334,10 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44186:  Loop in `proxy_ftp_handler` in mod_proxy_ftp 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -20239,14 +19399,10 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-49975:  mod_http2 denial of service 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -20308,14 +19464,9 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34355:  mod_proxy_html buffer overflow 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -20377,14 +19528,9 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-43951:  OOB Read in `merge_response_headers` can cause crash 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -20446,14 +19592,9 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-42535:  mod_dav_fs protected directory access 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -20515,12 +19656,10 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
+          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
 A crafted method sent through HTTP/2 will bypass validation and be forwarded by mod_proxy, which can lead to request splitting or cache poisoning. 
 Affected Versions: 
-Apache HTTP Server 2.4.17 to 2.4.48. 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
+Apache HTTP Server 2.4.17 to 2.4.48. </t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -20579,16 +19718,7 @@
           <t>Apache Hypertext Transfer Protocol Server (HTTP Server) Denial of Service (DoS) Vulnerability</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-A carefully crafted request uri-path can cause mod_proxy_uwsgi to read above the allocated memory and crash (DoS). 
-Affected Versions: 
-Apache HTTP Server versions 2.4.30 to 2.4.48. 
-QID Detection Logic:(Unauthenticated) 
-This QID checks for server banner to detect if the target is running vulnerable version of apache httpd.</t>
-        </is>
-      </c>
+      <c r="B345" t="inlineStr"/>
       <c r="C345" t="inlineStr">
         <is>
           <t>Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). 
@@ -20647,14 +19777,9 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2024-43204:  Apache HTTP Server: SSRF with mod_headers setting Content-Type header 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.64 </t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -20716,14 +19841,9 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-49630:  Apache HTTP Server: mod_proxy_http2 denial of service 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.26 through 2.4.63 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.26 through 2.4.63 </t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -20785,14 +19905,10 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2025-65082:  Apache HTTP Server: CGI environment variable override 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -20854,14 +19970,9 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2025-55753:  Apache HTTP Server: mod_md (ACME), unintended retry intervals 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.66 </t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -20923,13 +20034,10 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-34032:  Apache HTTP Server: mod_proxy_ajp: Heap Buffer Over-Read Due to Missing Null-Termination Check (ajp_msg_get_string) 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -20991,13 +20099,10 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-33007:  Apache HTTP Server: mod_authn_socache crash 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21059,13 +20164,10 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-33857:  Apache HTTP Server: Off-by-one OOB reads in AJP getter functions 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
- Note : Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21127,14 +20229,10 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-33523:  Apache HTTP Server: multiple modules: HTTP response splitting forwarding malicious status line 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -21196,14 +20294,10 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-28780:  Apache HTTP Server: buffer overflow in mod_proxy_ajp via  ajp_msg_check_header() 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -21265,14 +20359,9 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29168:  Apache HTTP Server: mod_md unrestricted OCSP response 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.67 </t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -21334,14 +20423,9 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29170:  mod_proxy_ftp XSS 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -21403,14 +20487,9 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29167:  mod_ldap per-dir use-after-free 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -21472,14 +20551,9 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-42536:  mod_xml2enc heap overflow 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -21541,14 +20615,9 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44185:  Stack Buffer Over-Read in mod_ssl OCSP `send_request` 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -21610,14 +20679,10 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-34356:  ProxyPassReverseCookieMap buffer overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -21679,14 +20744,10 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is an HTTP web server application. 
+          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
 CVE-2026-44631:  Heap Underflow in `ap_regname` via Signed Char Overflow 
 Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 
-QID Detection Logic: 
-The remote detection reviews the Apache version from the banner of the HTTP Server. 
-The authenticated detections reviews Apache version from the command "httpd -v". 
-Note: Detection is made practice as it checks for server banners only</t>
+Apache httpd 2.4.x before 2.4.68 </t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -21746,13 +20807,7 @@
           <t>Content-Security-Policy HTTP Security Header Not Detected</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>The HTTP Content-Security-Policy response header allows web site administrators to control resources the user agent is allowed to load for a given page. This helps guard against cross-site scripting attacks (XSS). 
-QID Detection Logic: 
-This QID detects the absence of the Content-Security-Policy HTTP header by transmitting a GET request.</t>
-        </is>
-      </c>
+      <c r="B362" t="inlineStr"/>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr"/>
@@ -22097,15 +21152,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards. 
-Apache HTTP Server was detected on the target. 
-QID Detection Logic (Authenticated): 
-Operating System: Linux 
-The detection looks for Apache HTTP Server installation path using ps command. The version is extracted from the Apache HTTP Server's binary. 
-Operating System: Windows 
-This QID checks Windows registry to see if Apache HTTP Server is installed. If found, it displays the installed version. 
-QID Detection Logic (Unauthenticated): 
-This QID checks the HTTP response headers if the Apache web server is running on the target system.</t>
+          <t xml:space="preserve">The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards. </t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
@@ -22502,16 +21549,14 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
+          <t xml:space="preserve">No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
 1) no-referrer 
 2) no-referrer-when-downgrade 
 3) same-origin 
 4) origin 
 5) origin-when-cross-origin 
 6) strict-origin 
-7) strict-origin-when-cross-origin  
-QID Detection Logic(Unauthenticated): 
-If the Referrer Policy header is not found , checks in response body for meta tag containing tag name as "referrer" and one of the above Referrer Policy.</t>
+7) strict-origin-when-cross-origin  </t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -22660,14 +21705,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
 phpMyAdmin is prone to following vulnerabilities. 
 CVE-2018-19968:Local file inclusion through transformation feature 
 CVE-2018-19970:XSS vulnerability in navigation tree 
 Affected Versions: 
-phpMyAdmin versions from at least 4.0 through 4.8.3  
- QID Detection Logic (Unauthenticated): 
-This checks for vulnerable versions of phpMyadmin in Http header.</t>
+phpMyAdmin versions from at least 4.0 through 4.8.3  </t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -22729,9 +21772,8 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.&lt;/P&gt;  Phpmyadmin through 5.0.2 allows csv injection via export section.  Note: the vendor disputes this because "the csv file is accurately generated based on the database contents.  &lt;/P&gt; Affected versions 
-from 5.0.0.0 before 5.0.3.0 
- QID Detection Logic (unauthenticated):  This QID sends a HTTP GET request to "doc/html/index.html" and determines the vulnerable version of phpMyAdmin running on the target system.&lt;/P&gt;</t>
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.&lt;/P&gt;  Phpmyadmin through 5.0.2 allows csv injection via export section.  Note: the vendor disputes this because "the csv file is accurately generated based on the database contents.  &lt;/P&gt; Affected versions 
+from 5.0.0.0 before 5.0.3.0 </t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -22792,14 +21834,9 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
- Multiple vulnerabilities were reported in PhpMyAdmin  
- CVE-2018-12581:A Cross-Site Scripting vulnerability has been found where an attacker can use a crafted database name to trigger an XSS attack when that database is referenced from the Designer feature.  
- CVE-2018-12613: An issue was discovered in phpMyAdmin, in which an attacker can include (view and potentially execute) files on the server. The vulnerability comes from a portion of code where pages are redirected and loaded within phpMyAdmin, and an improper test for whitelisted pages. An attacker must be authenticated, except in the "$cfg['AllowArbitraryServer'] = true" case (where an attacker can specify any host he/she is already in control of, and execute arbitrary code on phpMyAdmin) and the "$cfg['ServerDefault'] = 0" case (which bypasses the login requirement and runs the vulnerable code without any authentication).  
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
  Affected Versions: 
-phpMyAdmin versions prior to 4.8.2  
- QID Detection Logic (Unauthenticated): 
-This checks for vulnerable versions of phpMyadmin in Http header</t>
+phpMyAdmin versions prior to 4.8.2  </t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -22811,11 +21848,7 @@
   PMASA-2018-3: PhpMyAdmin (https://www.phpmyadmin.net/security/PMASA-2018-3/)  PMASA-2018-4: PhpMyAdmin (https://www.phpmyadmin.net/security/PMASA-2018-4/)</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>Successful exploitation can result in file inclusion ,remote code execution and cross-site-scripting attack.</t>
-        </is>
-      </c>
+      <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
           <t>['CVE-2018-12581', 'CVE-2018-12613']</t>
@@ -22861,28 +21894,13 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
-A Cross-Site Scripting vulnerability was found in the file import feature, where an attacker can deliver a payload to a user through importing a specially-crafted file. 
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
 Affected Versions: 
-phpMyAdmin versions prior to 4.8.3  
- QID Detection Logic (Unauthenticated): 
-This checks for vulnerable versions of phpMyadmin in Http header.</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>Users are advised to upgrade to phpMyAdmin 4.8.3 or newer from phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php).
-For more information check PMASA-2018-5 (https://www.phpmyadmin.net/security/PMASA-2018-5/)
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PMASA-2018-5 (https://www.phpmyadmin.net/security/PMASA-2018-5/)</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>A remote user can access the target user's cookies (including authentication cookies), if any, associated with the site running the phpMyAdmin software, access data recently submitted by the target user via web form to the site, or take actions on the site acting as the target user.</t>
-        </is>
-      </c>
+phpMyAdmin versions prior to 4.8.3  </t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
           <t>['CVE-2018-15605']</t>
@@ -22928,13 +21946,11 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
 The software is exposed to Arbitrary file read vulnerability: 
 CVE-2019-6799
  Affected Versions: 
-phpMyAdmin versions from at least 4.0 through 4.8.4  
- QID Detection Logic (Unauthenticated): 
-This checks for vulnerable versions of phpMyadmin in http header.</t>
+phpMyAdmin versions from at least 4.0 through 4.8.4  </t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -22995,13 +22011,11 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
 The software is exposed to SQL injection vulnerability in Designer feature: 
 CVE-2019-6799
  Affected Versions: 
-phpMyAdmin versions from 4.5.0 through 4.8.4  
- QID Detection Logic (Unauthenticated): 
-This checks for vulnerable versions of phpMyadmin in http header.</t>
+phpMyAdmin versions from 4.5.0 through 4.8.4  </t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -23303,13 +22317,11 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
 CVE-2020-5504: A malicious user could inject custom SQL in place of their own username when creating queries to this page. 
  Affected Versions: 
 phpMyAdmin versions from 4.0.x prior to 4.9.4. 
-phpMyAdmin versions from 5.0.x prior to 5.0.1. 
-QID Detection Logic (unauthenticated): 
-Look for vulnerable version of phpmyadmin installed.</t>
+phpMyAdmin versions from 5.0.x prior to 5.0.1. </t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -23370,28 +22382,19 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
 The software is exposed to the XSRF/CSRF vulnerability: 
 CVE-2019-12922
 Affected Versions: 
-phpMyAdmin versions prior to 4.9.1  
- QID Detection Logic (Unauthenticated): 
-This checks for vulnerable versions of phpMyadmin in Http header.</t>
+phpMyAdmin versions prior to 4.9.1  </t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Users are advised to upgrade to phpMyAdmin 4.8.4 or newer from phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php).
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  phpMyAdmin (https://seclists.org/fulldisclosure/2019/Sep/23)</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>By deceiving a user to click on a crafted URL, it is possible for an attacker to execute arbitrary SQL commands.</t>
-        </is>
-      </c>
+          <t>Users are advised to upgrade to phpMyAdmin 4.8.4 or newer from phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php).</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
           <t>['CVE-2019-12922']</t>
@@ -23437,12 +22440,10 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
 CVE-2019-12616: A vulnerability was found that allows an attacker to trigger a CSRF attack against a phpMyAdmin user. 
  Affected Versions: 
-phpMyAdmin versions prior to 4.9.0. 
-QID Detection Logic (unauthenticated): 
-Look for vulnerable version of phpmyadmin installed.</t>
+phpMyAdmin versions prior to 4.9.0. </t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -23503,12 +22504,10 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
 CVE-2022-0813: PhpMyAdmin 5.1.1 and before allows an attacker to retrieve potentially sensitive information by creating invalid requests. This affects the lang parameter, the pma_parameter, and the cookie section. 
  Affected Versions: 
-PhpMyAdmin version 5.1.1 and before. 
-QID Detection Logic (unauthenticated): 
-This QID sends a HTTP GET request to "doc/html/index.html" and determines the vulnerable version of phpMyAdmin running on the target system.</t>
+PhpMyAdmin version 5.1.1 and before. </t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -23569,13 +22568,11 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
+          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
 An XSS vulnerability has been discovered where an authenticated user can trigger an XSS attack by uploading a specially-crafted .sql file through the drag-and-drop interface. 
  Affected Versions: 
 phpMyAdmin versions from 4.3.0 prior to 4.9.1 
-phpMyAdmin versions from 5.0 prior to 5.2.1 
-QID Detection Logic (unauthenticated): 
-This QID sends a HTTP GET request to "doc/html/index.html" and determines the vulnerable version of phpMyAdmin running on the target system.</t>
+phpMyAdmin versions from 5.0 prior to 5.2.1 </t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -23935,17 +22932,8 @@
           <t>Open TCP Services List</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
-        </is>
-      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
           <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
@@ -24112,13 +23100,7 @@
           <t>PhpMyAdmin Detected</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>phpMyAdmin is a free software tool written in PHP, intended to handle the administration of MySQL over the Web. phpMyAdmin supports a wide range of operations on MySQL and MariaDB. 
-QID Detection Logic (Unauthenicated): 
-The qid sends a GET request to "doc/html/index.html" and "Documentation.html" pages to retrieve the PhpMyAdmin version.</t>
-        </is>
-      </c>
+      <c r="B406" t="inlineStr"/>
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr"/>
@@ -24254,11 +23236,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Nginx is a web server which can also be used as a reverse proxy, load balancer , mail proxy and HTTP cache. 
- QID Detection Logic:(authenticated) 
-This QID checks for the version from the nignx binary, the path is extracted via running processes. 
- QID Detection Logic:(unauthenticated) 
-This QID checks for the nginx web server by sending a GET / request and checking the response header.</t>
+          <t xml:space="preserve">Nginx is a web server which can also be used as a reverse proxy, load balancer , mail proxy and HTTP cache. </t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>

--- a/resources/qualys/Qualys_VulnLab_scan-b.xlsx
+++ b/resources/qualys/Qualys_VulnLab_scan-b.xlsx
@@ -486,20 +486,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The secure cookie flag is an option that can be set by the application server when sending a new cookie to the user within an HTTP Response. The purpose of the secure flag is to prevent cookies from being observed by unauthorized parties due to the transmission of a the cookie in clear text. By setting the secure flag, the browser will prevent the transmission of a cookie over an unencrypted channel. 
-A cookie with the secure attribute was not detected in the scan. 
-QID Detection Logic: 
-This unauthenticated QID checks for the existence of the "secure" cookie flag.</t>
+          <t>['The secure cookie flag is an option that can be set by the application server when sending a new cookie to the user within an HTTP Response. The purpose of the secure flag is to prevent cookies from being observed by unauthorized parties due to the transmission of a the cookie in clear text. By setting the secure flag, the browser will prevent the transmission of a cookie over an unencrypted channel. A cookie with the secure attribute was not detected in the scan. QID Detection Logic: This unauthenticated QID checks for the existence of the "secure" cookie flag.']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Apply the "secure" attribute to session cookies to ensure that they are sent via HTTPS only. More information about this flag can be found here: https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Set-Cookie.</t>
+          <t>['Apply the "secure" attribute to session cookies to ensure that they are sent via HTTPS only. More information about this flag can be found here: https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Set-Cookie.']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Session cookies sent via HTTP expose users to sniffing attacks that could lead to user impersonation or account compromise.</t>
+          <t>['Session cookies sent via HTTP expose users to sniffing attacks that could lead to user impersonation or account compromise.']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -543,23 +540,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Web server allows form based authentication without disabling the AutoComplete feature for the password field. 
-Autocomplete should be turned off for any input that takes sensitive information such as credit card number, CVV2/CVC code, U.S. social security number, etc.</t>
+          <t>['The Web server allows form based authentication without disabling the AutoComplete feature for the password field. Autocomplete should be turned off for any input that takes sensitive information such as credit card number, CVV2/CVC code, U.S. social security number, etc.']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Contact the vendor to have the AutoComplete attribute disabled for the password field in all forms. The AutoComplete attribute should also be disabled for the user ID field.  
-Developers can add the following attribute to the form or input element: autocomplete="off"  
-This attribute prevents the browser from prompting the user to save the populated form values for later reuse.   
-Most browsers no longer honor autocomplete="off" for password input fields. These browsers include  Chrome, Firefox, Microsoft Edge, IE, Opera 
-However, there is still an ability to turn off autocomplete through the browser and that is recommended for a shared computing environment. 
-Since the ability to turn autocomplete off for password inputs fields is controlled by the user it is highly recommended for application to enforce strong password rules.</t>
+          <t>['Contact the vendor to have the AutoComplete attribute disabled for the password field in all forms. The AutoComplete attribute should also be disabled for the user ID field. Developers can add the following attribute to the form or input element: autocomplete="off" This attribute prevents the browser from prompting the user to save the populated form values for later reuse. Most browsers no longer honor autocomplete="off" for password input fields. These browsers include Chrome, Firefox, Microsoft Edge, IE, Opera However, there is still an ability to turn off autocomplete through the browser and that is recommended for a shared computing environment. Since the ability to turn autocomplete off for password inputs fields is controlled by the user it is highly recommended for application to enforce strong password rules.']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>If the browser is used in a shared computing environment where more than one person may use the browser, then "autocomplete" values may be retrieved or submitted by an unauthorized user.</t>
+          <t>['If the browser is used in a shared computing environment where more than one person may use the browser, then "autocomplete" values may be retrieved or submitted by an unauthorized user.']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -645,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.</t>
+          <t>['This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.']</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -691,7 +682,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -731,8 +722,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -772,7 +762,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -812,7 +802,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -852,18 +842,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -901,14 +890,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -948,7 +930,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -988,8 +970,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1029,7 +1010,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server.</t>
+          <t>['The Result section displays the default Web page for the Web server.']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1075,7 +1056,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server following HTTP redirections.</t>
+          <t>['The Result section displays the default Web page for the Web server following HTTP redirections.']</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1121,7 +1102,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The HTTP methods returned in response to an OPTIONS request to the Web server detected on the target host are listed.</t>
+          <t>['The HTTP methods returned in response to an OPTIONS request to the Web server detected on the target host are listed.']</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1167,9 +1148,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request.  
-QID Detection Logic: 
-This QID returns the HTTP response method and header information returned by a web server.</t>
+          <t>["This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request. QID Detection Logic: This QID returns the HTTP response method and header information returned by a web server."]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1215,27 +1194,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
-1) no-referrer 
-2) no-referrer-when-downgrade 
-3) same-origin 
-4) origin 
-5) origin-when-cross-origin 
-6) strict-origin 
-7) strict-origin-when-cross-origin  </t>
+          <t>['No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 1) no-referrer 2) no-referrer-when-downgrade 3) same-origin 4) origin 5) origin-when-cross-origin 6) strict-origin 7) strict-origin-when-cross-origin']</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Referrer Policy header improves security by ensuring websites don't leak sensitive information via the referrer header. It's recommended to add secure Referrer Policies as a part of a defense-in-depth approach. 
-References: 
-- https://www.w3.org/TR/referrer-policy/ (https://www.w3.org/TR/referrer-policy/) 
-- https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy)</t>
+          <t>["Referrer Policy header improves security by ensuring websites don't leak sensitive information via the referrer header. It's recommended to add secure Referrer Policies as a part of a defense-in-depth approach.", 'References: - https://www.w3.org/TR/referrer-policy/ (https://www.w3.org/TR/referrer-policy/) - https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy)']</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>The Referrer-Policy header controls how much referrer information is sent to a site when navigating to it. Absence of Referrer-Policy header can lead to leakage of sensitive information via the referrer header.</t>
+          <t>['The Referrer-Policy header controls how much referrer information is sent to a site when navigating to it. Absence of Referrer-Policy header can lead to leakage of sensitive information via the referrer header.']</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1279,15 +1248,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UrlScan is a security tool offered by Microsoft that restricts the types of HTTP requests that Internet Information Services (IIS) will process. By blocking specific HTTP requests, the UrlScan security tool helps prevent potentially harmful requests from reaching the server.
-A weakness has been reported for URLScan that may result in the disclosure of sensitive information. The weakness exists because of the way URLScan handles HEAD HTTP requests. Specifically, when URLScan receives a HEAD request that is subsequently rejected, it is automatically converted to a GET request and sent to the underlying IIS server. As a result, the appropriate reject page is delivered to a requesting client.</t>
+          <t>['UrlScan is a security tool offered by Microsoft that restricts the types of HTTP requests that Internet Information Services (IIS) will process. By blocking specific HTTP requests, the UrlScan security tool helps prevent potentially harmful requests from reaching the server.', 'A weakness has been reported for URLScan that may result in the disclosure of sensitive information. The weakness exists because of the way URLScan handles HEAD HTTP requests. Specifically, when URLScan receives a HEAD request that is subsequently rejected, it is automatically converted to a GET request and sent to the underlying IIS server. As a result, the appropriate reject page is delivered to a requesting client.']</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>The information returned may allow an attacker to identify systems that incorporate the use of URLScan.
-The target host may not have been tested to the full extent due to the presence of this utility.</t>
+          <t>['The information returned may allow an attacker to identify systems that incorporate the use of URLScan.', 'The target host may not have been tested to the full extent due to the presence of this utility.']</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1331,14 +1298,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.
-The target Web server was found to support this functionality of the HTTP 1.1 protocol.</t>
+          <t>['Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.', 'The target Web server was found to support this functionality of the HTTP 1.1 protocol.']</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.</t>
+          <t>['Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.']</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1382,7 +1348,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Based largely on the HTTP reply code, the following directories are most likely present on the host.</t>
+          <t>['Based largely on the HTTP reply code, the following directories are most likely present on the host.']</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1428,17 +1394,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Web server uses plain-text form based authentication. A web page exists on the target host which uses an HTML login form. This data is sent from the client to the server in plain-text.</t>
+          <t>['The Web server uses plain-text form based authentication. A web page exists on the target host which uses an HTML login form. This data is sent from the client to the server in plain-text.']</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Please contact the vendor of the hardware/software for a possible fix for the issue. For custom applications, ensure that data sent via HTML login forms is encrypted before being sent from the client to the host.</t>
+          <t>['Please contact the vendor of the hardware/software for a possible fix for the issue. For custom applications, ensure that data sent via HTML login forms is encrypted before being sent from the client to the host.']</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>An attacker with access to the network traffic to and from the target host may be able to obtain login credentials for other users by sniffing the network traffic.</t>
+          <t>['An attacker with access to the network traffic to and from the target host may be able to obtain login credentials for other users by sniffing the network traffic.']</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1482,21 +1448,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PHP is a general purpose scripting language that is suited for web development and can be embedded in HTML.
- PHP 7.0 series reached End of Life in its support cycle on 10 Jan 2019.
- Since there are no further bug fixes or security updates for PHP 7.0 series, it's highly recommended to migrate from version 5.6 to newer supported versions.
- Affected Versions: 
-PHP 7.0.x versions</t>
+          <t>['PHP is a general purpose scripting language that is suited for web development and can be embedded in HTML.', 'PHP 7.0 series reached End of Life in its support cycle on 10 Jan 2019.', "Since there are no further bug fixes or security updates for PHP 7.0 series, it's highly recommended to migrate from version 5.6 to newer supported versions.", 'Affected Versions: PHP 7.0.x versions']</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP.</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP.']</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>The system is at high risk of being exposed to security vulnerabilities. Since the vendor no longer provides updates, obsolete software is more vulnerable to viruses and other attacks.</t>
+          <t>['The system is at high risk of being exposed to security vulnerabilities. Since the vendor no longer provides updates, obsolete software is more vulnerable to viruses and other attacks.']</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1534,27 +1496,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
-CVE-2022-31630: In installed version of PHP, when using imageloadfont() function in gd extension, it is possible to supply a specially crafted font file, such as if the loaded font is used with imagechar() function, the read outside allocated buffer will be used. This can lead to crashes or disclosure of confidential information. 
-CVE-2022-37454: The Keccak XKCP SHA-3 reference implementation before fdc6fef has an integer overflow and resultant buffer overflow that allows attackers to execute arbitrary code or eliminate expected cryptographic properties.  
-Affected Versions: 
-PHP versions before 7.4.33 
-PHP versions 8.0.0 prior to 8.0.25 
-PHP versions 8.1.0 prior to 8.1.12 </t>
+          <t>['PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications.', 'CVE-2022-31630: In installed version of PHP, when using imageloadfont() function in gd extension, it is possible to supply a specially crafted font file, such as if the loaded font is used with imagechar() function, the read outside allocated buffer will be used. This can lead to crashes or disclosure of confidential information. CVE-2022-37454: The Keccak XKCP SHA-3 reference implementation before fdc6fef has an integer overflow and resultant buffer overflow that allows attackers to execute arbitrary code or eliminate expected cryptographic properties.', 'Affected Versions: PHP versions before 7.4.33 PHP versions 8.0.0 prior to 8.0.25 PHP versions 8.1.0 prior to 8.1.12']</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) 
-For more information please refer to Sec Bug 81739 (https://bugs.php.net/bug.php?id=81739) . 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  81739 (https://bugs.php.net/bug.php?id=81739)  81738 (http://bugs.php.net/81738)</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) For more information please refer to Sec Bug 81739 (https://bugs.php.net/bug.php?id=81739) . Patch: Following are links for downloading patches to fix the vulnerabilities: 81739 (https://bugs.php.net/bug.php?id=81739) 81738 (http://bugs.php.net/81738)']</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Successful exploitation of the vulnerability may allow an attacker to crash the PHP process or Denial of Service (DoS) or tackers to execute arbitrary code on the system.</t>
+          <t>['Successful exploitation of the vulnerability may allow an attacker to crash the PHP process or Denial of Service (DoS) or tackers to execute arbitrary code on the system.']</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1602,24 +1554,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache Web Server is an open-source web server. 
-Uninitialized memory reflection in mod_auth_digest leading to leakage of potentially confidential information, and a segfault. 
-Affected Versions: 
-Apache httpd 2.2.x before 2.2.34 
-Apache httpd 2.4.x before 2.4.27 </t>
+          <t>['Apache Web Server is an open-source web server. Uninitialized memory reflection in mod_auth_digest leading to leakage of potentially confidential information, and a segfault.', 'Affected Versions: Apache httpd 2.2.x before 2.2.34 Apache httpd 2.4.x before 2.4.27']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to Apache httpd 2.2.34, 2.4.27 (https://httpd.apache.org/download.cgi) or later versions to remediate this vulnerability.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache httpd 2.2.34, 2.4.27 or later (https://httpd.apache.org/download.cgi)</t>
+          <t>['Customers are advised to upgrade to Apache httpd 2.2.34, 2.4.27 (https://httpd.apache.org/download.cgi) or later versions to remediate this vulnerability. Patch: Following are links for downloading patches to fix the vulnerabilities: Apache httpd 2.2.34, 2.4.27 or later (https://httpd.apache.org/download.cgi)']</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an attacker to make the targeted server unavailable and cause denial of service.</t>
+          <t>['Successful exploitation of this vulnerability may allow an attacker to make the targeted server unavailable and cause denial of service.']</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1667,23 +1612,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache HTTP Server versions 2.4.53 and earlier  </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'Affected Versions: Apache HTTP Server versions 2.4.53 and earlier']</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html).
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache httpd (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache httpd (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Successful exploitation allows information disclosure and possible remote code execution</t>
+          <t>['Successful exploitation allows information disclosure and possible remote code execution']</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1731,28 +1670,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2022-28330: Apache HTTP Server 2.4.53 and earlier on Windows may read beyond bounds when configured to process requests with the mod_isapi module. 
-CVE-2022-28614: The ap_rwrite() function in Apache HTTP Server 2.4.53 and earlier may read unintended memory if an attacker can cause the server to reflect very large input using ap_rwrite() or ap_rputs(), such as with mod_luas r:puts() function. 
-CVE-2022-28615: Apache HTTP Server 2.4.53 and earlier may crash or disclose information due to a read beyond bounds in ap_strcmp_match() when provided with an extremely large input buffer. 
-CVE-2022-29404: In Apache HTTP Server 2.4.53 and earlier, a malicious request to a lua script that calls r:parsebody(0) may cause a denial of service due to no default limit on possible input size. 
-CVE-2022-30556: Apache HTTP Server 2.4.53 and earlier may return lengths to applications calling r:wsread() that point past the end of the storage allocated for the buffer. 
-Affected Versions: 
-Apache HTTP Server versions 2.4.53 and earlier  </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2022-28330: Apache HTTP Server 2.4.53 and earlier on Windows may read beyond bounds when configured to process requests with the mod_isapi module. CVE-2022-28614: The ap_rwrite() function in Apache HTTP Server 2.4.53 and earlier may read unintended memory if an attacker can cause the server to reflect very large input using ap_rwrite() or ap_rputs(), such as with mod_luas r:puts() function. CVE-2022-28615: Apache HTTP Server 2.4.53 and earlier may crash or disclose information due to a read beyond bounds in ap_strcmp_match() when provided with an extremely large input buffer. CVE-2022-29404: In Apache HTTP Server 2.4.53 and earlier, a malicious request to a lua script that calls r:parsebody(0) may cause a denial of service due to no default limit on possible input size. CVE-2022-30556: Apache HTTP Server 2.4.53 and earlier may return lengths to applications calling r:wsread() that point past the end of the storage allocated for the buffer.', 'Affected Versions: Apache HTTP Server versions 2.4.53 and earlier']</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise Confidentiality, Integrity, and Availability of the Data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise Confidentiality, Integrity, and Availability of the Data.']</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1800,27 +1728,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Apache Web Server is an open-source web server. 
-On systems with the Limit directive set within a '.htaccess' file and set to an invalid HTTP method, a remote user can send a specially crafted HTTP OPTIONS request for a path to trigger a use-after-free memory error and view potentially sensitive information from process memory on the target system. 
-This vulnerability is referred to as "Optionsbleed". 
-Apache HTTP Server through 2.2.34 and 2.4.x through 2.4.27 
-QID Detection Logic (Un-authenticated) 
-This will check for vulnerable versions of Apache httpd server remotely by reviewing the httpd banner.</t>
+          <t>['Apache Web Server is an open-source web server. On systems with the Limit directive set within a \'.htaccess\' file and set to an invalid HTTP method, a remote user can send a specially crafted HTTP OPTIONS request for a path to trigger a use-after-free memory error and view potentially sensitive information from process memory on the target system. This vulnerability is referred to as "Optionsbleed". Apache HTTP Server through 2.2.34 and 2.4.x through 2.4.27 QID Detection Logic (Un-authenticated) This will check for vulnerable versions of Apache httpd server remotely by reviewing the httpd banner.']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The Apache HTTP Project released patch version (2.4.28) to resolve this issue.  
-Refer to Apache security advisory CVE-2017-9798. (https://httpd.apache.org/security/vulnerabilities_24.html)  
-If you are using a Linux distribution, please refer to your Linux vendor for further information and updates. 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache httpd 2.4.28: Apache (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['The Apache HTTP Project released patch version (2.4.28) to resolve this issue. Refer to Apache security advisory CVE-2017-9798. (https://httpd.apache.org/security/vulnerabilities_24.html) If you are using a Linux distribution, please refer to your Linux vendor for further information and updates. Patch: Following are links for downloading patches to fix the vulnerabilities: Apache httpd 2.4.28: Apache (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A remote user can obtain potentially sensitive information on the target system in certain cases.</t>
+          <t>['A remote user can obtain potentially sensitive information on the target system in certain cases.']</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1862,22 +1780,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Apache HTTP Server 2.4 releases 2.4.17 to 2.4.38, with MPM event, worker or prefork, code executing in less-privileged child processes or threads (including scripts executed by an in-process scripting interpreter) could execute arbitrary code with the privileges of the parent process (usually root) by manipulating the scoreboard. Non-Unix systems are not affected.
- Affected Versions: 
-2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.30, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17 </t>
+          <t>['In Apache HTTP Server 2.4 releases 2.4.17 to 2.4.38, with MPM event, worker or prefork, code executing in less-privileged child processes or threads (including scripts executed by an in-process scripting interpreter) could execute arbitrary code with the privileges of the parent process (usually root) by manipulating the scoreboard. Non-Unix systems are not affected. Affected Versions: 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.30, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>This vulnerability have been patched in Apache. Refer to  Apache httpd 2.4.39 Changelog (https://httpd.apache.org/security/vulnerabilities_24.html) or your Linux distro for further details. 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache httpd 2.4.39 (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['This vulnerability have been patched in Apache. Refer to Apache httpd 2.4.39 Changelog (https://httpd.apache.org/security/vulnerabilities_24.html) or your Linux distro for further details. Patch: Following are links for downloading patches to fix the vulnerabilities: Apache httpd 2.4.39 (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Successful exploitation allows a remote attacker to use this vulnerability to execute arbitrary code with the privileges of the parent process.</t>
+          <t>['Successful exploitation allows a remote attacker to use this vulnerability to execute arbitrary code with the privileges of the parent process.']</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1919,22 +1832,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Apache Module mod_mime is used to assign content metadata to the content selected for an HTTP response by mapping patterns in the URI or filenames to the metadata values. 
-In Apache httpd 2.2.x before 2.2.33 and 2.4.x before 2.4.26, mod_mime can read one byte past the end of a buffer when sending a malicious Content-Type response header. </t>
+          <t>['The Apache Module mod_mime is used to assign content metadata to the content selected for an HTTP response by mapping patterns in the URI or filenames to the metadata values.', 'In Apache httpd 2.2.x before 2.2.33 and 2.4.x before 2.4.26, mod_mime can read one byte past the end of a buffer when sending a malicious Content-Type response header.']</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>These vulnerabilities have been patched in Apache. Refer to  Apache httpd 2.4.27 Changelog (https://httpd.apache.org/security/vulnerabilities_24.html), 
-Apache httpd 2.2.34 Changelog (https://httpd.apache.org/security/vulnerabilities_22.html), or your Linux distro for further details. 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  CVE-2017-7679: Apache 2.2.x (https://httpd.apache.org/security/vulnerabilities_22.html)  CVE-2017-7679: Apache 2.4.x (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['These vulnerabilities have been patched in Apache. Refer to Apache httpd 2.4.27 Changelog (https://httpd.apache.org/security/vulnerabilities_24.html), Apache httpd 2.2.34 Changelog (https://httpd.apache.org/security/vulnerabilities_22.html), or your Linux distro for further details. Patch: Following are links for downloading patches to fix the vulnerabilities: CVE-2017-7679: Apache 2.2.x (https://httpd.apache.org/security/vulnerabilities_22.html) CVE-2017-7679: Apache 2.4.x (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A remote attacker could exploit this vulnerability to read one byte past the end of a buffer which could affect the confidentiality, integrity and availability of data on the target system.</t>
+          <t>['A remote attacker could exploit this vulnerability to read one byte past the end of a buffer which could affect the confidentiality, integrity and availability of data on the target system.']</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1976,28 +1884,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.46. 
- NOTE:  
-CVE-2021-26691, CVE-2021-26690, CVE-2020-35452, CVE-2020-13938 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6, 2.4.4, 2.4.3, 2.4.2, 2.4.1, 2.4.0. 
-CVE-2019-17567 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6 
-CVE-2021-30641 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39 
-CVE-2020-13950 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'Affected Versions: Apache HTTP Server versions prior to 2.4.46.', 'NOTE: CVE-2021-26691, CVE-2021-26690, CVE-2020-35452, CVE-2020-13938 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6, 2.4.4, 2.4.3, 2.4.2, 2.4.1, 2.4.0. CVE-2019-17567 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6 CVE-2021-30641 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39 CVE-2020-13950 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41']</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Customers are advised to update Apache httpd 2.4.48. 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html).
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server 2.4.47 (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update Apache httpd 2.4.48. For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server 2.4.47 (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an attacker to execute arbitrary code on the target.</t>
+          <t>['Successful exploitation of this vulnerability may allow an attacker to execute arbitrary code on the target.']</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2045,22 +1942,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-Affected Versions: 
-Apache HTTP Server 2.4.48 and earlier </t>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'Affected Versions: Apache HTTP Server 2.4.48 and earlier']</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an attacker to execute arbitrary code on the target.</t>
+          <t>['Successful exploitation of this vulnerability may allow an attacker to execute arbitrary code on the target.']</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2108,23 +2000,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-A carefully crafted request body can cause a buffer overflow in the mod_lua multipart parser (r:parsebody() called from Lua scripts). 
-Affected Versions: 
-Apache HTTP Server 2.4.51 and earlier </t>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'A carefully crafted request body can cause a buffer overflow in the mod_lua multipart parser (r:parsebody() called from Lua scripts).', 'Affected Versions: Apache HTTP Server 2.4.51 and earlier']</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.52 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.52 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Successful exploitation of the vulnerability may allow remote code execution and complete system compromise.&lt;/P&gt;</t>
+          <t>['Successful exploitation of the vulnerability may allow remote code execution and complete system compromise.&lt;/P&gt;']</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2172,23 +2058,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-A crafted URI sent to httpd configured as a forward proxy (ProxyRequests on) can cause a crash (NULL pointer dereference) or, for configurations mixing forward and reverse proxy declarations, can allow for requests to be directed to a declared Unix Domain Socket endpoint (Server Side Request Forgery). 
-Affected Versions: 
-Apache HTTP Server 2.4.7 - 2.4.51 </t>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'A crafted URI sent to httpd configured as a forward proxy (ProxyRequests on) can cause a crash (NULL pointer dereference) or, for configurations mixing forward and reverse proxy declarations, can allow for requests to be directed to a declared Unix Domain Socket endpoint (Server Side Request Forgery).', 'Affected Versions: Apache HTTP Server 2.4.7 - 2.4.51']</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.52 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.52 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Successful exploitation of the vulnerability may allow an attacker to redirect victim to a malicious server.&lt;/P&gt;</t>
+          <t>['Successful exploitation of the vulnerability may allow an attacker to redirect victim to a malicious server.&lt;/P&gt;']</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2236,26 +2116,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-CVE-2022-22719 - A carefully crafted request body can cause a read to a random memory area which could cause the process to crash.  
-CVE-2022-22720 - Apache HTTP Server 2.4.52 and earlier fails to close inbound connection when errors are encountered discarding the request body, exposing the server to HTTP Request Smuggling  
-CVE-2022-22721 - If LimitXMLRequestBody is set to allow request bodies larger than 350MB (defaults to 1M) on 32 bit systems an integer overflow happens which later causes out of bounds writes. 
-CVE-2022-23943 - Out-of-bounds Write vulnerability in mod_sed of Apache HTTP Server allows an attacker to overwrite heap memory with possibly attacker provided data. 
-Affected Versions: 
-Apache HTTP Server 2.4 - 2.4.52</t>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'CVE-2022-22719 - A carefully crafted request body can cause a read to a random memory area which could cause the process to crash. CVE-2022-22720 - Apache HTTP Server 2.4.52 and earlier fails to close inbound connection when errors are encountered discarding the request body, exposing the server to HTTP Request Smuggling CVE-2022-22721 - If LimitXMLRequestBody is set to allow request bodies larger than 350MB (defaults to 1M) on 32 bit systems an integer overflow happens which later causes out of bounds writes. CVE-2022-23943 - Out-of-bounds Write vulnerability in mod_sed of Apache HTTP Server allows an attacker to overwrite heap memory with possibly attacker provided data.', 'Affected Versions: Apache HTTP Server 2.4 - 2.4.52']</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.53 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.53 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Successful exploitation of the vulnerability may allow an attacker to redirect victim to a malicious server.</t>
+          <t>['Successful exploitation of the vulnerability may allow an attacker to redirect victim to a malicious server.']</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2303,23 +2174,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Some mod_proxy configurations on Apache HTTP Server versions 2.4.0 through 2.4.55 allow a HTTP Request Smuggling attack. 
-Configurations are affected when mod_proxy is enabled along with some form of RewriteRule or ProxyPassMatch in which a non-specific pattern matches some portion of the user-supplied request-target (URL) data and is then re-inserted into the proxied request-target using variable substitution.  
-Affected Versions: 
-Apache HTTP Server Versions 2.4.0 through 2.4.55 (including) </t>
+          <t>['Some mod_proxy configurations on Apache HTTP Server versions 2.4.0 through 2.4.55 allow a HTTP Request Smuggling attack. Configurations are affected when mod_proxy is enabled along with some form of RewriteRule or ProxyPassMatch in which a non-specific pattern matches some portion of the user-supplied request-target (URL) data and is then re-inserted into the proxied request-target using variable substitution.', 'Affected Versions: Apache HTTP Server Versions 2.4.0 through 2.4.55 (including)']</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to Apache HTTP Server version 2.4.56 or later. For more information please refer to  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56)
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56)</t>
+          <t>['Customers are advised to upgrade to Apache HTTP Server version 2.4.56 or later. For more information please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56)']</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Request splitting/smuggling could result in bypass of access controls in the proxy server, proxying unintended URLs to existing origin servers, and cache poisoning.</t>
+          <t>['Request splitting/smuggling could result in bypass of access controls in the proxy server, proxying unintended URLs to existing origin servers, and cache poisoning.']</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2367,25 +2232,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2006-20001: A carefully crafted If: request header can cause a memory read, or write of a single zero byte, in a pool (heap) memory location beyond the header value sent. This could cause the process to crash. 
-CVE-2022-37436: A malicious backend can cause the response headers to be truncated early, resulting in some headers being incorporated into the response body. If the later headers have any security purpose, they will not be interpreted by the client. 
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.55 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2006-20001: A carefully crafted If: request header can cause a memory read, or write of a single zero byte, in a pool (heap) memory location beyond the header value sent. This could cause the process to crash. CVE-2022-37436: A malicious backend can cause the response headers to be truncated early, resulting in some headers being incorporated into the response body. If the later headers have any security purpose, they will not be interpreted by the client.', 'Affected Versions: Apache HTTP Server versions prior to 2.4.55']</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Customers are advised to update the latest Apache HTTP Server versions 2.4.55 or later. 
-For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update the latest Apache HTTP Server versions 2.4.55 or later. For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.</t>
+          <t>['Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.']</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2433,25 +2290,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2023-31122: Out-of-bounds Read vulnerability in mod_macro of Apache HTTP Server.This issue affects Apache HTTP Server 
-CVE-2023-45802: A client could send new requests and resets, keeping the connection busy and open and causing the memory footprint to keep on growing. On connection close, all resources were reclaimed, but the process might run out of memory before that. 
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.58 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2023-31122: Out-of-bounds Read vulnerability in mod_macro of Apache HTTP Server.This issue affects Apache HTTP Server CVE-2023-45802: A client could send new requests and resets, keeping the connection busy and open and causing the memory footprint to keep on growing. On connection close, all resources were reclaimed, but the process might run out of memory before that.', 'Affected Versions: Apache HTTP Server versions prior to 2.4.58']</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Customers are advised to update the latest Apache HTTP Server versions 2.4.58 or later. 
-For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update the latest Apache HTTP Server versions 2.4.58 or later. For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.</t>
+          <t>['Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.']</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2499,24 +2348,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2022-36760: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to.  
-Affected Versions: 
-Apache HTTP Server from 2.4 through 2.4.54  </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', "CVE-2022-36760: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to.", 'Affected Versions: Apache HTTP Server from 2.4 through 2.4.54']</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Customers are advised to update the latest Apache HTTP Server versions 2.4.55 or later. 
-For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update the latest Apache HTTP Server versions 2.4.55 or later. For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability allows an attacker to smuggle requests to the AJP server it forwards requests.</t>
+          <t>['Successful exploitation of this vulnerability allows an attacker to smuggle requests to the AJP server it forwards requests.']</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2564,24 +2406,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2022-26377: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to. 
-Affected Versions: 
-Apache HTTP Server versions 2.4 to 2.4.53  </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', "CVE-2022-26377: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to.", 'Affected Versions: Apache HTTP Server versions 2.4 to 2.4.53']</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allows an attacker to smuggle requests to the AJP server it forwards requests to.</t>
+          <t>['Successful exploitation of this vulnerability may allows an attacker to smuggle requests to the AJP server it forwards requests to.']</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2629,30 +2464,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-38472: SSRF in Apache HTTP Server on Windows allows to potentially leak NTML hashes to a malicious server via SSRF and malicious requests or content 
-CVE-2024-38473: Apache HTTP Server proxy encoding problem 
-CVE-2024-38474: Apache HTTP Server weakness with encoded question marks in backreferences 
-CVE-2024-38475: Apache HTTP Server weakness in mod_rewrite when first segment of substitution matches filesystem path. 
-CVE-2024-38476: Apache HTTP Server may use exploitable/malicious backend application output to run local handlers via internal redirect 
-CVE-2024-38477: Apache HTTP Server Crash resulting in Denial of Service in mod_proxy via a malicious request 
-CVE-2024-39573: Apache HTTP Server mod_rewrite proxy handler substitution 
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.60 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-38472: SSRF in Apache HTTP Server on Windows allows to potentially leak NTML hashes to a malicious server via SSRF and malicious requests or content CVE-2024-38473: Apache HTTP Server proxy encoding problem CVE-2024-38474: Apache HTTP Server weakness with encoded question marks in backreferences CVE-2024-38475: Apache HTTP Server weakness in mod_rewrite when first segment of substitution matches filesystem path. CVE-2024-38476: Apache HTTP Server may use exploitable/malicious backend application output to run local handlers via internal redirect CVE-2024-38477: Apache HTTP Server Crash resulting in Denial of Service in mod_proxy via a malicious request CVE-2024-39573: Apache HTTP Server mod_rewrite proxy handler substitution', 'Affected Versions: Apache HTTP Server versions prior to 2.4.60']</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information, visit here (https://httpd.apache.org/download.cgi). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/download.cgi)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information, visit here (https://httpd.apache.org/download.cgi). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/download.cgi)']</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise Confidentiality, Integrity, and Availability of the Data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise Confidentiality, Integrity, and Availability of the Data.']</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2700,24 +2522,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-47252:  Apache HTTP Server: mod_ssl error log variable escaping 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-47252: Apache HTTP Server: mod_ssl error log variable escaping', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2765,24 +2580,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29169:  Apache HTTP Server: mod_dav_lock indirect lock crash 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29169: Apache HTTP Server: mod_dav_lock indirect lock crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2830,24 +2638,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34059:  Apache HTTP Server: mod_proxy_ajp: Heap Over-Read and memory disclosure in  ajp_parse_data() 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34059: Apache HTTP Server: mod_proxy_ajp: Heap Over-Read and memory disclosure in ajp_parse_data()', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2895,38 +2696,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TCP provides stateful communications between hosts on a network. TCP sessions are established by a three-way handshake and use random 32-bit sequence and acknowledgement numbers to ensure the validity of traffic. A vulnerability was reported that may permit TCP sequence numbers to be more easily approximated by remote attackers. This issue affects products released by multiple vendors.  
-The cause of the vulnerability is that affected implementations will accept TCP sequence numbers within a certain range, known as the acknowledgement range, of the expected sequence number for a packet in the session. This is determined by the TCP window size, which is negotiated during the three-way handshake for the session. Larger TCP window sizes may be set to allow for more throughput, but the larger the TCP window size, the more probable it is to guess a TCP sequence number that falls within an acceptable range. It was initially thought that guessing an acceptable sequence number was relatively difficult for most implementations given random distribution, making this type of attack impractical. However, some implementations may make it easier to successfully approximate an acceptable TCP sequence number, making these attacks possible with a number of protocols and implementations.
-This is further compounded by the fact that some implementations may support the use of the TCP Window Scale Option, as described in RFC 1323, to extend the TCP window size to a maximum value of 1 billion.
-This vulnerability will permit a remote attacker to inject a SYN or RST packet into the session, causing it to be reset and effectively allowing for denial of service attacks. An attacker would exploit this issue by sending a packet to a receiving implementation with an approximated sequence number and a forged source IP address and TCP port.
-There are a few factors that may present viable target implementations, such as those which depend on long-lived TCP connections, those that have known or easily guessed IP address endpoints and those implementations with easily guessed TCP source ports. It has been noted that Border Gateway Protocol (BGP) is reported to be particularly vulnerable to this type of attack, due to the use of long-lived TCP sessions and the possibility that some implementations may use the TCP Window Scale Option. As a result, this issue is likely to affect a number of routing platforms.
-Another factor to consider is the relative difficulty of injecting packets into TCP sessions, as a number of receiving implementations will reassemble packets in order, dropping any duplicates. This may make some implementations more resistant to attacks than others.
-It should be noted that while a number of vendors have confirmed this issue in various products, investigations are ongoing and it is likely that many other vendors and products will turn out to be vulnerable as the issue is investigated further.</t>
+          <t>['TCP provides stateful communications between hosts on a network. TCP sessions are established by a three-way handshake and use random 32-bit sequence and acknowledgement numbers to ensure the validity of traffic. A vulnerability was reported that may permit TCP sequence numbers to be more easily approximated by remote attackers. This issue affects products released by multiple vendors.', 'The cause of the vulnerability is that affected implementations will accept TCP sequence numbers within a certain range, known as the acknowledgement range, of the expected sequence number for a packet in the session. This is determined by the TCP window size, which is negotiated during the three-way handshake for the session. Larger TCP window sizes may be set to allow for more throughput, but the larger the TCP window size, the more probable it is to guess a TCP sequence number that falls within an acceptable range. It was initially thought that guessing an acceptable sequence number was relatively difficult for most implementations given random distribution, making this type of attack impractical. However, some implementations may make it easier to successfully approximate an acceptable TCP sequence number, making these attacks possible with a number of protocols and implementations.', 'This is further compounded by the fact that some implementations may support the use of the TCP Window Scale Option, as described in RFC 1323, to extend the TCP window size to a maximum value of 1 billion.', 'This vulnerability will permit a remote attacker to inject a SYN or RST packet into the session, causing it to be reset and effectively allowing for denial of service attacks. An attacker would exploit this issue by sending a packet to a receiving implementation with an approximated sequence number and a forged source IP address and TCP port.', 'There are a few factors that may present viable target implementations, such as those which depend on long-lived TCP connections, those that have known or easily guessed IP address endpoints and those implementations with easily guessed TCP source ports. It has been noted that Border Gateway Protocol (BGP) is reported to be particularly vulnerable to this type of attack, due to the use of long-lived TCP sessions and the possibility that some implementations may use the TCP Window Scale Option. As a result, this issue is likely to affect a number of routing platforms.', 'Another factor to consider is the relative difficulty of injecting packets into TCP sessions, as a number of receiving implementations will reassemble packets in order, dropping any duplicates. This may make some implementations more resistant to attacks than others.', 'It should be noted that while a number of vendors have confirmed this issue in various products, investigations are ongoing and it is likely that many other vendors and products will turn out to be vulnerable as the issue is investigated further.']</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Please first check the results section below for the port number on which this vulnerability was detected. If that port number is known to be used for port-forwarding, then it is the backend host that is really vulnerable.
-Various implementations and products including Check Point, Cisco, Cray Inc, Hitachi, Internet Initiative Japan, Inc (IIJ), Juniper Networks, NEC and Yamaha are currently undergoing review. Contact the vendors to obtain more information about affected products and fixes. NISCC Advisory 236929 - Vulnerability Issues in TCP (http://packetstormsecurity.org/0404-advisories/246929.html) details the vendor patch status as of the time of the advisory, and identifies resolutions and workarounds.
-Refer to US-CERT Vulnerability Note VU415294 (http://www.kb.cert.org/vuls/id/415294) and OSVDB Article 4030 (http://osvdb.org/4030) to obtain a list of vendors affected by this issue and a note on resolutions (if any) provided by the vendor.
-For Microsoft: Refer to MS05-019 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2005/ms05-019) and MS06-064 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2006/ms06-064) for further details.
-For SGI IRIX: Refer to SGI Security Advisory 20040905-01-P (ftp://patches.sgi.com/support/free/security/advisories/20040905-01-P.asc)
-For SCO UnixWare 7.1.3 and 7.1.1: Refer to SCO Security Advisory SCOSA-2005.14 (ftp://ftp.sco.com/pub/updates/UnixWare/SCOSA-2005.14/SCOSA-2005.14.txt)
-For Solaris (Sun Microsystems): The vendor has acknowledged the vulnerability; however a patch is not available. Refer to Sun Microsystems, Inc. Information for VU415294 (http://www.kb.cert.org/vuls/id/JARL-5YGQAJ) to obtain additional details. Also, refer to TA04-111A (http://www.us-cert.gov/cas/techalerts/TA04-111A.html) for detailed mitigating strategies against these attacks.
-For NetBSD: Refer to NetBSD-SA2004-006 (ftp://ftp.netbsd.org/pub/NetBSD/security/advisories/NetBSD-SA2004-006.txt.asc)
-For Cisco: Refer to cisco-sa-20040420-tcp-ios.shtml (http://www.cisco.com/warp/public/707/cisco-sa-20040420-tcp-ios.shtml).
-For IBM : Refer to IBM-tcp-sequence-number-cve-2004-0230 (https://www.ibm.com/support/pages/tcp-sequence-number-approximation-based-denial-service-cve-2004-0230).
-For Red Hat Linux: There is no fix available : Refer to  (https://access.redhat.com/security/cve/cve-2004-0230).
-Workaround: The following BGP-specific workaround information has been provided.
-For BGP implementations that support it, the TCP MD5 Signature Option should be enabled. Passwords that the MD5 checksum is applied to should be set to strong values and changed on a regular basis.
-Secure BGP configuration instructions have been provided for Cisco and Juniper at these locations:
-Secure Cisco IOS BGP Template (http://www.cymru.com/Documents/secure-bgp-template.html)
-JUNOS Secure BGP Template (http://www.cymru.com/gillsr/documents/junos-bgp-template.pdf)</t>
+          <t>['Please first check the results section below for the port number on which this vulnerability was detected. If that port number is known to be used for port-forwarding, then it is the backend host that is really vulnerable.', 'Various implementations and products including Check Point, Cisco, Cray Inc, Hitachi, Internet Initiative Japan, Inc (IIJ), Juniper Networks, NEC and Yamaha are currently undergoing review. Contact the vendors to obtain more information about affected products and fixes. NISCC Advisory 236929 - Vulnerability Issues in TCP (http://packetstormsecurity.org/0404-advisories/246929.html) details the vendor patch status as of the time of the advisory, and identifies resolutions and workarounds.', 'Refer to US-CERT Vulnerability Note VU415294 (http://www.kb.cert.org/vuls/id/415294) and OSVDB Article 4030 (http://osvdb.org/4030) to obtain a list of vendors affected by this issue and a note on resolutions (if any) provided by the vendor.', 'For Microsoft: Refer to MS05-019 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2005/ms05-019) and MS06-064 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2006/ms06-064) for further details.', 'For SGI IRIX: Refer to SGI Security Advisory 20040905-01-P (ftp://patches.sgi.com/support/free/security/advisories/20040905-01-P.asc)', 'For SCO UnixWare 7.1.3 and 7.1.1: Refer to SCO Security Advisory SCOSA-2005.14 (ftp://ftp.sco.com/pub/updates/UnixWare/SCOSA-2005.14/SCOSA-2005.14.txt)', 'For Solaris (Sun Microsystems): The vendor has acknowledged the vulnerability; however a patch is not available. Refer to Sun Microsystems, Inc. Information for VU415294 (http://www.kb.cert.org/vuls/id/JARL-5YGQAJ) to obtain additional details. Also, refer to TA04-111A (http://www.us-cert.gov/cas/techalerts/TA04-111A.html) for detailed mitigating strategies against these attacks.', 'For NetBSD: Refer to NetBSD-SA2004-006 (ftp://ftp.netbsd.org/pub/NetBSD/security/advisories/NetBSD-SA2004-006.txt.asc)', 'For Cisco: Refer to cisco-sa-20040420-tcp-ios.shtml (http://www.cisco.com/warp/public/707/cisco-sa-20040420-tcp-ios.shtml).', 'For IBM : Refer to IBM-tcp-sequence-number-cve-2004-0230 (https://www.ibm.com/support/pages/tcp-sequence-number-approximation-based-denial-service-cve-2004-0230).', 'For Red Hat Linux: There is no fix available : Refer to (https://access.redhat.com/security/cve/cve-2004-0230).', 'Workaround: The following BGP-specific workaround information has been provided.', 'For BGP implementations that support it, the TCP MD5 Signature Option should be enabled. Passwords that the MD5 checksum is applied to should be set to strong values and changed on a regular basis.', 'Secure BGP configuration instructions have been provided for Cisco and Juniper at these locations:', 'Secure Cisco IOS BGP Template (http://www.cymru.com/Documents/secure-bgp-template.html)', 'JUNOS Secure BGP Template (http://www.cymru.com/gillsr/documents/junos-bgp-template.pdf)']</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Successful exploitation of this issue could lead to denial of service attacks on the TCP based services of target hosts.</t>
+          <t>['Successful exploitation of this issue could lead to denial of service attacks on the TCP based services of target hosts.']</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2969,15 +2749,12 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to Apache httpd 2.2.33, 2.4.26 (https://httpd.apache.org/download.cgi) or later versions to remediate this vulnerability.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache httpd 2.2.33, 2.4.26 or later (https://httpd.apache.org/download.cgi)</t>
+          <t>['Customers are advised to upgrade to Apache httpd 2.2.33, 2.4.26 (https://httpd.apache.org/download.cgi) or later versions to remediate this vulnerability. Patch: Following are links for downloading patches to fix the vulnerabilities: Apache httpd 2.2.33, 2.4.26 or later (https://httpd.apache.org/download.cgi)']</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Successful exploitation allows remote attackers to bypass authentication and access sensitive information.</t>
+          <t>['Successful exploitation allows remote attackers to bypass authentication and access sensitive information.']</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3019,25 +2796,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application.
- CVE-2020-1934: In Apache HTTP Server, mod_proxy_ftp may use uninitialized memory when proxying to a malicious FTP server. 
- CVE-2020-1927: In Apache HTTP Server, redirects configured with mod_rewrite that were intended to be self-referential might be fooled by encoded newlines and redirect instead to an an unexpected URL within the request URL. 
- Affected Versions: 
-Apache httpd 2.4.0 to 2.4.41 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2020-1934: In Apache HTTP Server, mod_proxy_ftp may use uninitialized memory when proxying to a malicious FTP server. CVE-2020-1927: In Apache HTTP Server, redirects configured with mod_rewrite that were intended to be self-referential might be fooled by encoded newlines and redirect instead to an an unexpected URL within the request URL.', 'Affected Versions: Apache httpd 2.4.0 to 2.4.41']</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Customers are advised to update Apache httpd to 2.4.42 or later. 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html).
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache httpd 2.4.42 or later 2.4. (https://httpd.apache.org/download.cgi)</t>
+          <t>['Customers are advised to update Apache httpd to 2.4.42 or later. For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache httpd 2.4.42 or later 2.4. (https://httpd.apache.org/download.cgi)']</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>This vulnerability could be exploited to gain partial access to sensitive information. Malicious users could also use this vulnerability to change partial contents or configuration on the system</t>
+          <t>['This vulnerability could be exploited to gain partial access to sensitive information. Malicious users could also use this vulnerability to change partial contents or configuration on the system']</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3083,9 +2852,21 @@
           <t>PHP Multiple Denial of Service Vulnerabilities</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>['PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. Multiple vulnerabilities have been discovered in PHP :', 'Affected Version: PHP 5.x through 7.1.24']</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>['Vendor has Released the patch to addressed the vulnerability. Please update to PHP 7.1.25 (https://www.php.net/releases/7_1_25.php) Patch: Following are links for downloading patches to fix the vulnerabilities: Version 7.1.25 (https://www.php.net/releases/7_1_25.php)']</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>['ext/standard/var_unserializer.c in PHP 5.x through 7.1.24 allows attackers to cause a denial of service (application crash) via an unserialize call for the com, dotnet, or variant class.']</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>['CVE-2018-19396', 'CVE-2018-19395']</t>
@@ -3131,22 +2912,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
-Affected Versions: 
-PHP versions before 7.2.16 </t>
+          <t>['PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML.', 'Affected Versions: PHP versions before 7.2.16']</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php)
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  php downloads (https://www.php.net/downloads)</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) Patch: Following are links for downloading patches to fix the vulnerabilities: php downloads (https://www.php.net/downloads)']</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Successful exploitation allows a remote unauthenticated attacker to disclose local files on hosts.</t>
+          <t>['Successful exploitation allows a remote unauthenticated attacker to disclose local files on hosts.']</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3194,25 +2970,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
-PHP is affected by multiple vulnerabilities. 
-Affected Versions: 
-PHP versions prior to 7.4.24 
-PHP versions 7.3.x prior to 7.3.31 
-PHP versions 8.0.x prior to 8.0.11 </t>
+          <t>['PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML.', 'PHP is affected by multiple vulnerabilities.', 'Affected Versions: PHP versions prior to 7.4.24 PHP versions 7.3.x prior to 7.3.31 PHP versions 8.0.x prior to 8.0.11']</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php)
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PHP Changelog Version 7.4.24 (https://www.php.net/ChangeLog-7.phpPHP_7_4)  PHP Changelog Version 7.3.31 (https://www.php.net/ChangeLog-7.phpPHP_7_3)  PHP Changelog Version 8.0.11 (https://www.php.net/ChangeLog-8.php)</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) Patch: Following are links for downloading patches to fix the vulnerabilities: PHP Changelog Version 7.4.24 (https://www.php.net/ChangeLog-7.phpPHP_7_4) PHP Changelog Version 7.3.31 (https://www.php.net/ChangeLog-7.phpPHP_7_3) PHP Changelog Version 8.0.11 (https://www.php.net/ChangeLog-8.php)']</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an attacker to impact Confidentiality and Integrity.</t>
+          <t>['Successful exploitation of this vulnerability may allow an attacker to impact Confidentiality and Integrity.']</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3260,28 +3028,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
-Affected versions of PHP has multiple vulnerabilities: 
-CVE-2022-31628 : The vulnerability exists due to infinite loop within the phar uncompressor code when processing "quines" gzip files. A remote attacker can pass a specially crafted archive to the application, consume all available system resources and cause denial of service conditions. 
-CVE-2022-31629: The vulnerability exists due to the way PHP handles HTTP variable names. A remote attacker can set a standard insecure cookie in the victim's browser which is treated as a '__Host-' or '__Secure-' cookie by PHP applications. 
-Affected Versions: 
-PHP versions before 7.4.31 
-PHP versions 8.0.0 prior to 8.0.24 
-PHP versions 8.1.0 prior to 8.1.11 </t>
+          <t>['PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications.', 'Affected versions of PHP has multiple vulnerabilities: CVE-2022-31628 : The vulnerability exists due to infinite loop within the phar uncompressor code when processing "quines" gzip files. A remote attacker can pass a specially crafted archive to the application, consume all available system resources and cause denial of service conditions.', "CVE-2022-31629: The vulnerability exists due to the way PHP handles HTTP variable names. A remote attacker can set a standard insecure cookie in the victim's browser which is treated as a '__Host-' or '__Secure-' cookie by PHP applications.", 'Affected Versions: PHP versions before 7.4.31 PHP versions 8.0.0 prior to 8.0.24 PHP versions 8.1.0 prior to 8.1.11']</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) 
-For more information please refer to Sec Bug 81726 (https://bugs.php.net/bug.php?id=81726) and Sec Bug 81727 (https://bugs.php.net/bug.php?id=81727) . 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  81727 (https://bugs.php.net/bug.php?id=81727)  81726 (https://bugs.php.net/bug.php?id=81726)</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) For more information please refer to Sec Bug 81726 (https://bugs.php.net/bug.php?id=81726) and Sec Bug 81727 (https://bugs.php.net/bug.php?id=81727) . Patch: Following are links for downloading patches to fix the vulnerabilities: 81727 (https://bugs.php.net/bug.php?id=81727) 81726 (https://bugs.php.net/bug.php?id=81726)']</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability allows a remote attacker to perform a denial of service (DoS) attack or bypass implemented security restrictions.</t>
+          <t>['Successful exploitation of this vulnerability allows a remote attacker to perform a denial of service (DoS) attack or bypass implemented security restrictions.']</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3329,25 +3086,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2023-38709: Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. 
-CVE-2024-24795: HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack.  
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.59 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2023-38709: Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. CVE-2024-24795: HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack.', 'Affected Versions: Apache HTTP Server versions prior to 2.4.59']</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Customers are advised to update the latest Apache versions respectively. 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update the latest Apache versions respectively. For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.</t>
+          <t>['Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.']</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3395,24 +3144,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-49812:  Apache HTTP Server: mod_ssl TLS upgrade attack 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-49812: Apache HTTP Server: mod_ssl TLS upgrade attack', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3460,20 +3202,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Affected Versions: 
-Apache httpd 2.4.17 through 2.4.63 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-53020: Apache HTTP Server: HTTP/2 DoS by Memory Increase', 'Affected Versions: Apache httpd 2.4.17 through 2.4.63']</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>['CVE-2025-53020']</t>
@@ -3519,24 +3260,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-43394:  Apache HTTP Server: SSRF on Windows due to UNC paths 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-43394: Apache HTTP Server: SSRF on Windows due to UNC paths', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3584,24 +3318,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-42516:  Apache HTTP Server: HTTP response splitting 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-42516: Apache HTTP Server: HTTP response splitting', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3649,24 +3376,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-59775:  Apache HTTP Server: NTLM Leakage on Windows through UNC SSRF 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-59775: Apache HTTP Server: NTLM Leakage on Windows through UNC SSRF', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3714,24 +3434,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-66200:  Apache HTTP Server: mod_userdir+suexec bypass via AllowOverride FileInfo 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-66200: Apache HTTP Server: mod_userdir+suexec bypass via AllowOverride FileInfo', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3779,24 +3492,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-58098:  Apache HTTP Server: Server Side Includes adds query string to exec cmd=... 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-58098: Apache HTTP Server: Server Side Includes adds query string to exec cmd=...', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3844,24 +3550,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33006:  Apache HTTP Server: mod_auth_digest timing attack 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33006: Apache HTTP Server: mod_auth_digest timing attack', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3909,24 +3608,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-24072:  Apache HTTP Server: mod_rewrite elevation of privileges via ap_expr 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-24072: Apache HTTP Server: mod_rewrite elevation of privileges via ap_expr', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3974,24 +3666,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44119:  escalation of privilege through expressions in .htaccess in multiple modules 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44119: escalation of privilege through expressions in .htaccess in multiple modules', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4039,24 +3724,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44186:  Loop in `proxy_ftp_handler` in mod_proxy_ftp 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44186: Loop in `proxy_ftp_handler` in mod_proxy_ftp', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4104,24 +3782,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-49975:  mod_http2 denial of service 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-49975: mod_http2 denial of service', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4169,24 +3840,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34355:  mod_proxy_html buffer overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34355: mod_proxy_html buffer overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4234,24 +3898,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-43951:  OOB Read in `merge_response_headers` can cause crash 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-43951: OOB Read in `merge_response_headers` can cause crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4299,24 +3956,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-42535:  mod_dav_fs protected directory access 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-42535: mod_dav_fs protected directory access', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4364,23 +4014,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-A crafted method sent through HTTP/2 will bypass validation and be forwarded by mod_proxy, which can lead to request splitting or cache poisoning. 
-Affected Versions: 
-Apache HTTP Server 2.4.17 to 2.4.48. </t>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'A crafted method sent through HTTP/2 will bypass validation and be forwarded by mod_proxy, which can lead to request splitting or cache poisoning.', 'Affected Versions: Apache HTTP Server 2.4.17 to 2.4.48.']</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  NA (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: NA (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow request splitting or cache poisoning.</t>
+          <t>['Successful exploitation of this vulnerability may allow request splitting or cache poisoning.']</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4428,24 +4072,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-43204:  Apache HTTP Server: SSRF with mod_headers setting Content-Type header 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-43204: Apache HTTP Server: SSRF with mod_headers setting Content-Type header', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4493,24 +4130,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-65082:  Apache HTTP Server: CGI environment variable override 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-65082: Apache HTTP Server: CGI environment variable override', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4558,24 +4188,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34032:  Apache HTTP Server: mod_proxy_ajp: Heap Buffer Over-Read Due to Missing Null-Termination Check (ajp_msg_get_string) 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34032: Apache HTTP Server: mod_proxy_ajp: Heap Buffer Over-Read Due to Missing Null-Termination Check (ajp_msg_get_string)', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4623,24 +4246,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33007:  Apache HTTP Server: mod_authn_socache crash 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33007: Apache HTTP Server: mod_authn_socache crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4688,24 +4304,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33857:  Apache HTTP Server: Off-by-one OOB reads in AJP getter functions 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33857: Apache HTTP Server: Off-by-one OOB reads in AJP getter functions', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4753,24 +4362,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33523:  Apache HTTP Server: multiple modules: HTTP response splitting forwarding malicious status line 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33523: Apache HTTP Server: multiple modules: HTTP response splitting forwarding malicious status line', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4818,24 +4420,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-28780:  Apache HTTP Server: buffer overflow in mod_proxy_ajp via  ajp_msg_check_header() 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-28780: Apache HTTP Server: buffer overflow in mod_proxy_ajp via ajp_msg_check_header()', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4883,24 +4478,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29170:  mod_proxy_ftp XSS 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29170: mod_proxy_ftp XSS', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4948,24 +4536,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29167:  mod_ldap per-dir use-after-free 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29167: mod_ldap per-dir use-after-free', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5013,24 +4594,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-42536:  mod_xml2enc heap overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-42536: mod_xml2enc heap overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5078,24 +4652,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44185:  Stack Buffer Over-Read in mod_ssl OCSP `send_request` 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44185: Stack Buffer Over-Read in mod_ssl OCSP `send_request`', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5143,24 +4710,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34356:  ProxyPassReverseCookieMap buffer overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34356: ProxyPassReverseCookieMap buffer overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5208,24 +4768,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44631:  Heap Underflow in `ap_regname` via Signed Char Overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44631: Heap Underflow in `ap_regname` via Signed Char Overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5271,7 +4824,11 @@
           <t>PHP Server Detected</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>['PHP is a general purpose scripting language that is especially suited for Web development and can be embedded in HTML.']</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
@@ -5307,7 +4864,11 @@
           <t>Web Server HTTP Protocol Versions</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>['This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.']</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
@@ -5351,7 +4912,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -5391,8 +4952,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -5432,7 +4992,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -5470,7 +5030,11 @@
           <t>Apache HTTP Server Detected</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>['The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards.']</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
@@ -5508,7 +5072,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -5548,18 +5112,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -5597,14 +5160,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -5644,7 +5200,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -5684,8 +5240,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -5725,7 +5280,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server.</t>
+          <t>['The Result section displays the default Web page for the Web server.']</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -5771,7 +5326,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server following HTTP redirections.</t>
+          <t>['The Result section displays the default Web page for the Web server following HTTP redirections.']</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -5817,9 +5372,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request.  
-QID Detection Logic: 
-This QID returns the HTTP response method and header information returned by a web server.</t>
+          <t>["This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request. QID Detection Logic: This QID returns the HTTP response method and header information returned by a web server."]</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -5863,7 +5416,11 @@
           <t>Web Server Version</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>['A web server is server software, or hardware dedicated to running this software, that can satisfy client requests on the World Wide Web.']</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
@@ -5907,14 +5464,13 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.
-The target Web server was found to support this functionality of the HTTP 1.1 protocol.</t>
+          <t>['Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.', 'The target Web server was found to support this functionality of the HTTP 1.1 protocol.']</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.</t>
+          <t>['Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.']</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -5958,7 +5514,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Based largely on the HTTP reply code, the following directories are most likely present on the host.</t>
+          <t>['Based largely on the HTTP reply code, the following directories are most likely present on the host.']</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -6004,25 +5560,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
-Affected Versions: 
-PHP versions from 8.1.0 prior to 8.1.32 
-PHP versions from 8.2.0 prior to 8.2.28 
-PHP versions from 8.3.0 prior to 8.3.19 
-PHP versions from 8.4.0 prior to 8.4.5 </t>
+          <t>['PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications.', 'Affected Versions: PHP versions from 8.1.0 prior to 8.1.32 PHP versions from 8.2.0 prior to 8.2.28 PHP versions from 8.3.0 prior to 8.3.19 PHP versions from 8.4.0 prior to 8.4.5']</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP Downloads (https://www.php.net/downloads) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PHP 8.4.5 (https://www.php.net/ChangeLog-8.php8.4.5)  PHP 8.3.19 (https://www.php.net/ChangeLog-8.php8.3.19)  PHP 8.2.28 (https://www.php.net/ChangeLog-8.php8.2.28)  PHP 8.1.32 (https://www.php.net/ChangeLog-8.php8.1.32)</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP Downloads (https://www.php.net/downloads) Patch: Following are links for downloading patches to fix the vulnerabilities: PHP 8.4.5 (https://www.php.net/ChangeLog-8.php8.4.5) PHP 8.3.19 (https://www.php.net/ChangeLog-8.php8.3.19) PHP 8.2.28 (https://www.php.net/ChangeLog-8.php8.2.28) PHP 8.1.32 (https://www.php.net/ChangeLog-8.php8.1.32)']</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability can lead to the creation of malformed and allowing attackers to inject malicious code.</t>
+          <t>['Successful exploitation of this vulnerability can lead to the creation of malformed and allowing attackers to inject malicious code.']</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6070,25 +5618,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
-Affected PHP versions 
-from 8.4.0 before 8.4.10 
-from 8.3.0 before 8.3.23 
-from 8.2.0 before 8.2.29 
-from 8.1.0 before 8.1.33 </t>
+          <t>['PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications.', 'Affected PHP versions from 8.4.0 before 8.4.10 from 8.3.0 before 8.3.23 from 8.2.0 before 8.2.29 from 8.1.0 before 8.1.33']</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP on Downloads page (https://www.php.net/downloads) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PHP 8.1.33 (https://www.php.net/ChangeLog-8.php8.1.33)  PHP 8.2.29 (https://www.php.net/ChangeLog-8.php8.2.29)  PHP 8.3.23 (https://www.php.net/ChangeLog-8.php8.3.23)  PHP 8.4.10 (https://www.php.net/ChangeLog-8.php8.4.10)</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP on Downloads page (https://www.php.net/downloads) Patch: Following are links for downloading patches to fix the vulnerabilities: PHP 8.1.33 (https://www.php.net/ChangeLog-8.php8.1.33) PHP 8.2.29 (https://www.php.net/ChangeLog-8.php8.2.29) PHP 8.3.23 (https://www.php.net/ChangeLog-8.php8.3.23) PHP 8.4.10 (https://www.php.net/ChangeLog-8.php8.4.10)']</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability could lead to a security breach or affect integrity, availability and confidentiality.</t>
+          <t>['Successful exploitation of this vulnerability could lead to a security breach or affect integrity, availability and confidentiality.']</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6136,24 +5676,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-47252:  Apache HTTP Server: mod_ssl error log variable escaping 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-47252: Apache HTTP Server: mod_ssl error log variable escaping', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6201,23 +5734,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29169: Apache HTTP Server: mod_dav_lock indirect lock crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6265,23 +5792,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34059: Apache HTTP Server: mod_proxy_ajp: Heap Over-Read and memory disclosure in ajp_parse_data()', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6329,38 +5850,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TCP provides stateful communications between hosts on a network. TCP sessions are established by a three-way handshake and use random 32-bit sequence and acknowledgement numbers to ensure the validity of traffic. A vulnerability was reported that may permit TCP sequence numbers to be more easily approximated by remote attackers. This issue affects products released by multiple vendors.  
-The cause of the vulnerability is that affected implementations will accept TCP sequence numbers within a certain range, known as the acknowledgement range, of the expected sequence number for a packet in the session. This is determined by the TCP window size, which is negotiated during the three-way handshake for the session. Larger TCP window sizes may be set to allow for more throughput, but the larger the TCP window size, the more probable it is to guess a TCP sequence number that falls within an acceptable range. It was initially thought that guessing an acceptable sequence number was relatively difficult for most implementations given random distribution, making this type of attack impractical. However, some implementations may make it easier to successfully approximate an acceptable TCP sequence number, making these attacks possible with a number of protocols and implementations.
-This is further compounded by the fact that some implementations may support the use of the TCP Window Scale Option, as described in RFC 1323, to extend the TCP window size to a maximum value of 1 billion.
-This vulnerability will permit a remote attacker to inject a SYN or RST packet into the session, causing it to be reset and effectively allowing for denial of service attacks. An attacker would exploit this issue by sending a packet to a receiving implementation with an approximated sequence number and a forged source IP address and TCP port.
-There are a few factors that may present viable target implementations, such as those which depend on long-lived TCP connections, those that have known or easily guessed IP address endpoints and those implementations with easily guessed TCP source ports. It has been noted that Border Gateway Protocol (BGP) is reported to be particularly vulnerable to this type of attack, due to the use of long-lived TCP sessions and the possibility that some implementations may use the TCP Window Scale Option. As a result, this issue is likely to affect a number of routing platforms.
-Another factor to consider is the relative difficulty of injecting packets into TCP sessions, as a number of receiving implementations will reassemble packets in order, dropping any duplicates. This may make some implementations more resistant to attacks than others.
-It should be noted that while a number of vendors have confirmed this issue in various products, investigations are ongoing and it is likely that many other vendors and products will turn out to be vulnerable as the issue is investigated further.</t>
+          <t>['TCP provides stateful communications between hosts on a network. TCP sessions are established by a three-way handshake and use random 32-bit sequence and acknowledgement numbers to ensure the validity of traffic. A vulnerability was reported that may permit TCP sequence numbers to be more easily approximated by remote attackers. This issue affects products released by multiple vendors.', 'The cause of the vulnerability is that affected implementations will accept TCP sequence numbers within a certain range, known as the acknowledgement range, of the expected sequence number for a packet in the session. This is determined by the TCP window size, which is negotiated during the three-way handshake for the session. Larger TCP window sizes may be set to allow for more throughput, but the larger the TCP window size, the more probable it is to guess a TCP sequence number that falls within an acceptable range. It was initially thought that guessing an acceptable sequence number was relatively difficult for most implementations given random distribution, making this type of attack impractical. However, some implementations may make it easier to successfully approximate an acceptable TCP sequence number, making these attacks possible with a number of protocols and implementations.', 'This is further compounded by the fact that some implementations may support the use of the TCP Window Scale Option, as described in RFC 1323, to extend the TCP window size to a maximum value of 1 billion.', 'This vulnerability will permit a remote attacker to inject a SYN or RST packet into the session, causing it to be reset and effectively allowing for denial of service attacks. An attacker would exploit this issue by sending a packet to a receiving implementation with an approximated sequence number and a forged source IP address and TCP port.', 'There are a few factors that may present viable target implementations, such as those which depend on long-lived TCP connections, those that have known or easily guessed IP address endpoints and those implementations with easily guessed TCP source ports. It has been noted that Border Gateway Protocol (BGP) is reported to be particularly vulnerable to this type of attack, due to the use of long-lived TCP sessions and the possibility that some implementations may use the TCP Window Scale Option. As a result, this issue is likely to affect a number of routing platforms.', 'Another factor to consider is the relative difficulty of injecting packets into TCP sessions, as a number of receiving implementations will reassemble packets in order, dropping any duplicates. This may make some implementations more resistant to attacks than others.', 'It should be noted that while a number of vendors have confirmed this issue in various products, investigations are ongoing and it is likely that many other vendors and products will turn out to be vulnerable as the issue is investigated further.']</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Please first check the results section below for the port number on which this vulnerability was detected. If that port number is known to be used for port-forwarding, then it is the backend host that is really vulnerable.
-Various implementations and products including Check Point, Cisco, Cray Inc, Hitachi, Internet Initiative Japan, Inc (IIJ), Juniper Networks, NEC and Yamaha are currently undergoing review. Contact the vendors to obtain more information about affected products and fixes. NISCC Advisory 236929 - Vulnerability Issues in TCP (http://packetstormsecurity.org/0404-advisories/246929.html) details the vendor patch status as of the time of the advisory, and identifies resolutions and workarounds.
-Refer to US-CERT Vulnerability Note VU415294 (http://www.kb.cert.org/vuls/id/415294) and OSVDB Article 4030 (http://osvdb.org/4030) to obtain a list of vendors affected by this issue and a note on resolutions (if any) provided by the vendor.
-For Microsoft: Refer to MS05-019 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2005/ms05-019) and MS06-064 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2006/ms06-064) for further details.
-For SGI IRIX: Refer to SGI Security Advisory 20040905-01-P (ftp://patches.sgi.com/support/free/security/advisories/20040905-01-P.asc)
-For SCO UnixWare 7.1.3 and 7.1.1: Refer to SCO Security Advisory SCOSA-2005.14 (ftp://ftp.sco.com/pub/updates/UnixWare/SCOSA-2005.14/SCOSA-2005.14.txt)
-For Solaris (Sun Microsystems): The vendor has acknowledged the vulnerability; however a patch is not available. Refer to Sun Microsystems, Inc. Information for VU415294 (http://www.kb.cert.org/vuls/id/JARL-5YGQAJ) to obtain additional details. Also, refer to TA04-111A (http://www.us-cert.gov/cas/techalerts/TA04-111A.html) for detailed mitigating strategies against these attacks.
-For NetBSD: Refer to NetBSD-SA2004-006 (ftp://ftp.netbsd.org/pub/NetBSD/security/advisories/NetBSD-SA2004-006.txt.asc)
-For Cisco: Refer to cisco-sa-20040420-tcp-ios.shtml (http://www.cisco.com/warp/public/707/cisco-sa-20040420-tcp-ios.shtml).
-For IBM : Refer to IBM-tcp-sequence-number-cve-2004-0230 (https://www.ibm.com/support/pages/tcp-sequence-number-approximation-based-denial-service-cve-2004-0230).
-For Red Hat Linux: There is no fix available : Refer to  (https://access.redhat.com/security/cve/cve-2004-0230).
-Workaround: The following BGP-specific workaround information has been provided.
-For BGP implementations that support it, the TCP MD5 Signature Option should be enabled. Passwords that the MD5 checksum is applied to should be set to strong values and changed on a regular basis.
-Secure BGP configuration instructions have been provided for Cisco and Juniper at these locations:
-Secure Cisco IOS BGP Template (http://www.cymru.com/Documents/secure-bgp-template.html)
-JUNOS Secure BGP Template (http://www.cymru.com/gillsr/documents/junos-bgp-template.pdf)</t>
+          <t>['Please first check the results section below for the port number on which this vulnerability was detected. If that port number is known to be used for port-forwarding, then it is the backend host that is really vulnerable.', 'Various implementations and products including Check Point, Cisco, Cray Inc, Hitachi, Internet Initiative Japan, Inc (IIJ), Juniper Networks, NEC and Yamaha are currently undergoing review. Contact the vendors to obtain more information about affected products and fixes. NISCC Advisory 236929 - Vulnerability Issues in TCP (http://packetstormsecurity.org/0404-advisories/246929.html) details the vendor patch status as of the time of the advisory, and identifies resolutions and workarounds.', 'Refer to US-CERT Vulnerability Note VU415294 (http://www.kb.cert.org/vuls/id/415294) and OSVDB Article 4030 (http://osvdb.org/4030) to obtain a list of vendors affected by this issue and a note on resolutions (if any) provided by the vendor.', 'For Microsoft: Refer to MS05-019 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2005/ms05-019) and MS06-064 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2006/ms06-064) for further details.', 'For SGI IRIX: Refer to SGI Security Advisory 20040905-01-P (ftp://patches.sgi.com/support/free/security/advisories/20040905-01-P.asc)', 'For SCO UnixWare 7.1.3 and 7.1.1: Refer to SCO Security Advisory SCOSA-2005.14 (ftp://ftp.sco.com/pub/updates/UnixWare/SCOSA-2005.14/SCOSA-2005.14.txt)', 'For Solaris (Sun Microsystems): The vendor has acknowledged the vulnerability; however a patch is not available. Refer to Sun Microsystems, Inc. Information for VU415294 (http://www.kb.cert.org/vuls/id/JARL-5YGQAJ) to obtain additional details. Also, refer to TA04-111A (http://www.us-cert.gov/cas/techalerts/TA04-111A.html) for detailed mitigating strategies against these attacks.', 'For NetBSD: Refer to NetBSD-SA2004-006 (ftp://ftp.netbsd.org/pub/NetBSD/security/advisories/NetBSD-SA2004-006.txt.asc)', 'For Cisco: Refer to cisco-sa-20040420-tcp-ios.shtml (http://www.cisco.com/warp/public/707/cisco-sa-20040420-tcp-ios.shtml).', 'For IBM : Refer to IBM-tcp-sequence-number-cve-2004-0230 (https://www.ibm.com/support/pages/tcp-sequence-number-approximation-based-denial-service-cve-2004-0230).', 'For Red Hat Linux: There is no fix available : Refer to (https://access.redhat.com/security/cve/cve-2004-0230).', 'Workaround: The following BGP-specific workaround information has been provided.', 'For BGP implementations that support it, the TCP MD5 Signature Option should be enabled. Passwords that the MD5 checksum is applied to should be set to strong values and changed on a regular basis.', 'Secure BGP configuration instructions have been provided for Cisco and Juniper at these locations:', 'Secure Cisco IOS BGP Template (http://www.cymru.com/Documents/secure-bgp-template.html)', 'JUNOS Secure BGP Template (http://www.cymru.com/gillsr/documents/junos-bgp-template.pdf)']</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Successful exploitation of this issue could lead to denial of service attacks on the TCP based services of target hosts.</t>
+          <t>['Successful exploitation of this issue could lead to denial of service attacks on the TCP based services of target hosts.']</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6402,22 +5902,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JQuery is prone to a cross-site-scripting vulnerability because it fails to sufficiently sanitize user-supplied input. 
-Affected Versions:  
-jQuery versions greater than or equal to 1.2 and before 3.5.0.</t>
+          <t>['JQuery is prone to a cross-site-scripting vulnerability because it fails to sufficiently sanitize user-supplied input.', 'Affected Versions: jQuery versions greater than or equal to 1.2 and before 3.5.0.']</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Vendor has advised to Upgrade jquery to version 3.5.0
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  jQuery (https://jquery.com/download/)</t>
+          <t>['Vendor has advised to Upgrade jquery to version 3.5.0 Patch: Following are links for downloading patches to fix the vulnerabilities: jQuery (https://jquery.com/download/)']</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>An attacker may leverage this issue to execute arbitrary script code in the browser of an unsuspecting user in the context of the affected site.</t>
+          <t>['An attacker may leverage this issue to execute arbitrary script code in the browser of an unsuspecting user in the context of the affected site.']</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6465,22 +5960,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JQuery is prone to a cross-site-scripting vulnerability because it fails to sufficiently sanitize user-supplied input. 
-Affected Versions:  
-jQuery versions greater than or equal to 1.0.3 and before 3.5.0.</t>
+          <t>['JQuery is prone to a cross-site-scripting vulnerability because it fails to sufficiently sanitize user-supplied input.', 'Affected Versions: jQuery versions greater than or equal to 1.0.3 and before 3.5.0.']</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Vendor has advised to Upgrade jquery to version 3.5.0
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  jQuery (https://jquery.com/download/)</t>
+          <t>['Vendor has advised to Upgrade jquery to version 3.5.0 Patch: Following are links for downloading patches to fix the vulnerabilities: jQuery (https://jquery.com/download/)']</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>An attacker may leverage this issue to execute arbitrary script code in the browser of an unsuspecting user in the context of the affected site.</t>
+          <t>['An attacker may leverage this issue to execute arbitrary script code in the browser of an unsuspecting user in the context of the affected site.']</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6528,27 +6018,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>The Apache HTTP Server, commonly referred to as Apache is a freely available Web server.
-Apache is vulnerable to a denial of service due to holding a connection open for partial HTTP requests. 
-Apache Versions 1.x and 2.x are vulnerable.</t>
+          <t>['The Apache HTTP Server, commonly referred to as Apache is a freely available Web server.', 'Apache is vulnerable to a denial of service due to holding a connection open for partial HTTP requests.', 'Apache Versions 1.x and 2.x are vulnerable.']</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Patch - 
-There are no vendor-supplied patches available at this time.
-Workaround: - Server-specific recommendations can be found here (https://community.qualys.com/blogs/securitylabs/2011/11/02/how-to-protect-against-slow-http-attacks). 
-- Countermeasures for Apache are described here (http://httpd.apache.org/docs/trunk/misc/security_tips.htmldos). 
-- Reverse proxies, load balancers and iptables can help to prevent this attack from occurring. 
-- Adjusting the TimeOut Directive (http://httpd.apache.org/docs/2.2/mod/core.htmltimeout) can also prevent this attack from occurring. 
-- A new module mod_reqtimeout (http://httpd.apache.org/docs/2.2/mod/mod_reqtimeout.html) has been introduced since Apache 2.2.15 to provide tools for mitigation against these forms of attack.
-Also refer to Cert Blog (http://www.cert.org/blogs/certcc/2009/07/slowloris_vs_your_webserver.html) and Slowloris and Mitigations for Apache document (http://bedagainstthewall.blogspot.com/2011/01/slowloris-and-mitigations-for-apache.html) for further information.</t>
+          <t>['Patch - There are no vendor-supplied patches available at this time.', 'Workaround: - Server-specific recommendations can be found here (https://community.qualys.com/blogs/securitylabs/2011/11/02/how-to-protect-against-slow-http-attacks). - Countermeasures for Apache are described here (http://httpd.apache.org/docs/trunk/misc/security_tips.htmldos). - Reverse proxies, load balancers and iptables can help to prevent this attack from occurring. - Adjusting the TimeOut Directive (http://httpd.apache.org/docs/2.2/mod/core.htmltimeout) can also prevent this attack from occurring. - A new module mod_reqtimeout (http://httpd.apache.org/docs/2.2/mod/mod_reqtimeout.html) has been introduced since Apache 2.2.15 to provide tools for mitigation against these forms of attack.', 'Also refer to Cert Blog (http://www.cert.org/blogs/certcc/2009/07/slowloris_vs_your_webserver.html) and Slowloris and Mitigations for Apache document (http://bedagainstthewall.blogspot.com/2011/01/slowloris-and-mitigations-for-apache.html) for further information.']</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>A remote attacker can cause a denial of service against the Web server which would prevent legitimate users from accessing the site. 
-Denial of service tools and scripts such as Slowloris takes advantage of this vulnerability.</t>
+          <t>['A remote attacker can cause a denial of service against the Web server which would prevent legitimate users from accessing the site. Denial of service tools and scripts such as Slowloris takes advantage of this vulnerability.']</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6596,24 +6076,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-49812:  Apache HTTP Server: mod_ssl TLS upgrade attack 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-49812: Apache HTTP Server: mod_ssl TLS upgrade attack', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6661,24 +6134,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-53020:  Apache HTTP Server: HTTP/2 DoS by Memory Increase 
-Affected Versions: 
-Apache httpd 2.4.17 through 2.4.63 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-53020: Apache HTTP Server: HTTP/2 DoS by Memory Increase', 'Affected Versions: Apache httpd 2.4.17 through 2.4.63']</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6726,24 +6192,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-43394:  Apache HTTP Server: SSRF on Windows due to UNC paths 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-43394: Apache HTTP Server: SSRF on Windows due to UNC paths', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6791,24 +6250,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-23048:  Apache HTTP Server: mod_ssl access control bypass with session resumption 
-Affected Versions: 
-Apache httpd 2.4.35 through 2.4.63 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-23048: Apache HTTP Server: mod_ssl access control bypass with session resumption', 'Affected Versions: Apache httpd 2.4.35 through 2.4.63']</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6856,24 +6308,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-42516:  Apache HTTP Server: HTTP response splitting 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-42516: Apache HTTP Server: HTTP response splitting', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6921,23 +6366,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-59775: Apache HTTP Server: NTLM Leakage on Windows through UNC SSRF', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6985,23 +6424,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-66200: Apache HTTP Server: mod_userdir+suexec bypass via AllowOverride FileInfo', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7049,23 +6482,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-58098: Apache HTTP Server: Server Side Includes adds query string to exec cmd=...', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7113,23 +6540,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33006: Apache HTTP Server: mod_auth_digest timing attack', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7177,23 +6598,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-24072: Apache HTTP Server: mod_rewrite elevation of privileges via ap_expr', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7241,24 +6656,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44119:  escalation of privilege through expressions in .htaccess in multiple modules 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44119: escalation of privilege through expressions in .htaccess in multiple modules', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7306,24 +6714,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44186:  Loop in `proxy_ftp_handler` in mod_proxy_ftp 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44186: Loop in `proxy_ftp_handler` in mod_proxy_ftp', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7371,24 +6772,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-49975:  mod_http2 denial of service 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-49975: mod_http2 denial of service', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7436,24 +6830,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34355:  mod_proxy_html buffer overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34355: mod_proxy_html buffer overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7501,24 +6888,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-43951:  OOB Read in `merge_response_headers` can cause crash 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-43951: OOB Read in `merge_response_headers` can cause crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7566,24 +6946,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-42535:  mod_dav_fs protected directory access 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-42535: mod_dav_fs protected directory access', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7631,24 +7004,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-43204:  Apache HTTP Server: SSRF with mod_headers setting Content-Type header 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-43204: Apache HTTP Server: SSRF with mod_headers setting Content-Type header', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7696,24 +7062,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-49630:  Apache HTTP Server: mod_proxy_http2 denial of service 
-Affected Versions: 
-Apache httpd 2.4.26 through 2.4.63 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-49630: Apache HTTP Server: mod_proxy_http2 denial of service', 'Affected Versions: Apache httpd 2.4.26 through 2.4.63']</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7761,23 +7120,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-65082: Apache HTTP Server: CGI environment variable override', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7825,23 +7178,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-55753: Apache HTTP Server: mod_md (ACME), unintended retry intervals', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7889,23 +7236,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34032: Apache HTTP Server: mod_proxy_ajp: Heap Buffer Over-Read Due to Missing Null-Termination Check (ajp_msg_get_string)', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7953,23 +7294,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33007: Apache HTTP Server: mod_authn_socache crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8017,23 +7352,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33857: Apache HTTP Server: Off-by-one OOB reads in AJP getter functions', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8081,23 +7410,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33523: Apache HTTP Server: multiple modules: HTTP response splitting forwarding malicious status line', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8145,23 +7468,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-28780: Apache HTTP Server: buffer overflow in mod_proxy_ajp via ajp_msg_check_header()', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8209,23 +7526,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29168: Apache HTTP Server: mod_md unrestricted OCSP response', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8273,24 +7584,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29170:  mod_proxy_ftp XSS 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29170: mod_proxy_ftp XSS', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8338,24 +7642,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29167:  mod_ldap per-dir use-after-free 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29167: mod_ldap per-dir use-after-free', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8403,24 +7700,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-42536:  mod_xml2enc heap overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-42536: mod_xml2enc heap overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8468,24 +7758,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44185:  Stack Buffer Over-Read in mod_ssl OCSP `send_request` 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44185: Stack Buffer Over-Read in mod_ssl OCSP `send_request`', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8533,24 +7816,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-48913:  mod_http2 memory corruption when file handles exhausted 
-Affected Versions: 
-Apache httpd 2.4.55 before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-48913: mod_http2 memory corruption when file handles exhausted', 'Affected Versions: Apache httpd 2.4.55 before 2.4.68']</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8598,24 +7874,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34356:  ProxyPassReverseCookieMap buffer overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34356: ProxyPassReverseCookieMap buffer overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8663,24 +7932,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44631:  Heap Underflow in `ap_regname` via Signed Char Overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44631: Heap Underflow in `ap_regname` via Signed Char Overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8768,7 +8030,11 @@
           <t>PHP Server Detected</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>['PHP is a general purpose scripting language that is especially suited for Web development and can be embedded in HTML.']</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
@@ -8806,7 +8072,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PHP is a general purpose scripting language that is especially suited for Web development and can be embedded in HTML.</t>
+          <t>['PHP is a general purpose scripting language that is especially suited for Web development and can be embedded in HTML.']</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -8852,55 +8118,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>The result section of this QID lists web applications and plugins that were detected on the target using web application fingerprinting. This technique compares static files at known locations against precomputed hashes for versions of those files in all available releases. The technique is fast, low-bandwidth, non-invasive, generic, and highly automatable.
- Following open source and free applications are currently supported:
- Joomla!
- MediaWiki
- WordPress
- phpBB
- MovableType
- Drupal
- osCommerce
- PHP-Nuke
- Moodle
- Liferay
- Tikiwiki
- Twiki
- phpmyadmin
- SPIP
- Confluence(free versions)
- Wikka
- Wacko
- Usemod
- e107
- Flyspray
- AppRain
- V-CMS
- AjaxPlorer/Pydio
- eFront Learning Management System
- vTigerCRM (Open source versions)
- MyBB
- WebCalendar
- PivotX WebLog
- DokuWiki
- MODX Revolution
- MODX Evolution
- Collabtive
- Achievo
- Magento 1.x CE
- iCE Hrm (Opensource Version)
- AdaptCMS
- ownCloud
- HumHub
- Redaxscript
- phpwcms
- Wolf CMS
- Pligg CMS
- Zen Cart
- Xoops
- TYPO3
- Microweber
- This QID is based on the Blind Elephant project (http://blindelephant.sourceforge.net/). For a complete list of supported web applications and plugins, please check the following link: DOC-5480 (https://community.qualys.com/docs/DOC-5480).</t>
+          <t>['The result section of this QID lists web applications and plugins that were detected on the target using web application fingerprinting. This technique compares static files at known locations against precomputed hashes for versions of those files in all available releases. The technique is fast, low-bandwidth, non-invasive, generic, and highly automatable. Following open source and free applications are currently supported: Joomla! MediaWiki WordPress phpBB MovableType Drupal osCommerce PHP-Nuke Moodle Liferay Tikiwiki Twiki phpmyadmin SPIP Confluence(free versions) Wikka Wacko Usemod e107 Flyspray AppRain V-CMS AjaxPlorer/Pydio eFront Learning Management System vTigerCRM (Open source versions) MyBB WebCalendar PivotX WebLog DokuWiki MODX Revolution MODX Evolution Collabtive Achievo Magento 1.x CE iCE Hrm (Opensource Version) AdaptCMS ownCloud HumHub Redaxscript phpwcms Wolf CMS Pligg CMS Zen Cart Xoops TYPO3 Microweber', 'This QID is based on the Blind Elephant project (http://blindelephant.sourceforge.net/). For a complete list of supported web applications and plugins, please check the following link: DOC-5480 (https://community.qualys.com/docs/DOC-5480).']</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -8944,7 +8162,11 @@
           <t>Web Server HTTP Protocol Versions</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>['This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.']</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
@@ -8988,7 +8210,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -9028,7 +8250,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drupal is a free and open source content management framework written in PHP and distributed under the GNU General Public License. </t>
+          <t>['Drupal is a free and open source content management framework written in PHP and distributed under the GNU General Public License.']</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -9068,8 +8290,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -9109,7 +8330,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -9149,7 +8370,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards. </t>
+          <t>['The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards.']</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -9189,7 +8410,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -9229,18 +8450,17 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -9278,14 +8498,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -9325,7 +8538,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -9365,8 +8578,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -9406,7 +8618,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server.</t>
+          <t>['The Result section displays the default Web page for the Web server.']</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -9452,7 +8664,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server following HTTP redirections.</t>
+          <t>['The Result section displays the default Web page for the Web server following HTTP redirections.']</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -9498,9 +8710,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request.  
-QID Detection Logic: 
-This QID returns the HTTP response method and header information returned by a web server.</t>
+          <t>["This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request. QID Detection Logic: This QID returns the HTTP response method and header information returned by a web server."]</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -9546,27 +8756,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
-1) no-referrer 
-2) no-referrer-when-downgrade 
-3) same-origin 
-4) origin 
-5) origin-when-cross-origin 
-6) strict-origin 
-7) strict-origin-when-cross-origin  </t>
+          <t>['No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 1) no-referrer 2) no-referrer-when-downgrade 3) same-origin 4) origin 5) origin-when-cross-origin 6) strict-origin 7) strict-origin-when-cross-origin']</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Referrer Policy header improves security by ensuring websites don't leak sensitive information via the referrer header. It's recommended to add secure Referrer Policies as a part of a defense-in-depth approach. 
-References: 
-- https://www.w3.org/TR/referrer-policy/ (https://www.w3.org/TR/referrer-policy/) 
-- https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy)</t>
+          <t>["Referrer Policy header improves security by ensuring websites don't leak sensitive information via the referrer header. It's recommended to add secure Referrer Policies as a part of a defense-in-depth approach.", 'References: - https://www.w3.org/TR/referrer-policy/ (https://www.w3.org/TR/referrer-policy/) - https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy)']</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>The Referrer-Policy header controls how much referrer information is sent to a site when navigating to it. Absence of Referrer-Policy header can lead to leakage of sensitive information via the referrer header.</t>
+          <t>['The Referrer-Policy header controls how much referrer information is sent to a site when navigating to it. Absence of Referrer-Policy header can lead to leakage of sensitive information via the referrer header.']</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -9608,7 +8808,11 @@
           <t>Web Server Version</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>['A web server is server software, or hardware dedicated to running this software, that can satisfy client requests on the World Wide Web.']</t>
+        </is>
+      </c>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
@@ -9652,14 +8856,13 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.
-The target Web server was found to support this functionality of the HTTP 1.1 protocol.</t>
+          <t>['Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.', 'The target Web server was found to support this functionality of the HTTP 1.1 protocol.']</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.</t>
+          <t>['Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.']</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -9703,7 +8906,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Based largely on the HTTP reply code, the following directories are most likely present on the host.</t>
+          <t>['Based largely on the HTTP reply code, the following directories are most likely present on the host.']</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -9749,21 +8952,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>The Secure Socket Layer (SSL) protocol allows for secure communication between a client and a server. The client usually authenticates the server using an algorithm like RSA or DSS. Some SSL ciphers allow SSL communication without authentication. Most common Web browsers like Microsoft Internet Explorer, Netscape and Mozilla do not use anonymous authentication ciphers by default.
- A vulnerability exists in SSL communications when clients are allowed to connect
-using no authentication algorithm. SSL client-server communication may use several different types of
-authentication: RSA, Diffie-Hellman, DSS or none. When 'none' is used, the
-communications are vulnerable to a man-in-the-middle attack."</t>
+          <t>['The Secure Socket Layer (SSL) protocol allows for secure communication between a client and a server. The client usually authenticates the server using an algorithm like RSA or DSS. Some SSL ciphers allow SSL communication without authentication. Most common Web browsers like Microsoft Internet Explorer, Netscape and Mozilla do not use anonymous authentication ciphers by default.', 'A vulnerability exists in SSL communications when clients are allowed to connect using no authentication algorithm. SSL client-server communication may use several different types of authentication: RSA, Diffie-Hellman, DSS or none. When \'none\' is used, the communications are vulnerable to a man-in-the-middle attack."']</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Disable support for anonymous authentication to mitigate this vulnerability.</t>
+          <t>['Disable support for anonymous authentication to mitigate this vulnerability.']</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>An attacker can exploit this vulnerability to impersonate your server to clients.</t>
+          <t>['An attacker can exploit this vulnerability to impersonate your server to clients.']</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -9808,14 +9007,12 @@
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Change the SSL/TLS server configuration to only allow strong key exchanges. Key exchanges used on the server should provide at least 112 bits of security, so the minimum key size to not flag this QID should be:
- 2048 bit key size for Diffie Hellman (DH) or RSA key exchanges
- 224 bit key size for Elliptic Curve Diffie Hellman (EDCH) key exchanges.</t>
+          <t>['Change the SSL/TLS server configuration to only allow strong key exchanges. Key exchanges used on the server should provide at least 112 bits of security, so the minimum key size to not flag this QID should be: 2048 bit key size for Diffie Hellman (DH) or RSA key exchanges 224 bit key size for Elliptic Curve Diffie Hellman (EDCH) key exchanges.']</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>An attacker with access to sufficient computational power might be able to recover the session key and decrypt session content.</t>
+          <t>['An attacker with access to sufficient computational power might be able to recover the session key and decrypt session content.']</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -9859,19 +9056,17 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>A remote management service that accepts unencrypted credentials was detected on the target host.
-Services like HTTP with basic auth are checked.</t>
+          <t>['A remote management service that accepts unencrypted credentials was detected on the target host.', 'Services like HTTP with basic auth are checked.']</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>If possible, use alternate services that provide encryption. 
-Using strong cryptography, render all authentication credentials (such as passwords/phrases) unreadable during transmission.</t>
+          <t>['If possible, use alternate services that provide encryption. Using strong cryptography, render all authentication credentials (such as passwords/phrases) unreadable during transmission.']</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>A malicious individual can easily intercept unencrypted passwords during transmission using a "network sniffer" and use this data to gain unauthorized access.</t>
+          <t>['A malicious individual can easily intercept unencrypted passwords during transmission using a "network sniffer" and use this data to gain unauthorized access.']</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -9909,19 +9104,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>During Web server authentication, communication can take place with the user by Clear Text User Credentials. 
-This Qid detects the HTTP basic authentication by sending a request and looks for the value of "WWW-Authenticate: Basic realm=" header field in response.</t>
+          <t>['During Web server authentication, communication can take place with the user by Clear Text User Credentials. This Qid detects the HTTP basic authentication by sending a request and looks for the value of "WWW-Authenticate: Basic realm=" header field in response.']</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Please contact the vendor of the hardware/software for a possible fix for the issue. It is advisable to work with vendor to disable communication over HTTP and make sure that every sensitive information transmits over HTTPS.</t>
+          <t>['Please contact the vendor of the hardware/software for a possible fix for the issue. It is advisable to work with vendor to disable communication over HTTP and make sure that every sensitive information transmits over HTTPS.']</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Using Readable Clear Text can help eavesdropping and thereby compromise confidentiality. 
-An attacker can successfully exploit this issue when the 401 error is returned when authentication is required. Also, an attacker can find out that the Basic Authentication scheme is used using the WWW-authenticate header.</t>
+          <t>['Using Readable Clear Text can help eavesdropping and thereby compromise confidentiality. An attacker can successfully exploit this issue when the 401 error is returned when authentication is required. Also, an attacker can find out that the Basic Authentication scheme is used using the WWW-authenticate header.']</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -9965,32 +9158,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">TLS is capable of using a multitude of ciphers (algorithms) to create the public and private key pairs. 
-For example if TLSv1.0 uses either the RC4 stream cipher, or a block cipher in CBC mode. 
-RC4 is known to have biases and the block cipher in CBC mode is vulnerable to the POODLE attack. 
-TLSv1.0, if configured to use the same cipher suites as SSLv3, includes a means by which a TLS implementation can downgrade the connection to SSL v3.0, thus weakening security. 
-A POODLE-type (https://blog.qualys.com/ssllabs/2014/12/08/poodle-bites-tls) attack could also be launched directly at TLS without negotiating a downgrade. 
-  This QID is an automatic PCI FAIL in accordance with the PCI standards.  
-Further details can be found under:  
-PCI: ASV Program Guide v3.1 (page 27) (https://www.pcisecuritystandards.org/documents/ASV_Program_Guide_v3.1.pdf) 
-PCI: Use of SSL Early TLS and ASV Scans (https://www.pcisecuritystandards.org/documents/Use-of-SSL-Early-TLS-and-ASV-Scans.pdf)
-NOTE: On March 31, 2021 Transport Layer Security (TLS) versions 1.0 (RFC 2246) and 1.1 (RFC 4346) are formally deprecated.
-Refer to Deprecating TLS 1.0 and TLS 1.1 (https://tools.ietf.org/html/rfc8996) </t>
+          <t>['TLS is capable of using a multitude of ciphers (algorithms) to create the public and private key pairs. For example if TLSv1.0 uses either the RC4 stream cipher, or a block cipher in CBC mode. RC4 is known to have biases and the block cipher in CBC mode is vulnerable to the POODLE attack.', 'TLSv1.0, if configured to use the same cipher suites as SSLv3, includes a means by which a TLS implementation can downgrade the connection to SSL v3.0, thus weakening security.', 'A POODLE-type (https://blog.qualys.com/ssllabs/2014/12/08/poodle-bites-tls) attack could also be launched directly at TLS without negotiating a downgrade.', 'This QID is an automatic PCI FAIL in accordance with the PCI standards.', 'Further details can be found under: PCI: ASV Program Guide v3.1 (page 27) (https://www.pcisecuritystandards.org/documents/ASV_Program_Guide_v3.1.pdf) PCI: Use of SSL Early TLS and ASV Scans (https://www.pcisecuritystandards.org/documents/Use-of-SSL-Early-TLS-and-ASV-Scans.pdf)', 'NOTE: On March 31, 2021 Transport Layer Security (TLS) versions 1.0 (RFC 2246) and 1.1 (RFC 4346) are formally deprecated. Refer to Deprecating TLS 1.0 and TLS 1.1 (https://tools.ietf.org/html/rfc8996)']</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Disable the use of TLSv1.0 protocol in favor of a cryptographically stronger protocol such as TLSv1.2.
-The following openssl commands can be used to do a manual test:
-openssl s_client -connect ip:port -tls1
-If the test is successful, then the target support TLSv1</t>
+          <t>['Disable the use of TLSv1.0 protocol in favor of a cryptographically stronger protocol such as TLSv1.2. The following openssl commands can be used to do a manual test: openssl s_client -connect ip:port -tls1', 'If the test is successful, then the target support TLSv1']</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>An attacker can exploit cryptographic flaws to conduct man-in-the-middle type attacks or to decryption communications. 
-For example: An attacker could force a downgrade from the TLS protocol to the older SSLv3.0 protocol and exploit the POODLE vulnerability, read secure communications or maliciously modify messages. 
-A POODLE-type (https://blog.qualys.com/ssllabs/2014/12/08/poodle-bites-tls) attack could also be launched directly at TLS without negotiating a downgrade.</t>
+          <t>['An attacker can exploit cryptographic flaws to conduct man-in-the-middle type attacks or to decryption communications. For example: An attacker could force a downgrade from the TLS protocol to the older SSLv3.0 protocol and exploit the POODLE vulnerability, read secure communications or maliciously modify messages. A POODLE-type (https://blog.qualys.com/ssllabs/2014/12/08/poodle-bites-tls) attack could also be launched directly at TLS without negotiating a downgrade.']</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -10034,23 +9212,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">The scan target supports version 1.1 of the TLS protocol. That version is in the process of being deprecated and is no longer recommended. Instead the newer versions 1.2 and/or 1.3 should be used. The TLSv1.1 protocol itself does not have any currently exploitable vulnerabilities. However some vendor implementations of TLSv1.1 have weaknesses which may be exploitable. 
-This QID is posted as potential, when servers require client certificates and we cannot complete the handshake. 
-NOTE: On March 31, 2021 Transport Layer Security (TLS) versions 1.0 (RFC 2246) and 1.1 (RFC 4346) are formally deprecated.
-Refer to Deprecating TLS 1.0 and TLS 1.1 (https://tools.ietf.org/html/rfc8996) </t>
+          <t>['The scan target supports version 1.1 of the TLS protocol. That version is in the process of being deprecated and is no longer recommended. Instead the newer versions 1.2 and/or 1.3 should be used. The TLSv1.1 protocol itself does not have any currently exploitable vulnerabilities. However some vendor implementations of TLSv1.1 have weaknesses which may be exploitable. This QID is posted as potential, when servers require client certificates and we cannot complete the handshake.', 'NOTE: On March 31, 2021 Transport Layer Security (TLS) versions 1.0 (RFC 2246) and 1.1 (RFC 4346) are formally deprecated. Refer to Deprecating TLS 1.0 and TLS 1.1 (https://tools.ietf.org/html/rfc8996)']</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Disable the use of TLSv1.1 protocol in favor of a cryptographically stronger protocol such as TLSv1.2.
-The following openssl commands can be used to do a manual test:
-openssl s_client -connect ip:port -tls1_1
-If the test is successful, then the target support TLSv1.1</t>
+          <t>['Disable the use of TLSv1.1 protocol in favor of a cryptographically stronger protocol such as TLSv1.2. The following openssl commands can be used to do a manual test: openssl s_client -connect ip:port -tls1_1', 'If the test is successful, then the target support TLSv1.1']</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Supporting TLSv1.1 by itself does not necessarily have any harmful consequences, but it is no longer considered best practice because of bad past experience with some vendor implementations of TLSv1.1.</t>
+          <t>['Supporting TLSv1.1 by itself does not necessarily have any harmful consequences, but it is no longer considered best practice because of bad past experience with some vendor implementations of TLSv1.1.']</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -10094,19 +9266,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>An SSL Certificate associates an entity (person, organization, host, etc.) with a Public Key. In an SSL connection, the client authenticates the remote server using the server's Certificate and extracts the Public Key in the Certificate to establish the secure connection.
-The client can trust that the Server Certificate belongs to the server only if it is signed by a mutually trusted third-party Certificate Authority (CA). Self-signed certificates are created generally for testing purposes or to avoid paying third-party CAs. These should not be used on any production or critical servers.
-By exploiting this vulnerability, an attacker can impersonate the server by presenting a fake self-signed certificate. If the client knows that the server does not have a trusted certificate, it will accept this spoofed certificate and communicate with the remote server.</t>
+          <t>["An SSL Certificate associates an entity (person, organization, host, etc.) with a Public Key. In an SSL connection, the client authenticates the remote server using the server's Certificate and extracts the Public Key in the Certificate to establish the secure connection.", 'The client can trust that the Server Certificate belongs to the server only if it is signed by a mutually trusted third-party Certificate Authority (CA). Self-signed certificates are created generally for testing purposes or to avoid paying third-party CAs. These should not be used on any production or critical servers.', 'By exploiting this vulnerability, an attacker can impersonate the server by presenting a fake self-signed certificate. If the client knows that the server does not have a trusted certificate, it will accept this spoofed certificate and communicate with the remote server.']</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Please install a server certificate signed by a trusted third-party Certificate Authority.</t>
+          <t>['Please install a server certificate signed by a trusted third-party Certificate Authority.']</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>By exploiting this vulnerability, an attacker can launch a man-in-the-middle attack.</t>
+          <t>['By exploiting this vulnerability, an attacker can launch a man-in-the-middle attack.']</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -10150,20 +9320,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>An SSL Certificate associates an entity (person, organization, host, etc.) with a Public Key. In an SSL connection, the client authenticates the remote server using the server's Certificate and extracts the Public Key in the Certificate to establish the secure connection.
-A certificate whose Subject commonName or subjectAltName does not match the server FQDN offers only encryption without authentication.
-Please note that a false positive reporting of this vulnerability is possible in the following case:
- If the common name of the certificate uses a wildcard such as *.somedomainname.com and the reverse DNS resolution of the target IP is not configured. In this case there is no way for Qualys to associate the wildcard common name to the IP. Adding a reverse DNS lookup entry to the target IP will solve this problem.</t>
+          <t>["An SSL Certificate associates an entity (person, organization, host, etc.) with a Public Key. In an SSL connection, the client authenticates the remote server using the server's Certificate and extracts the Public Key in the Certificate to establish the secure connection.", 'A certificate whose Subject commonName or subjectAltName does not match the server FQDN offers only encryption without authentication.', 'Please note that a false positive reporting of this vulnerability is possible in the following case: If the common name of the certificate uses a wildcard such as *.somedomainname.com and the reverse DNS resolution of the target IP is not configured. In this case there is no way for Qualys to associate the wildcard common name to the IP. Adding a reverse DNS lookup entry to the target IP will solve this problem.']</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Please install a server certificate whose Subject commonName or subjectAltName matches the server FQDN.</t>
+          <t>['Please install a server certificate whose Subject commonName or subjectAltName matches the server FQDN.']</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>A man-in-the-middle attacker can exploit this vulnerability in tandem with a DNS cache poisoning attack to lure the client to another server, and then steal all the encryption communication.</t>
+          <t>['A man-in-the-middle attacker can exploit this vulnerability in tandem with a DNS cache poisoning attack to lure the client to another server, and then steal all the encryption communication.']</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -10207,22 +9374,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>An SSL Certificate associates an entity with a Public Key and is used by clients to authenticate the server during an SSL/TLS connection. This authentication relies on verifying that the certificate is signed by a trusted Certificate Authority (CA). 
-If certificate verification fails, the client cannot reliably authenticate the server and may abort the connection or proceed without validation. 
-Verification failure may occur due to reasons such as a self-signed certificate, untrusted CA, missing intermediate certificates, expired or invalid certificates, mismatched issuer information, unsupported signature algorithms, or signature validation errors. 
-This may allow an attacker to perform man-in-the-middle attacks and compromise the confidentiality and integrity of the communication.</t>
+          <t>['An SSL Certificate associates an entity with a Public Key and is used by clients to authenticate the server during an SSL/TLS connection. This authentication relies on verifying that the certificate is signed by a trusted Certificate Authority (CA). If certificate verification fails, the client cannot reliably authenticate the server and may abort the connection or proceed without validation. Verification failure may occur due to reasons such as a self-signed certificate, untrusted CA, missing intermediate certificates, expired or invalid certificates, mismatched issuer information, unsupported signature algorithms, or signature validation errors. This may allow an attacker to perform man-in-the-middle attacks and compromise the confidentiality and integrity of the communication.']</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ensure the SSL certificate is valid and trusted. Install a certificate signed by a trusted Certificate Authority and configure the complete certificate chain, including any required intermediate certificates. Replace expired or invalid certificates and ensure proper issuer and signature configuration</t>
+          <t>['Ensure the SSL certificate is valid and trusted. Install a certificate signed by a trusted Certificate Authority and configure the complete certificate chain, including any required intermediate certificates. Replace expired or invalid certificates and ensure proper issuer and signature configuration']</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>By exploiting this vulnerability, man-in-the-middle attacks in tandem with DNS cache poisoning can occur.
-Exception: 
-If the server communicates only with a restricted set of clients who have the server certificate or the trusted CA certificate, then the server or CA certificate may not be available publicly, and the scan will be unable to verify the signature.</t>
+          <t>['By exploiting this vulnerability, man-in-the-middle attacks in tandem with DNS cache poisoning can occur.', 'Exception: If the server communicates only with a restricted set of clients who have the server certificate or the trusted CA certificate, then the server or CA certificate may not be available publicly, and the scan will be unable to verify the signature.']</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -10266,21 +9428,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Subscriber Certificates issued on or after 1 September 2020 SHOULD NOT have a Validity Period greater than 397 days and MUST NOT have a Validity Period greater than 398 days. (13 months) 
-Subscriber Certificates issued after 1 March 2018, but prior to 1 September 2020, MUST NOT have a Validity Period greater than 825 days. (27 months) 
-Subscriber Certificates issued after 1 July 2016 but prior to 1 March 2018 MUST NOT have a Validity Period greater than 39 months. 
-SSL certificates have limited validity periods so that the certificate's holder identity information is re-authenticated more frequently. 
-It is detected that maximum validity of certificate on the system is more than what is recommended.</t>
+          <t>["Subscriber Certificates issued on or after 1 September 2020 SHOULD NOT have a Validity Period greater than 397 days and MUST NOT have a Validity Period greater than 398 days. (13 months) Subscriber Certificates issued after 1 March 2018, but prior to 1 September 2020, MUST NOT have a Validity Period greater than 825 days. (27 months) Subscriber Certificates issued after 1 July 2016 but prior to 1 March 2018 MUST NOT have a Validity Period greater than 39 months. SSL certificates have limited validity periods so that the certificate's holder identity information is re-authenticated more frequently.", 'It is detected that maximum validity of certificate on the system is more than what is recommended.']</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Please install a server certificate with recommended maximum validity.</t>
+          <t>['Please install a server certificate with recommended maximum validity.']</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>By exploiting this vulnerability, an attacker can launch a man-in-the-middle attack.</t>
+          <t>['By exploiting this vulnerability, an attacker can launch a man-in-the-middle attack.']</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -10324,30 +9482,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-38472: SSRF in Apache HTTP Server on Windows allows to potentially leak NTML hashes to a malicious server via SSRF and malicious requests or content 
-CVE-2024-38473: Apache HTTP Server proxy encoding problem 
-CVE-2024-38474: Apache HTTP Server weakness with encoded question marks in backreferences 
-CVE-2024-38475: Apache HTTP Server weakness in mod_rewrite when first segment of substitution matches filesystem path. 
-CVE-2024-38476: Apache HTTP Server may use exploitable/malicious backend application output to run local handlers via internal redirect 
-CVE-2024-38477: Apache HTTP Server Crash resulting in Denial of Service in mod_proxy via a malicious request 
-CVE-2024-39573: Apache HTTP Server mod_rewrite proxy handler substitution 
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.60 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-38472: SSRF in Apache HTTP Server on Windows allows to potentially leak NTML hashes to a malicious server via SSRF and malicious requests or content CVE-2024-38473: Apache HTTP Server proxy encoding problem CVE-2024-38474: Apache HTTP Server weakness with encoded question marks in backreferences CVE-2024-38475: Apache HTTP Server weakness in mod_rewrite when first segment of substitution matches filesystem path. CVE-2024-38476: Apache HTTP Server may use exploitable/malicious backend application output to run local handlers via internal redirect CVE-2024-38477: Apache HTTP Server Crash resulting in Denial of Service in mod_proxy via a malicious request CVE-2024-39573: Apache HTTP Server mod_rewrite proxy handler substitution', 'Affected Versions: Apache HTTP Server versions prior to 2.4.60']</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information, visit here (https://httpd.apache.org/download.cgi). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/download.cgi)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information, visit here (https://httpd.apache.org/download.cgi). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/download.cgi)']</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise Confidentiality, Integrity, and Availability of the Data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise Confidentiality, Integrity, and Availability of the Data.']</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10395,24 +9540,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-47252:  Apache HTTP Server: mod_ssl error log variable escaping 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-47252: Apache HTTP Server: mod_ssl error log variable escaping', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10460,23 +9598,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29169: Apache HTTP Server: mod_dav_lock indirect lock crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10524,23 +9656,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34059: Apache HTTP Server: mod_proxy_ajp: Heap Over-Read and memory disclosure in ajp_parse_data()', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10588,38 +9714,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TCP provides stateful communications between hosts on a network. TCP sessions are established by a three-way handshake and use random 32-bit sequence and acknowledgement numbers to ensure the validity of traffic. A vulnerability was reported that may permit TCP sequence numbers to be more easily approximated by remote attackers. This issue affects products released by multiple vendors.  
-The cause of the vulnerability is that affected implementations will accept TCP sequence numbers within a certain range, known as the acknowledgement range, of the expected sequence number for a packet in the session. This is determined by the TCP window size, which is negotiated during the three-way handshake for the session. Larger TCP window sizes may be set to allow for more throughput, but the larger the TCP window size, the more probable it is to guess a TCP sequence number that falls within an acceptable range. It was initially thought that guessing an acceptable sequence number was relatively difficult for most implementations given random distribution, making this type of attack impractical. However, some implementations may make it easier to successfully approximate an acceptable TCP sequence number, making these attacks possible with a number of protocols and implementations.
-This is further compounded by the fact that some implementations may support the use of the TCP Window Scale Option, as described in RFC 1323, to extend the TCP window size to a maximum value of 1 billion.
-This vulnerability will permit a remote attacker to inject a SYN or RST packet into the session, causing it to be reset and effectively allowing for denial of service attacks. An attacker would exploit this issue by sending a packet to a receiving implementation with an approximated sequence number and a forged source IP address and TCP port.
-There are a few factors that may present viable target implementations, such as those which depend on long-lived TCP connections, those that have known or easily guessed IP address endpoints and those implementations with easily guessed TCP source ports. It has been noted that Border Gateway Protocol (BGP) is reported to be particularly vulnerable to this type of attack, due to the use of long-lived TCP sessions and the possibility that some implementations may use the TCP Window Scale Option. As a result, this issue is likely to affect a number of routing platforms.
-Another factor to consider is the relative difficulty of injecting packets into TCP sessions, as a number of receiving implementations will reassemble packets in order, dropping any duplicates. This may make some implementations more resistant to attacks than others.
-It should be noted that while a number of vendors have confirmed this issue in various products, investigations are ongoing and it is likely that many other vendors and products will turn out to be vulnerable as the issue is investigated further.</t>
+          <t>['TCP provides stateful communications between hosts on a network. TCP sessions are established by a three-way handshake and use random 32-bit sequence and acknowledgement numbers to ensure the validity of traffic. A vulnerability was reported that may permit TCP sequence numbers to be more easily approximated by remote attackers. This issue affects products released by multiple vendors.', 'The cause of the vulnerability is that affected implementations will accept TCP sequence numbers within a certain range, known as the acknowledgement range, of the expected sequence number for a packet in the session. This is determined by the TCP window size, which is negotiated during the three-way handshake for the session. Larger TCP window sizes may be set to allow for more throughput, but the larger the TCP window size, the more probable it is to guess a TCP sequence number that falls within an acceptable range. It was initially thought that guessing an acceptable sequence number was relatively difficult for most implementations given random distribution, making this type of attack impractical. However, some implementations may make it easier to successfully approximate an acceptable TCP sequence number, making these attacks possible with a number of protocols and implementations.', 'This is further compounded by the fact that some implementations may support the use of the TCP Window Scale Option, as described in RFC 1323, to extend the TCP window size to a maximum value of 1 billion.', 'This vulnerability will permit a remote attacker to inject a SYN or RST packet into the session, causing it to be reset and effectively allowing for denial of service attacks. An attacker would exploit this issue by sending a packet to a receiving implementation with an approximated sequence number and a forged source IP address and TCP port.', 'There are a few factors that may present viable target implementations, such as those which depend on long-lived TCP connections, those that have known or easily guessed IP address endpoints and those implementations with easily guessed TCP source ports. It has been noted that Border Gateway Protocol (BGP) is reported to be particularly vulnerable to this type of attack, due to the use of long-lived TCP sessions and the possibility that some implementations may use the TCP Window Scale Option. As a result, this issue is likely to affect a number of routing platforms.', 'Another factor to consider is the relative difficulty of injecting packets into TCP sessions, as a number of receiving implementations will reassemble packets in order, dropping any duplicates. This may make some implementations more resistant to attacks than others.', 'It should be noted that while a number of vendors have confirmed this issue in various products, investigations are ongoing and it is likely that many other vendors and products will turn out to be vulnerable as the issue is investigated further.']</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Please first check the results section below for the port number on which this vulnerability was detected. If that port number is known to be used for port-forwarding, then it is the backend host that is really vulnerable.
-Various implementations and products including Check Point, Cisco, Cray Inc, Hitachi, Internet Initiative Japan, Inc (IIJ), Juniper Networks, NEC and Yamaha are currently undergoing review. Contact the vendors to obtain more information about affected products and fixes. NISCC Advisory 236929 - Vulnerability Issues in TCP (http://packetstormsecurity.org/0404-advisories/246929.html) details the vendor patch status as of the time of the advisory, and identifies resolutions and workarounds.
-Refer to US-CERT Vulnerability Note VU415294 (http://www.kb.cert.org/vuls/id/415294) and OSVDB Article 4030 (http://osvdb.org/4030) to obtain a list of vendors affected by this issue and a note on resolutions (if any) provided by the vendor.
-For Microsoft: Refer to MS05-019 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2005/ms05-019) and MS06-064 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2006/ms06-064) for further details.
-For SGI IRIX: Refer to SGI Security Advisory 20040905-01-P (ftp://patches.sgi.com/support/free/security/advisories/20040905-01-P.asc)
-For SCO UnixWare 7.1.3 and 7.1.1: Refer to SCO Security Advisory SCOSA-2005.14 (ftp://ftp.sco.com/pub/updates/UnixWare/SCOSA-2005.14/SCOSA-2005.14.txt)
-For Solaris (Sun Microsystems): The vendor has acknowledged the vulnerability; however a patch is not available. Refer to Sun Microsystems, Inc. Information for VU415294 (http://www.kb.cert.org/vuls/id/JARL-5YGQAJ) to obtain additional details. Also, refer to TA04-111A (http://www.us-cert.gov/cas/techalerts/TA04-111A.html) for detailed mitigating strategies against these attacks.
-For NetBSD: Refer to NetBSD-SA2004-006 (ftp://ftp.netbsd.org/pub/NetBSD/security/advisories/NetBSD-SA2004-006.txt.asc)
-For Cisco: Refer to cisco-sa-20040420-tcp-ios.shtml (http://www.cisco.com/warp/public/707/cisco-sa-20040420-tcp-ios.shtml).
-For IBM : Refer to IBM-tcp-sequence-number-cve-2004-0230 (https://www.ibm.com/support/pages/tcp-sequence-number-approximation-based-denial-service-cve-2004-0230).
-For Red Hat Linux: There is no fix available : Refer to  (https://access.redhat.com/security/cve/cve-2004-0230).
-Workaround: The following BGP-specific workaround information has been provided.
-For BGP implementations that support it, the TCP MD5 Signature Option should be enabled. Passwords that the MD5 checksum is applied to should be set to strong values and changed on a regular basis.
-Secure BGP configuration instructions have been provided for Cisco and Juniper at these locations:
-Secure Cisco IOS BGP Template (http://www.cymru.com/Documents/secure-bgp-template.html)
-JUNOS Secure BGP Template (http://www.cymru.com/gillsr/documents/junos-bgp-template.pdf)</t>
+          <t>['Please first check the results section below for the port number on which this vulnerability was detected. If that port number is known to be used for port-forwarding, then it is the backend host that is really vulnerable.', 'Various implementations and products including Check Point, Cisco, Cray Inc, Hitachi, Internet Initiative Japan, Inc (IIJ), Juniper Networks, NEC and Yamaha are currently undergoing review. Contact the vendors to obtain more information about affected products and fixes. NISCC Advisory 236929 - Vulnerability Issues in TCP (http://packetstormsecurity.org/0404-advisories/246929.html) details the vendor patch status as of the time of the advisory, and identifies resolutions and workarounds.', 'Refer to US-CERT Vulnerability Note VU415294 (http://www.kb.cert.org/vuls/id/415294) and OSVDB Article 4030 (http://osvdb.org/4030) to obtain a list of vendors affected by this issue and a note on resolutions (if any) provided by the vendor.', 'For Microsoft: Refer to MS05-019 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2005/ms05-019) and MS06-064 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2006/ms06-064) for further details.', 'For SGI IRIX: Refer to SGI Security Advisory 20040905-01-P (ftp://patches.sgi.com/support/free/security/advisories/20040905-01-P.asc)', 'For SCO UnixWare 7.1.3 and 7.1.1: Refer to SCO Security Advisory SCOSA-2005.14 (ftp://ftp.sco.com/pub/updates/UnixWare/SCOSA-2005.14/SCOSA-2005.14.txt)', 'For Solaris (Sun Microsystems): The vendor has acknowledged the vulnerability; however a patch is not available. Refer to Sun Microsystems, Inc. Information for VU415294 (http://www.kb.cert.org/vuls/id/JARL-5YGQAJ) to obtain additional details. Also, refer to TA04-111A (http://www.us-cert.gov/cas/techalerts/TA04-111A.html) for detailed mitigating strategies against these attacks.', 'For NetBSD: Refer to NetBSD-SA2004-006 (ftp://ftp.netbsd.org/pub/NetBSD/security/advisories/NetBSD-SA2004-006.txt.asc)', 'For Cisco: Refer to cisco-sa-20040420-tcp-ios.shtml (http://www.cisco.com/warp/public/707/cisco-sa-20040420-tcp-ios.shtml).', 'For IBM : Refer to IBM-tcp-sequence-number-cve-2004-0230 (https://www.ibm.com/support/pages/tcp-sequence-number-approximation-based-denial-service-cve-2004-0230).', 'For Red Hat Linux: There is no fix available : Refer to (https://access.redhat.com/security/cve/cve-2004-0230).', 'Workaround: The following BGP-specific workaround information has been provided.', 'For BGP implementations that support it, the TCP MD5 Signature Option should be enabled. Passwords that the MD5 checksum is applied to should be set to strong values and changed on a regular basis.', 'Secure BGP configuration instructions have been provided for Cisco and Juniper at these locations:', 'Secure Cisco IOS BGP Template (http://www.cymru.com/Documents/secure-bgp-template.html)', 'JUNOS Secure BGP Template (http://www.cymru.com/gillsr/documents/junos-bgp-template.pdf)']</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Successful exploitation of this issue could lead to denial of service attacks on the TCP based services of target hosts.</t>
+          <t>['Successful exploitation of this issue could lead to denial of service attacks on the TCP based services of target hosts.']</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10661,25 +9766,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2023-38709: Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. 
-CVE-2024-24795: HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack.  
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.59 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2023-38709: Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. CVE-2024-24795: HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack.', 'Affected Versions: Apache HTTP Server versions prior to 2.4.59']</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Customers are advised to update the latest Apache versions respectively. 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update the latest Apache versions respectively. For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.</t>
+          <t>['Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.']</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10727,24 +9824,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-49812:  Apache HTTP Server: mod_ssl TLS upgrade attack 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-49812: Apache HTTP Server: mod_ssl TLS upgrade attack', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10792,24 +9882,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-53020:  Apache HTTP Server: HTTP/2 DoS by Memory Increase 
-Affected Versions: 
-Apache httpd 2.4.17 through 2.4.63 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-53020: Apache HTTP Server: HTTP/2 DoS by Memory Increase', 'Affected Versions: Apache httpd 2.4.17 through 2.4.63']</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10857,24 +9940,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-43394:  Apache HTTP Server: SSRF on Windows due to UNC paths 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-43394: Apache HTTP Server: SSRF on Windows due to UNC paths', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10922,24 +9998,17 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-23048:  Apache HTTP Server: mod_ssl access control bypass with session resumption 
-Affected Versions: 
-Apache httpd 2.4.35 through 2.4.63 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-23048: Apache HTTP Server: mod_ssl access control bypass with session resumption', 'Affected Versions: Apache httpd 2.4.35 through 2.4.63']</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10987,24 +10056,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-42516:  Apache HTTP Server: HTTP response splitting 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-42516: Apache HTTP Server: HTTP response splitting', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11052,23 +10114,17 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-59775: Apache HTTP Server: NTLM Leakage on Windows through UNC SSRF', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11116,23 +10172,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-66200: Apache HTTP Server: mod_userdir+suexec bypass via AllowOverride FileInfo', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11180,23 +10230,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-58098: Apache HTTP Server: Server Side Includes adds query string to exec cmd=...', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11244,23 +10288,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33006: Apache HTTP Server: mod_auth_digest timing attack', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11308,23 +10346,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-24072: Apache HTTP Server: mod_rewrite elevation of privileges via ap_expr', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11372,24 +10404,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44119:  escalation of privilege through expressions in .htaccess in multiple modules 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44119: escalation of privilege through expressions in .htaccess in multiple modules', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11437,24 +10462,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44186:  Loop in `proxy_ftp_handler` in mod_proxy_ftp 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44186: Loop in `proxy_ftp_handler` in mod_proxy_ftp', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11502,24 +10520,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-49975:  mod_http2 denial of service 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-49975: mod_http2 denial of service', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11567,24 +10578,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34355:  mod_proxy_html buffer overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34355: mod_proxy_html buffer overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11632,24 +10636,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-43951:  OOB Read in `merge_response_headers` can cause crash 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-43951: OOB Read in `merge_response_headers` can cause crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11697,24 +10694,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-42535:  mod_dav_fs protected directory access 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-42535: mod_dav_fs protected directory access', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11762,21 +10752,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is the global system user list, which was retrieved during the scan by exploiting one or more vulnerabilities or via authentication provided by user. The Qualys IDs for the vulnerabilities leading to the disclosure of these users are also given in the Result section. Each user will be displayed only once, even though it may be obtained by using different methods. </t>
+          <t>['This is the global system user list, which was retrieved during the scan by exploiting one or more vulnerabilities or via authentication provided by user. The Qualys IDs for the vulnerabilities leading to the disclosure of these users are also given in the Result section. Each user will be displayed only once, even though it may be obtained by using different methods.']</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>To prevent your host from being attacked, do one or more of the following:
- Remove (or rename) unnecessary accounts
- Shutdown unnecessary network services
- Ensure the passwords to these accounts are kept secret
- Use a firewall to restrict access to your hosts from unauthorized domains</t>
+          <t>['To prevent your host from being attacked, do one or more of the following:', 'Remove (or rename) unnecessary accounts Shutdown unnecessary network services Ensure the passwords to these accounts are kept secret Use a firewall to restrict access to your hosts from unauthorized domains']</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>These common account(s) can be used by a malicious user to break-in the system via password bruteforcing.</t>
+          <t>['These common account(s) can be used by a malicious user to break-in the system via password bruteforcing.']</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -11814,18 +10800,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Simple Mail Transfer Protocol (SMTP) is used to transfer mail between servers.  When one mail server establishes a connection with another mail server to deliver an e-mail message, it can check the validity of the destination user on the remote host by using the VRFY command.</t>
+          <t>['Simple Mail Transfer Protocol (SMTP) is used to transfer mail between servers. When one mail server establishes a connection with another mail server to deliver an e-mail message, it can check the validity of the destination user on the remote host by using the VRFY command.']</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Your mail server should not allow remote users to verify the existence of a particular user on your system.  If you are using Sendmail Version 8, then you can disable the VRFY command by adding the line "novrfy" to your sendmail.cf file, which is usually located in the /etc directory.
-Please note that RFC 821 (Simple Mail Transfer Protocol) defines SMTP 2xx replies as positive completion replies, noting "The requested action has been successfully completed". An SMTP server that responds to a VRFY command with a 2xx reply will be marked as vulnerable.</t>
+          <t>['Your mail server should not allow remote users to verify the existence of a particular user on your system. If you are using Sendmail Version 8, then you can disable the VRFY command by adding the line "novrfy" to your sendmail.cf file, which is usually located in the /etc directory.', 'Please note that RFC 821 (Simple Mail Transfer Protocol) defines SMTP 2xx replies as positive completion replies, noting "The requested action has been successfully completed". An SMTP server that responds to a VRFY command with a 2xx reply will be marked as vulnerable.']</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>If a host is running an SMTP server, unauthorized users can obtain valid logins by brute forcing common "login names" with the VRFY command.</t>
+          <t>['If a host is running an SMTP server, unauthorized users can obtain valid logins by brute forcing common "login names" with the VRFY command.']</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -11869,24 +10854,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-43204:  Apache HTTP Server: SSRF with mod_headers setting Content-Type header 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-43204: Apache HTTP Server: SSRF with mod_headers setting Content-Type header', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11934,24 +10912,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-49630:  Apache HTTP Server: mod_proxy_http2 denial of service 
-Affected Versions: 
-Apache httpd 2.4.26 through 2.4.63 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-49630: Apache HTTP Server: mod_proxy_http2 denial of service', 'Affected Versions: Apache httpd 2.4.26 through 2.4.63']</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11999,23 +10970,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-65082: Apache HTTP Server: CGI environment variable override', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12063,23 +11028,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-55753: Apache HTTP Server: mod_md (ACME), unintended retry intervals', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12127,23 +11086,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34032: Apache HTTP Server: mod_proxy_ajp: Heap Buffer Over-Read Due to Missing Null-Termination Check (ajp_msg_get_string)', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12191,23 +11144,17 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33007: Apache HTTP Server: mod_authn_socache crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12255,23 +11202,17 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33857: Apache HTTP Server: Off-by-one OOB reads in AJP getter functions', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12319,23 +11260,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33523: Apache HTTP Server: multiple modules: HTTP response splitting forwarding malicious status line', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -12383,23 +11318,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-28780: Apache HTTP Server: buffer overflow in mod_proxy_ajp via ajp_msg_check_header()', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -12447,23 +11376,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29168: Apache HTTP Server: mod_md unrestricted OCSP response', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -12511,24 +11434,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29170:  mod_proxy_ftp XSS 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29170: mod_proxy_ftp XSS', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -12576,24 +11492,17 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-29167:  mod_ldap per-dir use-after-free 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29167: mod_ldap per-dir use-after-free', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -12641,24 +11550,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-42536:  mod_xml2enc heap overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-42536: mod_xml2enc heap overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -12706,24 +11608,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44185:  Stack Buffer Over-Read in mod_ssl OCSP `send_request` 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44185: Stack Buffer Over-Read in mod_ssl OCSP `send_request`', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12771,24 +11666,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-48913:  mod_http2 memory corruption when file handles exhausted 
-Affected Versions: 
-Apache httpd 2.4.55 before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-48913: mod_http2 memory corruption when file handles exhausted', 'Affected Versions: Apache httpd 2.4.55 before 2.4.68']</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -12836,24 +11724,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34356:  ProxyPassReverseCookieMap buffer overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34356: ProxyPassReverseCookieMap buffer overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -12901,24 +11782,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44631:  Heap Underflow in `ap_regname` via Signed Char Overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44631: Heap Underflow in `ap_regname` via Signed Char Overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12966,7 +11840,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Simple Mail Transfer Protocol is a communication protocol for electronic mail transmission. </t>
+          <t>['The Simple Mail Transfer Protocol is a communication protocol for electronic mail transmission.']</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -13012,7 +11886,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.</t>
+          <t>['This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.']</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -13058,7 +11932,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -13098,8 +11972,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -13139,7 +12012,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -13177,7 +12050,11 @@
           <t>Apache HTTP Server Detected</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>['The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards.']</t>
+        </is>
+      </c>
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr"/>
@@ -13215,7 +12092,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -13255,18 +12132,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -13304,14 +12180,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -13351,7 +12220,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -13391,8 +12260,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -13432,7 +12300,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server.</t>
+          <t>['The Result section displays the default Web page for the Web server.']</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -13478,7 +12346,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server following HTTP redirections.</t>
+          <t>['The Result section displays the default Web page for the Web server following HTTP redirections.']</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -13524,9 +12392,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request.  
-QID Detection Logic: 
-This QID returns the HTTP response method and header information returned by a web server.</t>
+          <t>["This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request. QID Detection Logic: This QID returns the HTTP response method and header information returned by a web server."]</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -13572,7 +12438,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">cAdvisor (Container Advisor) provides container users an understanding of the resource usage and performance characteristics of their running containers. It is a running daemon that collects, aggregates, processes, and exports information about running containers. </t>
+          <t>['cAdvisor (Container Advisor) provides container users an understanding of the resource usage and performance characteristics of their running containers. It is a running daemon that collects, aggregates, processes, and exports information about running containers.']</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -13618,7 +12484,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>A web server is server software, or hardware dedicated to running this software, that can satisfy client requests on the World Wide Web.</t>
+          <t>['A web server is server software, or hardware dedicated to running this software, that can satisfy client requests on the World Wide Web.']</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -13664,14 +12530,13 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.
-The target Web server was found to support this functionality of the HTTP 1.1 protocol.</t>
+          <t>['Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.', 'The target Web server was found to support this functionality of the HTTP 1.1 protocol.']</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.</t>
+          <t>['Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.']</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -13715,7 +12580,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Based largely on the HTTP reply code, the following directories are most likely present on the host.</t>
+          <t>['Based largely on the HTTP reply code, the following directories are most likely present on the host.']</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -13761,8 +12626,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>The following is a list of supported SSL ciphers. 
-Note: If a cipher is included in this list it means that it was possible to establish a SSL connection using that cipher. There are some web servers setups that allow connections to be established using a LOW grade cipher, only to provide a web page stating that the URL is accessible only through a non-LOW grade cipher. In this case even though LOW grade cipher will be listed here QID 38140 will not be reported.</t>
+          <t>['The following is a list of supported SSL ciphers. Note: If a cipher is included in this list it means that it was possible to establish a SSL connection using that cipher. There are some web servers setups that allow connections to be established using a LOW grade cipher, only to provide a web page stating that the URL is accessible only through a non-LOW grade cipher. In this case even though LOW grade cipher will be listed here QID 38140 will not be reported.']</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -13808,14 +12672,13 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SSL session is a collection of security parameters that are negotiated by the SSL client and server for each SSL connection. SSL session caching is targeted to reduce the overhead of negotiations in recurring SSL connections. SSL sessions can be reused to resume an earlier connection or to establish multiple simultaneous connections. The client suggests an SSL session to be reused by identifying the session with a Session-ID during SSL handshake. If the server finds it appropriate to reuse the session,  then they both proceed to secure communication with already known security parameters.
-This test determines if SSL session caching is enabled on the host.</t>
+          <t>['SSL session is a collection of security parameters that are negotiated by the SSL client and server for each SSL connection. SSL session caching is targeted to reduce the overhead of negotiations in recurring SSL connections. SSL sessions can be reused to resume an earlier connection or to establish multiple simultaneous connections. The client suggests an SSL session to be reused by identifying the session with a Session-ID during SSL handshake. If the server finds it appropriate to reuse the session, then they both proceed to secure communication with already known security parameters.', 'This test determines if SSL session caching is enabled on the host.']</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>SSL session caching is part of the SSL and TLS protocols and is not a security threat. The result of this test is for informational purposes only.</t>
+          <t>['SSL session caching is part of the SSL and TLS protocols and is not a security threat. The result of this test is for informational purposes only.']</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -13859,7 +12722,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SSL/TLS protocols have different version that can be supported by both the client and the server. This test attempts to send invalid protocol versions to the target in order to find out what is the target's behavior. The results section contains a table that indicates what was the target's response to each of our tests.</t>
+          <t>["SSL/TLS protocols have different version that can be supported by both the client and the server. This test attempts to send invalid protocol versions to the target in order to find out what is the target's behavior. The results section contains a table that indicates what was the target's response to each of our tests."]</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -13905,9 +12768,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Diffie-Hellman is a popular cryptographic algorithm used by SSL/TLS. 
-- For fixed primes: 1024 and below are considered unsafe.
-- For variable primes: 512 is unsafe. 768 is probably mostly safe, but might not be for long. 1024 and above are considered safe.</t>
+          <t>['Diffie-Hellman is a popular cryptographic algorithm used by SSL/TLS. - For fixed primes: 1024 and below are considered unsafe.', '- For variable primes: 512 is unsafe. 768 is probably mostly safe, but might not be for long. 1024 and above are considered safe.']</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -13953,7 +12814,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>The following is a list of SSL/TLS key exchange methods supported by the server, along with their respective key sizes, strengths and ciphers.</t>
+          <t>['The following is a list of SSL/TLS key exchange methods supported by the server, along with their respective key sizes, strengths and ciphers.']</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -13999,18 +12860,13 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>The following is a list of detected SSL/TLS protocol properties.</t>
+          <t>['The following is a list of detected SSL/TLS protocol properties.']</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Items include:  
- Extended Master Secret: indicates whether the extended_master_secret extension is supported or required by the server. This extension enhances security and is recommended. Applicable to TLSv1, TLSv1.1, TLSv1.2, DTLSv1, DTLSv1.2 
- Encrypt Then MAC: indicates whether the encrypt_then_mac extension is supported or required by the server. This extension enhances the security of non-AEAD ciphers and is recommended. Applicable to TLSv1, TLSv1.1, TLSv1.2, DTLSv1, DTLSv1.2 
- Heartbeat: indicates whether the heartbeat extension is supported. It is not recommended to enable this, except for DTLS. Applicable to TLSv1, TLSv1.1, TLSv1.2, TLSv1.3, DTLSv1, DTLSv1.2 
- Truncated HMAC: indicates whether the truncated_hmac extension is supported. This can degrade security and is not recommended. Applicable to TLSv1, TLSv1.1, TLSv1.2, DTLSv1, DTLSv1.2 
- Cipher priority: indicates whether client, server or both determine the priority of ciphers. Having the server determine the priority is recommended. Applicable to SSLv3, TLSv1, TLSv1.1, TLSv1.2, TLSv1.3, DTLSv1, DTLSv1.2</t>
+          <t>['Items include: Extended Master Secret: indicates whether the extended_master_secret extension is supported or required by the server. This extension enhances security and is recommended. Applicable to TLSv1, TLSv1.1, TLSv1.2, DTLSv1, DTLSv1.2 Encrypt Then MAC: indicates whether the encrypt_then_mac extension is supported or required by the server. This extension enhances the security of non-AEAD ciphers and is recommended. Applicable to TLSv1, TLSv1.1, TLSv1.2, DTLSv1, DTLSv1.2 Heartbeat: indicates whether the heartbeat extension is supported. It is not recommended to enable this, except for DTLS. Applicable to TLSv1, TLSv1.1, TLSv1.2, TLSv1.3, DTLSv1, DTLSv1.2 Truncated HMAC: indicates whether the truncated_hmac extension is supported. This can degrade security and is not recommended. Applicable to TLSv1, TLSv1.1, TLSv1.2, DTLSv1, DTLSv1.2 Cipher priority: indicates whether client, server or both determine the priority of ciphers. Having the server determine the priority is recommended. Applicable to SSLv3, TLSv1, TLSv1.1, TLSv1.2, TLSv1.3, DTLSv1, DTLSv1.2']</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -14054,7 +12910,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Secure Socket Layer (SSL) and Transport Layer Security (TLS) renegotiation are vulnerable to an attack in which the attacker forms a TLS connection with the target server, injects content of his choice, and then splices in a new TLS connection from a client. The server treats the client's initial TLS handshake as a renegotiation and thus believes that the initial data transmitted by the attacker is from the same entity as the subsequent client data. TLS protocol was extended to cryptographically tierenegotiations to the TLS connections they are being performed over. This is referred to as TLS secure renegotiation extension. This detection determines whether the TLS secure renegotiation extension is supported by the server or not.</t>
+          <t>["Secure Socket Layer (SSL) and Transport Layer Security (TLS) renegotiation are vulnerable to an attack in which the attacker forms a TLS connection with the target server, injects content of his choice, and then splices in a new TLS connection from a client. The server treats the client's initial TLS handshake as a renegotiation and thus believes that the initial data transmitted by the attacker is from the same entity as the subsequent client data. TLS protocol was extended to cryptographically tierenegotiations to the TLS connections they are being performed over. This is referred to as TLS secure renegotiation extension. This detection determines whether the TLS secure renegotiation extension is supported by the server or not."]</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -14142,7 +12998,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SSL certificate information is provided in the Results section.</t>
+          <t>['SSL certificate information is provided in the Results section.']</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -14186,9 +13042,21 @@
           <t>HTTP Security Header Not Detected</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
-      <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>['This QID reports the absence of the following HTTP headers (https://www.owasp.org/index.php/OWASP_Secure_Headers_Projecttab=Headers) according to CWE-693: Protection Mechanism Failure (https://cwe.mitre.org/data/definitions/693.html):', 'X-Content-Type-Options: This HTTP header will prevent the browser from interpreting files as a different MIME type to what is specified in the Content-Type HTTP header. Strict-Transport-Security: The HTTP Strict-Transport-Security response header (HSTS) allows web servers to declare that web browsers (or other complying user agents) should only interact with it using secure HTTPS connections, and never via the insecure HTTP protocol.']</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>['Note: To better debug the results of this QID, it is requested that customers execute commands to simulate the following functionality: curl -lkL --verbose. CWE-693: Protection Mechanism Failure mentions the following - The product does not use or incorrectly uses a protection mechanism that provides sufficient defense against directed attacks against the product. A "missing" protection mechanism occurs when the application does not define any mechanism against a certain class of attack. An "insufficient" protection mechanism might provide some defenses - for example, against the most common attacks - but it does not protect against everything that is intended. Finally, an "ignored" mechanism occurs when a mechanism is available and in active use within the product, but the developer has not applied it in some code path. Customers are advised to set proper X-Content-Type-Options (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/X-Content-Type-Options) and Strict-Transport-Security (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Strict-Transport-Security) HTTP response headers. Depending on their server software, customers can set directives in their site configuration or Web.config files. Few examples are: X-Content-Type-Options: Apache: Header always set X-Content-Type-Options: nosniff HTTP Strict-Transport-Security: Apache: Header always set Strict-Transport-Security "max-age=31536000; includeSubDomains" Nginx: add_header Strict-Transport-Security max-age=31536000; Note: Network devices that include a HTTP/HTTPS console for administrative/management purposes often do not include all/some of the security headers. This is a known issue and it is recommend to contact the vendor for a solution.']</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>['Depending on the vulnerability being exploited, an unauthenticated remote attacker could conduct cross-site scripting, clickjacking or MIME-type sniffing attacks.']</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
@@ -14272,7 +13140,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.</t>
+          <t>['This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.']</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -14318,7 +13186,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -14358,8 +13226,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -14399,7 +13266,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -14439,7 +13306,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -14479,18 +13346,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -14528,14 +13394,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -14575,7 +13434,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -14615,8 +13474,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -14656,7 +13514,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server.</t>
+          <t>['The Result section displays the default Web page for the Web server.']</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -14702,7 +13560,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server following HTTP redirections.</t>
+          <t>['The Result section displays the default Web page for the Web server following HTTP redirections.']</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -14748,9 +13606,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request.  
-QID Detection Logic: 
-This QID returns the HTTP response method and header information returned by a web server.</t>
+          <t>["This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request. QID Detection Logic: This QID returns the HTTP response method and header information returned by a web server."]</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -14796,27 +13652,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
-1) no-referrer 
-2) no-referrer-when-downgrade 
-3) same-origin 
-4) origin 
-5) origin-when-cross-origin 
-6) strict-origin 
-7) strict-origin-when-cross-origin  </t>
+          <t>['No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 1) no-referrer 2) no-referrer-when-downgrade 3) same-origin 4) origin 5) origin-when-cross-origin 6) strict-origin 7) strict-origin-when-cross-origin']</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Referrer Policy header improves security by ensuring websites don't leak sensitive information via the referrer header. It's recommended to add secure Referrer Policies as a part of a defense-in-depth approach. 
-References: 
-- https://www.w3.org/TR/referrer-policy/ (https://www.w3.org/TR/referrer-policy/) 
-- https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy)</t>
+          <t>["Referrer Policy header improves security by ensuring websites don't leak sensitive information via the referrer header. It's recommended to add secure Referrer Policies as a part of a defense-in-depth approach.", 'References: - https://www.w3.org/TR/referrer-policy/ (https://www.w3.org/TR/referrer-policy/) - https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy)']</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>The Referrer-Policy header controls how much referrer information is sent to a site when navigating to it. Absence of Referrer-Policy header can lead to leakage of sensitive information via the referrer header.</t>
+          <t>['The Referrer-Policy header controls how much referrer information is sent to a site when navigating to it. Absence of Referrer-Policy header can lead to leakage of sensitive information via the referrer header.']</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -14860,14 +13706,13 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.
-The target Web server was found to support this functionality of the HTTP 1.1 protocol.</t>
+          <t>['Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.', 'The target Web server was found to support this functionality of the HTTP 1.1 protocol.']</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.</t>
+          <t>['Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.']</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -14911,7 +13756,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Based largely on the HTTP reply code, the following directories are most likely present on the host.</t>
+          <t>['Based largely on the HTTP reply code, the following directories are most likely present on the host.']</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -14957,7 +13802,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.</t>
+          <t>['This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.']</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -15003,7 +13848,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -15043,8 +13888,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -15084,7 +13928,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -15124,7 +13968,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -15164,18 +14008,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -15213,14 +14056,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -15260,7 +14096,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -15300,8 +14136,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -15341,7 +14176,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server.</t>
+          <t>['The Result section displays the default Web page for the Web server.']</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -15387,7 +14222,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server following HTTP redirections.</t>
+          <t>['The Result section displays the default Web page for the Web server following HTTP redirections.']</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -15433,9 +14268,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request.  
-QID Detection Logic: 
-This QID returns the HTTP response method and header information returned by a web server.</t>
+          <t>["This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request. QID Detection Logic: This QID returns the HTTP response method and header information returned by a web server."]</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -15481,14 +14314,13 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.
-The target Web server was found to support this functionality of the HTTP 1.1 protocol.</t>
+          <t>['Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.', 'The target Web server was found to support this functionality of the HTTP 1.1 protocol.']</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.</t>
+          <t>['Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.']</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -15532,22 +14364,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Several different techniques can be used to identify the operating system (OS) running on a host. A short description of these techniques is provided below. The specific technique used to identify the OS on this host is included in the RESULTS section of your report.
-1)  TCP/IP Fingerprint : The operating system of a host can be identified from a remote system using TCP/IP fingerprinting. All underlying operating system TCP/IP stacks have subtle differences that can be seen in their responses to specially-crafted TCP packets. According to the results of this "fingerprinting" technique, the OS version is among those listed below. 
-Note that if one or more of these subtle differences are modified by a firewall or a packet filtering device between the scanner and the host, the fingerprinting technique may fail. Consequently, the version of the OS may not be detected correctly. If the host is behind a proxy-type firewall, the version of the operating system detected may be that of the firewall instead of the host being scanned.
-2)  NetBIOS : Short for Network Basic Input Output System, an application programming interface (API) that augments the DOS BIOS by adding special functions for local-area networks (LANs). Almost all LANs for PCs are based on the NetBIOS. Some LAN manufacturers have even extended it, adding additional network capabilities. NetBIOS relies on a message format called Server Message Block (SMB). 
-3)  PHP Info : PHP is a hypertext pre-processor, an open-source, server-side, HTML-embedded scripting language used to create dynamic Web pages. Under some configurations it is possible to call PHP functions like phpinfo() and obtain operating system information.
-4)  SNMP : The Simple Network Monitoring Protocol is used to monitor hosts, routers, and the networks to which they attach. The SNMP service maintains Management Information Base (MIB), a set of variables (database) that can be fetched by Managers. These include "MIB_II.system.sysDescr" for the operating system.</t>
+          <t>['Several different techniques can be used to identify the operating system (OS) running on a host. A short description of these techniques is provided below. The specific technique used to identify the OS on this host is included in the RESULTS section of your report.', '1) TCP/IP Fingerprint : The operating system of a host can be identified from a remote system using TCP/IP fingerprinting. All underlying operating system TCP/IP stacks have subtle differences that can be seen in their responses to specially-crafted TCP packets. According to the results of this "fingerprinting" technique, the OS version is among those listed below.', 'Note that if one or more of these subtle differences are modified by a firewall or a packet filtering device between the scanner and the host, the fingerprinting technique may fail. Consequently, the version of the OS may not be detected correctly. If the host is behind a proxy-type firewall, the version of the operating system detected may be that of the firewall instead of the host being scanned.', '2) NetBIOS : Short for Network Basic Input Output System, an application programming interface (API) that augments the DOS BIOS by adding special functions for local-area networks (LANs). Almost all LANs for PCs are based on the NetBIOS. Some LAN manufacturers have even extended it, adding additional network capabilities. NetBIOS relies on a message format called Server Message Block (SMB).', '3) PHP Info : PHP is a hypertext pre-processor, an open-source, server-side, HTML-embedded scripting language used to create dynamic Web pages. Under some configurations it is possible to call PHP functions like phpinfo() and obtain operating system information.', '4) SNMP : The Simple Network Monitoring Protocol is used to monitor hosts, routers, and the networks to which they attach. The SNMP service maintains Management Information Base (MIB), a set of variables (database) that can be fetched by Managers. These include "MIB_II.system.sysDescr" for the operating system.']</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Not  applicable.</t>
+          <t>['Not applicable.']</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Not  applicable.</t>
+          <t>['Not applicable.']</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -15585,7 +14412,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -15625,8 +14452,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -15666,7 +14492,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -15706,7 +14532,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -15746,9 +14572,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confluent is a fully managed Kafka service and enterprise stream processing platform.
-Mapping of Confluent Platform and Apache Kafka can be done using the 
- Mapping Confluent Platform/Apache Kafka  (https://docs.confluent.io/current/installation/versions-interoperability.html) </t>
+          <t>['Confluent is a fully managed Kafka service and enterprise stream processing platform. Mapping of Confluent Platform and Apache Kafka can be done using the Mapping Confluent Platform/Apache Kafka (https://docs.confluent.io/current/installation/versions-interoperability.html)']</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -15788,18 +14612,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -15837,14 +14660,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -15884,7 +14700,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -15924,8 +14740,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -15966,12 +14781,12 @@
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Workaround: Enable ACL on all the nodes</t>
+          <t>['Workaround: Enable ACL on all the nodes']</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>A remote attacker could exploit this to steal or modify sensitive information.</t>
+          <t>['A remote attacker could exploit this to steal or modify sensitive information.']</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -16015,19 +14830,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t xml:space="preserve">ZooKeeper is a centralized service for maintaining configuration information, naming, providing distributed synchronization, and providing group services. 
-Apache ZooKeeper 3.4.x has reached EOL and will be effective from 1st of June, 2020 
-Currently supported versions of Apache ZooKeeper are 3.6.x, 3.7.x and 3.8.x </t>
+          <t>['ZooKeeper is a centralized service for maintaining configuration information, naming, providing distributed synchronization, and providing group services.', 'Apache ZooKeeper 3.4.x has reached EOL and will be effective from 1st of June, 2020 Currently supported versions of Apache ZooKeeper are 3.6.x, 3.7.x and 3.8.x']</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to Apache ZooKeeper  (https://zookeeper.apache.org/releases.htmldownload) latest versions to remediate these vulnerabilities.</t>
+          <t>['Customers are advised to upgrade to Apache ZooKeeper (https://zookeeper.apache.org/releases.htmldownload) latest versions to remediate these vulnerabilities.']</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>The system is at high risk of exposure to security vulnerabilities. Since the vendor no longer provides updates, obsolete software is more vulnerable to attacks.</t>
+          <t>['The system is at high risk of exposure to security vulnerabilities. Since the vendor no longer provides updates, obsolete software is more vulnerable to attacks.']</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -16071,26 +14884,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache ZooKeeper is a centralized service for maintaining configuration information, naming, providing distributed synchronization, and providing group services. 
-CVE-2023-44981: Apache ZooKeeper is vulnerable to authorization bypass vulnerability. 
-Affected Versions: 
-Apache ZooKeeper 3.9.0 
-Apache ZooKeeper 3.8.0 through 3.8.2 
-Apache ZooKeeper 3.7.0 through 3.7.1 
-Apache ZooKeeper before 3.7.0 </t>
+          <t>['Apache ZooKeeper is a centralized service for maintaining configuration information, naming, providing distributed synchronization, and providing group services.', 'CVE-2023-44981: Apache ZooKeeper is vulnerable to authorization bypass vulnerability.', 'Affected Versions: Apache ZooKeeper 3.9.0 Apache ZooKeeper 3.8.0 through 3.8.2 Apache ZooKeeper 3.7.0 through 3.7.1 Apache ZooKeeper before 3.7.0']</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to Apache ZooKeeper  (https://zookeeper.apache.org/releases.htmldownload) latest versions to remediate these vulnerabilities.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache ZooKeeper Security Advisory (https://lists.apache.org/thread/wf0yrk84dg1942z1o74kd8nycg6pgm5b)</t>
+          <t>['Customers are advised to upgrade to Apache ZooKeeper (https://zookeeper.apache.org/releases.htmldownload) latest versions to remediate these vulnerabilities. Patch: Following are links for downloading patches to fix the vulnerabilities: Apache ZooKeeper Security Advisory (https://lists.apache.org/thread/wf0yrk84dg1942z1o74kd8nycg6pgm5b)']</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow attacker to access unauthorized cluster and data manipulation.</t>
+          <t>['Successful exploitation of this vulnerability may allow attacker to access unauthorized cluster and data manipulation.']</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -16138,7 +14942,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -16178,8 +14982,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -16219,7 +15022,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -16259,7 +15062,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -16299,7 +15102,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache ZooKeeper is essentially a centralized service for distributed systems to a hierarchical key-value store, which is used to provide a distributed configuration service, synchronization service, and naming registry for large distributed systems.  </t>
+          <t>['Apache ZooKeeper is essentially a centralized service for distributed systems to a hierarchical key-value store, which is used to provide a distributed configuration service, synchronization service, and naming registry for large distributed systems.']</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -16339,18 +15142,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -16388,14 +15190,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -16435,7 +15230,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -16475,8 +15270,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -16516,7 +15310,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -16556,8 +15350,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -16597,7 +15390,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -16637,14 +15430,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -16684,20 +15470,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>The secure cookie flag is an option that can be set by the application server when sending a new cookie to the user within an HTTP Response. The purpose of the secure flag is to prevent cookies from being observed by unauthorized parties due to the transmission of a the cookie in clear text. By setting the secure flag, the browser will prevent the transmission of a cookie over an unencrypted channel. 
-A cookie with the secure attribute was not detected in the scan. 
-QID Detection Logic: 
-This unauthenticated QID checks for the existence of the "secure" cookie flag.</t>
+          <t>['The secure cookie flag is an option that can be set by the application server when sending a new cookie to the user within an HTTP Response. The purpose of the secure flag is to prevent cookies from being observed by unauthorized parties due to the transmission of a the cookie in clear text. By setting the secure flag, the browser will prevent the transmission of a cookie over an unencrypted channel. A cookie with the secure attribute was not detected in the scan. QID Detection Logic: This unauthenticated QID checks for the existence of the "secure" cookie flag.']</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Apply the "secure" attribute to session cookies to ensure that they are sent via HTTPS only. More information about this flag can be found here: https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Set-Cookie.</t>
+          <t>['Apply the "secure" attribute to session cookies to ensure that they are sent via HTTPS only. More information about this flag can be found here: https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Set-Cookie.']</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Session cookies sent via HTTP expose users to sniffing attacks that could lead to user impersonation or account compromise.</t>
+          <t>['Session cookies sent via HTTP expose users to sniffing attacks that could lead to user impersonation or account compromise.']</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
@@ -16741,17 +15524,17 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>The scanner found PHP version information in the headers returned by the PHP-enabled target Web server. This likely means that the "expose_php" variable is set to "On" in the "php.ini" configuration file for the Web server.</t>
+          <t>['The scanner found PHP version information in the headers returned by the PHP-enabled target Web server. This likely means that the "expose_php" variable is set to "On" in the "php.ini" configuration file for the Web server.']</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Locate the "php.ini" configuration file on the target host and add this  setting to it: "expose_php=Off". Restart the Web server.</t>
+          <t>['Locate the "php.ini" configuration file on the target host and add this setting to it: "expose_php=Off". Restart the Web server.']</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>This allows remote users to easily know that PHP is installed on the Web server. It also provides version information of the PHP installation. This could aid an attacker in launching more targeted attacks in the future.</t>
+          <t>['This allows remote users to easily know that PHP is installed on the Web server. It also provides version information of the PHP installation. This could aid an attacker in launching more targeted attacks in the future.']</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -16795,16 +15578,19 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Affected Versions: 
-PHP 7.1.x versions</t>
+          <t>['PHP is a general purpose scripting language that is suited for web development and can be embedded in HTML.', 'PHP 7.1 series reached End of Life in its support cycle on 1 Dec 2019.', "Since there are no further bug fixes or security updates for PHP 7.1 series, it's highly recommended to migrate from version 5.6 to newer supported versions.", 'Affected Versions: PHP 7.1.x versions']</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP.</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>['Customers are advised to upgrade to the latest version of PHP.']</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>['The system is at high risk of being exposed to security vulnerabilities. Since the vendor no longer provides updates, obsolete software is more vulnerable to viruses and other attacks.']</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
@@ -16840,27 +15626,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
-CVE-2022-31630: In installed version of PHP, when using imageloadfont() function in gd extension, it is possible to supply a specially crafted font file, such as if the loaded font is used with imagechar() function, the read outside allocated buffer will be used. This can lead to crashes or disclosure of confidential information. 
-CVE-2022-37454: The Keccak XKCP SHA-3 reference implementation before fdc6fef has an integer overflow and resultant buffer overflow that allows attackers to execute arbitrary code or eliminate expected cryptographic properties.  
-Affected Versions: 
-PHP versions before 7.4.33 
-PHP versions 8.0.0 prior to 8.0.25 
-PHP versions 8.1.0 prior to 8.1.12 </t>
+          <t>['PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications.', 'CVE-2022-31630: In installed version of PHP, when using imageloadfont() function in gd extension, it is possible to supply a specially crafted font file, such as if the loaded font is used with imagechar() function, the read outside allocated buffer will be used. This can lead to crashes or disclosure of confidential information. CVE-2022-37454: The Keccak XKCP SHA-3 reference implementation before fdc6fef has an integer overflow and resultant buffer overflow that allows attackers to execute arbitrary code or eliminate expected cryptographic properties.', 'Affected Versions: PHP versions before 7.4.33 PHP versions 8.0.0 prior to 8.0.25 PHP versions 8.1.0 prior to 8.1.12']</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) 
-For more information please refer to Sec Bug 81739 (https://bugs.php.net/bug.php?id=81739) . 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  81739 (https://bugs.php.net/bug.php?id=81739)  81738 (http://bugs.php.net/81738)</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) For more information please refer to Sec Bug 81739 (https://bugs.php.net/bug.php?id=81739) . Patch: Following are links for downloading patches to fix the vulnerabilities: 81739 (https://bugs.php.net/bug.php?id=81739) 81738 (http://bugs.php.net/81738)']</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Successful exploitation of the vulnerability may allow an attacker to crash the PHP process or Denial of Service (DoS) or tackers to execute arbitrary code on the system.</t>
+          <t>['Successful exploitation of the vulnerability may allow an attacker to crash the PHP process or Denial of Service (DoS) or tackers to execute arbitrary code on the system.']</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -16908,21 +15684,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PHP is a general purpose scripting language that is suited for web development and can be embedded in HTML.
- PHP 7.1 series reached End of Life in its support cycle on 1 Dec 2019.
- Since there are no further bug fixes or security updates for PHP 7.1 series, it's highly recommended to migrate from version 5.6 to newer supported versions.
- Affected Versions: 
-PHP 7.1.x versions</t>
+          <t>['PHP is a general purpose scripting language that is suited for web development and can be embedded in HTML.', 'PHP 7.1 series reached End of Life in its support cycle on 1 Dec 2019.', "Since there are no further bug fixes or security updates for PHP 7.1 series, it's highly recommended to migrate from version 5.6 to newer supported versions.", 'Affected Versions: PHP 7.1.x versions']</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP.</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP.']</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>The system is at high risk of being exposed to security vulnerabilities. Since the vendor no longer provides updates, obsolete software is more vulnerable to viruses and other attacks.</t>
+          <t>['The system is at high risk of being exposed to security vulnerabilities. Since the vendor no longer provides updates, obsolete software is more vulnerable to viruses and other attacks.']</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
@@ -16966,23 +15738,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache HTTP Server versions 2.4.53 and earlier  </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'Affected Versions: Apache HTTP Server versions 2.4.53 and earlier']</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html).
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache httpd (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache httpd (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Successful exploitation allows information disclosure and possible remote code execution</t>
+          <t>['Successful exploitation allows information disclosure and possible remote code execution']</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -17030,28 +15796,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2022-28330: Apache HTTP Server 2.4.53 and earlier on Windows may read beyond bounds when configured to process requests with the mod_isapi module. 
-CVE-2022-28614: The ap_rwrite() function in Apache HTTP Server 2.4.53 and earlier may read unintended memory if an attacker can cause the server to reflect very large input using ap_rwrite() or ap_rputs(), such as with mod_luas r:puts() function. 
-CVE-2022-28615: Apache HTTP Server 2.4.53 and earlier may crash or disclose information due to a read beyond bounds in ap_strcmp_match() when provided with an extremely large input buffer. 
-CVE-2022-29404: In Apache HTTP Server 2.4.53 and earlier, a malicious request to a lua script that calls r:parsebody(0) may cause a denial of service due to no default limit on possible input size. 
-CVE-2022-30556: Apache HTTP Server 2.4.53 and earlier may return lengths to applications calling r:wsread() that point past the end of the storage allocated for the buffer. 
-Affected Versions: 
-Apache HTTP Server versions 2.4.53 and earlier  </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2022-28330: Apache HTTP Server 2.4.53 and earlier on Windows may read beyond bounds when configured to process requests with the mod_isapi module. CVE-2022-28614: The ap_rwrite() function in Apache HTTP Server 2.4.53 and earlier may read unintended memory if an attacker can cause the server to reflect very large input using ap_rwrite() or ap_rputs(), such as with mod_luas r:puts() function. CVE-2022-28615: Apache HTTP Server 2.4.53 and earlier may crash or disclose information due to a read beyond bounds in ap_strcmp_match() when provided with an extremely large input buffer. CVE-2022-29404: In Apache HTTP Server 2.4.53 and earlier, a malicious request to a lua script that calls r:parsebody(0) may cause a denial of service due to no default limit on possible input size. CVE-2022-30556: Apache HTTP Server 2.4.53 and earlier may return lengths to applications calling r:wsread() that point past the end of the storage allocated for the buffer.', 'Affected Versions: Apache HTTP Server versions 2.4.53 and earlier']</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise Confidentiality, Integrity, and Availability of the Data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise Confidentiality, Integrity, and Availability of the Data.']</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -17099,22 +15854,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t xml:space="preserve">In Apache HTTP Server 2.4 releases 2.4.17 to 2.4.38, with MPM event, worker or prefork, code executing in less-privileged child processes or threads (including scripts executed by an in-process scripting interpreter) could execute arbitrary code with the privileges of the parent process (usually root) by manipulating the scoreboard. Non-Unix systems are not affected.
- Affected Versions: 
-2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.30, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17 </t>
+          <t>['In Apache HTTP Server 2.4 releases 2.4.17 to 2.4.38, with MPM event, worker or prefork, code executing in less-privileged child processes or threads (including scripts executed by an in-process scripting interpreter) could execute arbitrary code with the privileges of the parent process (usually root) by manipulating the scoreboard. Non-Unix systems are not affected. Affected Versions: 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.30, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17']</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>This vulnerability have been patched in Apache. Refer to  Apache httpd 2.4.39 Changelog (https://httpd.apache.org/security/vulnerabilities_24.html) or your Linux distro for further details. 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache httpd 2.4.39 (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['This vulnerability have been patched in Apache. Refer to Apache httpd 2.4.39 Changelog (https://httpd.apache.org/security/vulnerabilities_24.html) or your Linux distro for further details. Patch: Following are links for downloading patches to fix the vulnerabilities: Apache httpd 2.4.39 (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Successful exploitation allows a remote attacker to use this vulnerability to execute arbitrary code with the privileges of the parent process.</t>
+          <t>['Successful exploitation allows a remote attacker to use this vulnerability to execute arbitrary code with the privileges of the parent process.']</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -17154,9 +15904,21 @@
           <t>PHP 7 Remote Code Execution Vulnerability</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr"/>
-      <c r="C305" t="inlineStr"/>
-      <c r="D305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>["PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. PHP 7 is exposed to a remote code execution vulnerability due to a underflow issue in the 'env_path_info' in PHP-FPM. Affected Versions: PHP 7 versions 7.3.x before 7.3.11, 7.2.x before 7.2.24, and 7.1.x before 7.1.33."]</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>['Customers are advised to upgrade to the latest version of PHP (http://www.php.net/). For more information please visit the advisories. Patch: Following are links for downloading patches to fix the vulnerabilities: php download (http://php.net/downloads.php)']</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>['Successful exploitation of this vulnerability allows a remote attacker to execute arbitrary code on vulnerable server.']</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>['CVE-2019-11043']</t>
@@ -17202,28 +15964,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.46. 
- NOTE:  
-CVE-2021-26691, CVE-2021-26690, CVE-2020-35452, CVE-2020-13938 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6, 2.4.4, 2.4.3, 2.4.2, 2.4.1, 2.4.0. 
-CVE-2019-17567 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6 
-CVE-2021-30641 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39 
-CVE-2020-13950 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'Affected Versions: Apache HTTP Server versions prior to 2.4.46.', 'NOTE: CVE-2021-26691, CVE-2021-26690, CVE-2020-35452, CVE-2020-13938 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6, 2.4.4, 2.4.3, 2.4.2, 2.4.1, 2.4.0. CVE-2019-17567 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39, 2.4.38, 2.4.37, 2.4.35, 2.4.34, 2.4.33, 2.4.29, 2.4.28, 2.4.27, 2.4.26, 2.4.25, 2.4.23, 2.4.20, 2.4.18, 2.4.17, 2.4.16, 2.4.12, 2.4.10, 2.4.9, 2.4.7, 2.4.6 CVE-2021-30641 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41, 2.4.39 CVE-2020-13950 affects to Apache HTTP Server versions 2.4.46, 2.4.43, 2.4.41']</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Customers are advised to update Apache httpd 2.4.48. 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html).
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server 2.4.47 (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update Apache httpd 2.4.48. For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server 2.4.47 (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an attacker to execute arbitrary code on the target.</t>
+          <t>['Successful exploitation of this vulnerability may allow an attacker to execute arbitrary code on the target.']</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -17271,22 +16022,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-Affected Versions: 
-Apache HTTP Server 2.4.48 and earlier </t>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'Affected Versions: Apache HTTP Server 2.4.48 and earlier']</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an attacker to execute arbitrary code on the target.</t>
+          <t>['Successful exploitation of this vulnerability may allow an attacker to execute arbitrary code on the target.']</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -17332,16 +16078,21 @@
           <t>Apache Hypertext Transfer Protocol (HTTP) Server Buffer Overflow Vulnerability</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'A carefully crafted request body can cause a buffer overflow in the mod_lua multipart parser (r:parsebody() called from Lua scripts).', 'Affected Versions: Apache HTTP Server 2.4.51 and earlier']</t>
+        </is>
+      </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.52 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr"/>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.52 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>['Successful exploitation of the vulnerability may allow remote code execution and complete system compromise.&lt;/P&gt;']</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>['CVE-2021-44790']</t>
@@ -17387,23 +16138,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-A crafted URI sent to httpd configured as a forward proxy (ProxyRequests on) can cause a crash (NULL pointer dereference) or, for configurations mixing forward and reverse proxy declarations, can allow for requests to be directed to a declared Unix Domain Socket endpoint (Server Side Request Forgery). 
-Affected Versions: 
-Apache HTTP Server 2.4.7 - 2.4.51 </t>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'A crafted URI sent to httpd configured as a forward proxy (ProxyRequests on) can cause a crash (NULL pointer dereference) or, for configurations mixing forward and reverse proxy declarations, can allow for requests to be directed to a declared Unix Domain Socket endpoint (Server Side Request Forgery).', 'Affected Versions: Apache HTTP Server 2.4.7 - 2.4.51']</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.52 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.52 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Successful exploitation of the vulnerability may allow an attacker to redirect victim to a malicious server.&lt;/P&gt;</t>
+          <t>['Successful exploitation of the vulnerability may allow an attacker to redirect victim to a malicious server.&lt;/P&gt;']</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -17451,26 +16196,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-CVE-2022-22719 - A carefully crafted request body can cause a read to a random memory area which could cause the process to crash.  
-CVE-2022-22720 - Apache HTTP Server 2.4.52 and earlier fails to close inbound connection when errors are encountered discarding the request body, exposing the server to HTTP Request Smuggling  
-CVE-2022-22721 - If LimitXMLRequestBody is set to allow request bodies larger than 350MB (defaults to 1M) on 32 bit systems an integer overflow happens which later causes out of bounds writes. 
-CVE-2022-23943 - Out-of-bounds Write vulnerability in mod_sed of Apache HTTP Server allows an attacker to overwrite heap memory with possibly attacker provided data. 
-Affected Versions: 
-Apache HTTP Server 2.4 - 2.4.52</t>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'CVE-2022-22719 - A carefully crafted request body can cause a read to a random memory area which could cause the process to crash. CVE-2022-22720 - Apache HTTP Server 2.4.52 and earlier fails to close inbound connection when errors are encountered discarding the request body, exposing the server to HTTP Request Smuggling CVE-2022-22721 - If LimitXMLRequestBody is set to allow request bodies larger than 350MB (defaults to 1M) on 32 bit systems an integer overflow happens which later causes out of bounds writes. CVE-2022-23943 - Out-of-bounds Write vulnerability in mod_sed of Apache HTTP Server allows an attacker to overwrite heap memory with possibly attacker provided data.', 'Affected Versions: Apache HTTP Server 2.4 - 2.4.52']</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.53 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.53 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Successful exploitation of the vulnerability may allow an attacker to redirect victim to a malicious server.</t>
+          <t>['Successful exploitation of the vulnerability may allow an attacker to redirect victim to a malicious server.']</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -17518,23 +16254,17 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Some mod_proxy configurations on Apache HTTP Server versions 2.4.0 through 2.4.55 allow a HTTP Request Smuggling attack. 
-Configurations are affected when mod_proxy is enabled along with some form of RewriteRule or ProxyPassMatch in which a non-specific pattern matches some portion of the user-supplied request-target (URL) data and is then re-inserted into the proxied request-target using variable substitution.  
-Affected Versions: 
-Apache HTTP Server Versions 2.4.0 through 2.4.55 (including) </t>
+          <t>['Some mod_proxy configurations on Apache HTTP Server versions 2.4.0 through 2.4.55 allow a HTTP Request Smuggling attack. Configurations are affected when mod_proxy is enabled along with some form of RewriteRule or ProxyPassMatch in which a non-specific pattern matches some portion of the user-supplied request-target (URL) data and is then re-inserted into the proxied request-target using variable substitution.', 'Affected Versions: Apache HTTP Server Versions 2.4.0 through 2.4.55 (including)']</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to Apache HTTP Server version 2.4.56 or later. For more information please refer to  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56)
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56)</t>
+          <t>['Customers are advised to upgrade to Apache HTTP Server version 2.4.56 or later. For more information please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56)']</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Request splitting/smuggling could result in bypass of access controls in the proxy server, proxying unintended URLs to existing origin servers, and cache poisoning.</t>
+          <t>['Request splitting/smuggling could result in bypass of access controls in the proxy server, proxying unintended URLs to existing origin servers, and cache poisoning.']</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -17582,23 +16312,17 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.55 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2006-20001: A carefully crafted If: request header can cause a memory read, or write of a single zero byte, in a pool (heap) memory location beyond the header value sent. This could cause the process to crash. CVE-2022-37436: A malicious backend can cause the response headers to be truncated early, resulting in some headers being incorporated into the response body. If the later headers have any security purpose, they will not be interpreted by the client.', 'Affected Versions: Apache HTTP Server versions prior to 2.4.55']</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Customers are advised to update the latest Apache HTTP Server versions 2.4.55 or later. 
-For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update the latest Apache HTTP Server versions 2.4.55 or later. For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.</t>
+          <t>['Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.']</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -17646,23 +16370,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.58 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2023-31122: Out-of-bounds Read vulnerability in mod_macro of Apache HTTP Server.This issue affects Apache HTTP Server CVE-2023-45802: A client could send new requests and resets, keeping the connection busy and open and causing the memory footprint to keep on growing. On connection close, all resources were reclaimed, but the process might run out of memory before that.', 'Affected Versions: Apache HTTP Server versions prior to 2.4.58']</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Customers are advised to update the latest Apache HTTP Server versions 2.4.58 or later. 
-For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update the latest Apache HTTP Server versions 2.4.58 or later. For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.</t>
+          <t>['Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.']</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -17710,24 +16428,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2022-36760: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to.  
-Affected Versions: 
-Apache HTTP Server from 2.4 through 2.4.54  </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', "CVE-2022-36760: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to.", 'Affected Versions: Apache HTTP Server from 2.4 through 2.4.54']</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Customers are advised to update the latest Apache HTTP Server versions 2.4.55 or later. 
-For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update the latest Apache HTTP Server versions 2.4.55 or later. For further information, please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability allows an attacker to smuggle requests to the AJP server it forwards requests.</t>
+          <t>['Successful exploitation of this vulnerability allows an attacker to smuggle requests to the AJP server it forwards requests.']</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -17775,24 +16486,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2022-26377: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to. 
-Affected Versions: 
-Apache HTTP Server versions 2.4 to 2.4.53  </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', "CVE-2022-26377: Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') vulnerability in mod_proxy_ajp of Apache HTTP Server allows an attacker to smuggle requests to the AJP server it forwards requests to.", 'Affected Versions: Apache HTTP Server versions 2.4 to 2.4.53']</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allows an attacker to smuggle requests to the AJP server it forwards requests to.</t>
+          <t>['Successful exploitation of this vulnerability may allows an attacker to smuggle requests to the AJP server it forwards requests to.']</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -17840,23 +16544,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.60 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-38472: SSRF in Apache HTTP Server on Windows allows to potentially leak NTML hashes to a malicious server via SSRF and malicious requests or content CVE-2024-38473: Apache HTTP Server proxy encoding problem CVE-2024-38474: Apache HTTP Server weakness with encoded question marks in backreferences CVE-2024-38475: Apache HTTP Server weakness in mod_rewrite when first segment of substitution matches filesystem path. CVE-2024-38476: Apache HTTP Server may use exploitable/malicious backend application output to run local handlers via internal redirect CVE-2024-38477: Apache HTTP Server Crash resulting in Denial of Service in mod_proxy via a malicious request CVE-2024-39573: Apache HTTP Server mod_rewrite proxy handler substitution', 'Affected Versions: Apache HTTP Server versions prior to 2.4.60']</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information, visit here (https://httpd.apache.org/download.cgi). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/download.cgi)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information, visit here (https://httpd.apache.org/download.cgi). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/download.cgi)']</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise Confidentiality, Integrity, and Availability of the Data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise Confidentiality, Integrity, and Availability of the Data.']</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -17904,24 +16602,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-47252:  Apache HTTP Server: mod_ssl error log variable escaping 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-47252: Apache HTTP Server: mod_ssl error log variable escaping', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -17969,23 +16660,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29169: Apache HTTP Server: mod_dav_lock indirect lock crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -18033,23 +16718,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34059: Apache HTTP Server: mod_proxy_ajp: Heap Over-Read and memory disclosure in ajp_parse_data()', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -18097,38 +16776,17 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>TCP provides stateful communications between hosts on a network. TCP sessions are established by a three-way handshake and use random 32-bit sequence and acknowledgement numbers to ensure the validity of traffic. A vulnerability was reported that may permit TCP sequence numbers to be more easily approximated by remote attackers. This issue affects products released by multiple vendors.  
-The cause of the vulnerability is that affected implementations will accept TCP sequence numbers within a certain range, known as the acknowledgement range, of the expected sequence number for a packet in the session. This is determined by the TCP window size, which is negotiated during the three-way handshake for the session. Larger TCP window sizes may be set to allow for more throughput, but the larger the TCP window size, the more probable it is to guess a TCP sequence number that falls within an acceptable range. It was initially thought that guessing an acceptable sequence number was relatively difficult for most implementations given random distribution, making this type of attack impractical. However, some implementations may make it easier to successfully approximate an acceptable TCP sequence number, making these attacks possible with a number of protocols and implementations.
-This is further compounded by the fact that some implementations may support the use of the TCP Window Scale Option, as described in RFC 1323, to extend the TCP window size to a maximum value of 1 billion.
-This vulnerability will permit a remote attacker to inject a SYN or RST packet into the session, causing it to be reset and effectively allowing for denial of service attacks. An attacker would exploit this issue by sending a packet to a receiving implementation with an approximated sequence number and a forged source IP address and TCP port.
-There are a few factors that may present viable target implementations, such as those which depend on long-lived TCP connections, those that have known or easily guessed IP address endpoints and those implementations with easily guessed TCP source ports. It has been noted that Border Gateway Protocol (BGP) is reported to be particularly vulnerable to this type of attack, due to the use of long-lived TCP sessions and the possibility that some implementations may use the TCP Window Scale Option. As a result, this issue is likely to affect a number of routing platforms.
-Another factor to consider is the relative difficulty of injecting packets into TCP sessions, as a number of receiving implementations will reassemble packets in order, dropping any duplicates. This may make some implementations more resistant to attacks than others.
-It should be noted that while a number of vendors have confirmed this issue in various products, investigations are ongoing and it is likely that many other vendors and products will turn out to be vulnerable as the issue is investigated further.</t>
+          <t>['TCP provides stateful communications between hosts on a network. TCP sessions are established by a three-way handshake and use random 32-bit sequence and acknowledgement numbers to ensure the validity of traffic. A vulnerability was reported that may permit TCP sequence numbers to be more easily approximated by remote attackers. This issue affects products released by multiple vendors.', 'The cause of the vulnerability is that affected implementations will accept TCP sequence numbers within a certain range, known as the acknowledgement range, of the expected sequence number for a packet in the session. This is determined by the TCP window size, which is negotiated during the three-way handshake for the session. Larger TCP window sizes may be set to allow for more throughput, but the larger the TCP window size, the more probable it is to guess a TCP sequence number that falls within an acceptable range. It was initially thought that guessing an acceptable sequence number was relatively difficult for most implementations given random distribution, making this type of attack impractical. However, some implementations may make it easier to successfully approximate an acceptable TCP sequence number, making these attacks possible with a number of protocols and implementations.', 'This is further compounded by the fact that some implementations may support the use of the TCP Window Scale Option, as described in RFC 1323, to extend the TCP window size to a maximum value of 1 billion.', 'This vulnerability will permit a remote attacker to inject a SYN or RST packet into the session, causing it to be reset and effectively allowing for denial of service attacks. An attacker would exploit this issue by sending a packet to a receiving implementation with an approximated sequence number and a forged source IP address and TCP port.', 'There are a few factors that may present viable target implementations, such as those which depend on long-lived TCP connections, those that have known or easily guessed IP address endpoints and those implementations with easily guessed TCP source ports. It has been noted that Border Gateway Protocol (BGP) is reported to be particularly vulnerable to this type of attack, due to the use of long-lived TCP sessions and the possibility that some implementations may use the TCP Window Scale Option. As a result, this issue is likely to affect a number of routing platforms.', 'Another factor to consider is the relative difficulty of injecting packets into TCP sessions, as a number of receiving implementations will reassemble packets in order, dropping any duplicates. This may make some implementations more resistant to attacks than others.', 'It should be noted that while a number of vendors have confirmed this issue in various products, investigations are ongoing and it is likely that many other vendors and products will turn out to be vulnerable as the issue is investigated further.']</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Please first check the results section below for the port number on which this vulnerability was detected. If that port number is known to be used for port-forwarding, then it is the backend host that is really vulnerable.
-Various implementations and products including Check Point, Cisco, Cray Inc, Hitachi, Internet Initiative Japan, Inc (IIJ), Juniper Networks, NEC and Yamaha are currently undergoing review. Contact the vendors to obtain more information about affected products and fixes. NISCC Advisory 236929 - Vulnerability Issues in TCP (http://packetstormsecurity.org/0404-advisories/246929.html) details the vendor patch status as of the time of the advisory, and identifies resolutions and workarounds.
-Refer to US-CERT Vulnerability Note VU415294 (http://www.kb.cert.org/vuls/id/415294) and OSVDB Article 4030 (http://osvdb.org/4030) to obtain a list of vendors affected by this issue and a note on resolutions (if any) provided by the vendor.
-For Microsoft: Refer to MS05-019 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2005/ms05-019) and MS06-064 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2006/ms06-064) for further details.
-For SGI IRIX: Refer to SGI Security Advisory 20040905-01-P (ftp://patches.sgi.com/support/free/security/advisories/20040905-01-P.asc)
-For SCO UnixWare 7.1.3 and 7.1.1: Refer to SCO Security Advisory SCOSA-2005.14 (ftp://ftp.sco.com/pub/updates/UnixWare/SCOSA-2005.14/SCOSA-2005.14.txt)
-For Solaris (Sun Microsystems): The vendor has acknowledged the vulnerability; however a patch is not available. Refer to Sun Microsystems, Inc. Information for VU415294 (http://www.kb.cert.org/vuls/id/JARL-5YGQAJ) to obtain additional details. Also, refer to TA04-111A (http://www.us-cert.gov/cas/techalerts/TA04-111A.html) for detailed mitigating strategies against these attacks.
-For NetBSD: Refer to NetBSD-SA2004-006 (ftp://ftp.netbsd.org/pub/NetBSD/security/advisories/NetBSD-SA2004-006.txt.asc)
-For Cisco: Refer to cisco-sa-20040420-tcp-ios.shtml (http://www.cisco.com/warp/public/707/cisco-sa-20040420-tcp-ios.shtml).
-For IBM : Refer to IBM-tcp-sequence-number-cve-2004-0230 (https://www.ibm.com/support/pages/tcp-sequence-number-approximation-based-denial-service-cve-2004-0230).
-For Red Hat Linux: There is no fix available : Refer to  (https://access.redhat.com/security/cve/cve-2004-0230).
-Workaround: The following BGP-specific workaround information has been provided.
-For BGP implementations that support it, the TCP MD5 Signature Option should be enabled. Passwords that the MD5 checksum is applied to should be set to strong values and changed on a regular basis.
-Secure BGP configuration instructions have been provided for Cisco and Juniper at these locations:
-Secure Cisco IOS BGP Template (http://www.cymru.com/Documents/secure-bgp-template.html)
-JUNOS Secure BGP Template (http://www.cymru.com/gillsr/documents/junos-bgp-template.pdf)</t>
+          <t>['Please first check the results section below for the port number on which this vulnerability was detected. If that port number is known to be used for port-forwarding, then it is the backend host that is really vulnerable.', 'Various implementations and products including Check Point, Cisco, Cray Inc, Hitachi, Internet Initiative Japan, Inc (IIJ), Juniper Networks, NEC and Yamaha are currently undergoing review. Contact the vendors to obtain more information about affected products and fixes. NISCC Advisory 236929 - Vulnerability Issues in TCP (http://packetstormsecurity.org/0404-advisories/246929.html) details the vendor patch status as of the time of the advisory, and identifies resolutions and workarounds.', 'Refer to US-CERT Vulnerability Note VU415294 (http://www.kb.cert.org/vuls/id/415294) and OSVDB Article 4030 (http://osvdb.org/4030) to obtain a list of vendors affected by this issue and a note on resolutions (if any) provided by the vendor.', 'For Microsoft: Refer to MS05-019 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2005/ms05-019) and MS06-064 (https://docs.microsoft.com/en-us/security-updates/securitybulletins/2006/ms06-064) for further details.', 'For SGI IRIX: Refer to SGI Security Advisory 20040905-01-P (ftp://patches.sgi.com/support/free/security/advisories/20040905-01-P.asc)', 'For SCO UnixWare 7.1.3 and 7.1.1: Refer to SCO Security Advisory SCOSA-2005.14 (ftp://ftp.sco.com/pub/updates/UnixWare/SCOSA-2005.14/SCOSA-2005.14.txt)', 'For Solaris (Sun Microsystems): The vendor has acknowledged the vulnerability; however a patch is not available. Refer to Sun Microsystems, Inc. Information for VU415294 (http://www.kb.cert.org/vuls/id/JARL-5YGQAJ) to obtain additional details. Also, refer to TA04-111A (http://www.us-cert.gov/cas/techalerts/TA04-111A.html) for detailed mitigating strategies against these attacks.', 'For NetBSD: Refer to NetBSD-SA2004-006 (ftp://ftp.netbsd.org/pub/NetBSD/security/advisories/NetBSD-SA2004-006.txt.asc)', 'For Cisco: Refer to cisco-sa-20040420-tcp-ios.shtml (http://www.cisco.com/warp/public/707/cisco-sa-20040420-tcp-ios.shtml).', 'For IBM : Refer to IBM-tcp-sequence-number-cve-2004-0230 (https://www.ibm.com/support/pages/tcp-sequence-number-approximation-based-denial-service-cve-2004-0230).', 'For Red Hat Linux: There is no fix available : Refer to (https://access.redhat.com/security/cve/cve-2004-0230).', 'Workaround: The following BGP-specific workaround information has been provided.', 'For BGP implementations that support it, the TCP MD5 Signature Option should be enabled. Passwords that the MD5 checksum is applied to should be set to strong values and changed on a regular basis.', 'Secure BGP configuration instructions have been provided for Cisco and Juniper at these locations:', 'Secure Cisco IOS BGP Template (http://www.cymru.com/Documents/secure-bgp-template.html)', 'JUNOS Secure BGP Template (http://www.cymru.com/gillsr/documents/junos-bgp-template.pdf)']</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Successful exploitation of this issue could lead to denial of service attacks on the TCP based services of target hosts.</t>
+          <t>['Successful exploitation of this issue could lead to denial of service attacks on the TCP based services of target hosts.']</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -18170,25 +16828,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application.
- CVE-2020-1934: In Apache HTTP Server, mod_proxy_ftp may use uninitialized memory when proxying to a malicious FTP server. 
- CVE-2020-1927: In Apache HTTP Server, redirects configured with mod_rewrite that were intended to be self-referential might be fooled by encoded newlines and redirect instead to an an unexpected URL within the request URL. 
- Affected Versions: 
-Apache httpd 2.4.0 to 2.4.41 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2020-1934: In Apache HTTP Server, mod_proxy_ftp may use uninitialized memory when proxying to a malicious FTP server. CVE-2020-1927: In Apache HTTP Server, redirects configured with mod_rewrite that were intended to be self-referential might be fooled by encoded newlines and redirect instead to an an unexpected URL within the request URL.', 'Affected Versions: Apache httpd 2.4.0 to 2.4.41']</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Customers are advised to update Apache httpd to 2.4.42 or later. 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html).
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache httpd 2.4.42 or later 2.4. (https://httpd.apache.org/download.cgi)</t>
+          <t>['Customers are advised to update Apache httpd to 2.4.42 or later. For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache httpd 2.4.42 or later 2.4. (https://httpd.apache.org/download.cgi)']</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>This vulnerability could be exploited to gain partial access to sensitive information. Malicious users could also use this vulnerability to change partial contents or configuration on the system</t>
+          <t>['This vulnerability could be exploited to gain partial access to sensitive information. Malicious users could also use this vulnerability to change partial contents or configuration on the system']</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -18236,22 +16886,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
-Affected Versions: 
-PHP versions before 7.2.16 </t>
+          <t>['PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML.', 'Affected Versions: PHP versions before 7.2.16']</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php)
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  php downloads (https://www.php.net/downloads)</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) Patch: Following are links for downloading patches to fix the vulnerabilities: php downloads (https://www.php.net/downloads)']</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Successful exploitation allows a remote unauthenticated attacker to disclose local files on hosts.</t>
+          <t>['Successful exploitation allows a remote unauthenticated attacker to disclose local files on hosts.']</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -18299,25 +16944,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML. 
-PHP is affected by multiple vulnerabilities. 
-Affected Versions: 
-PHP versions prior to 7.4.24 
-PHP versions 7.3.x prior to 7.3.31 
-PHP versions 8.0.x prior to 8.0.11 </t>
+          <t>['PHP is a general purpose scripting language that is especially suited for web development and can be embedded into HTML.', 'PHP is affected by multiple vulnerabilities.', 'Affected Versions: PHP versions prior to 7.4.24 PHP versions 7.3.x prior to 7.3.31 PHP versions 8.0.x prior to 8.0.11']</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php)
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PHP Changelog Version 7.4.24 (https://www.php.net/ChangeLog-7.phpPHP_7_4)  PHP Changelog Version 7.3.31 (https://www.php.net/ChangeLog-7.phpPHP_7_3)  PHP Changelog Version 8.0.11 (https://www.php.net/ChangeLog-8.php)</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) Patch: Following are links for downloading patches to fix the vulnerabilities: PHP Changelog Version 7.4.24 (https://www.php.net/ChangeLog-7.phpPHP_7_4) PHP Changelog Version 7.3.31 (https://www.php.net/ChangeLog-7.phpPHP_7_3) PHP Changelog Version 8.0.11 (https://www.php.net/ChangeLog-8.php)']</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an attacker to impact Confidentiality and Integrity.</t>
+          <t>['Successful exploitation of this vulnerability may allow an attacker to impact Confidentiality and Integrity.']</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -18365,28 +17002,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t xml:space="preserve">PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications. 
-Affected versions of PHP has multiple vulnerabilities: 
-CVE-2022-31628 : The vulnerability exists due to infinite loop within the phar uncompressor code when processing "quines" gzip files. A remote attacker can pass a specially crafted archive to the application, consume all available system resources and cause denial of service conditions. 
-CVE-2022-31629: The vulnerability exists due to the way PHP handles HTTP variable names. A remote attacker can set a standard insecure cookie in the victim's browser which is treated as a '__Host-' or '__Secure-' cookie by PHP applications. 
-Affected Versions: 
-PHP versions before 7.4.31 
-PHP versions 8.0.0 prior to 8.0.24 
-PHP versions 8.1.0 prior to 8.1.11 </t>
+          <t>['PHP is a programming language originally designed for use in web-based applications with HTML content. PHP supports a wide variety of platforms and is used by numerous web-based software applications.', 'Affected versions of PHP has multiple vulnerabilities: CVE-2022-31628 : The vulnerability exists due to infinite loop within the phar uncompressor code when processing "quines" gzip files. A remote attacker can pass a specially crafted archive to the application, consume all available system resources and cause denial of service conditions.', "CVE-2022-31629: The vulnerability exists due to the way PHP handles HTTP variable names. A remote attacker can set a standard insecure cookie in the victim's browser which is treated as a '__Host-' or '__Secure-' cookie by PHP applications.", 'Affected Versions: PHP versions before 7.4.31 PHP versions 8.0.0 prior to 8.0.24 PHP versions 8.1.0 prior to 8.1.11']</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) 
-For more information please refer to Sec Bug 81726 (https://bugs.php.net/bug.php?id=81726) and Sec Bug 81727 (https://bugs.php.net/bug.php?id=81727) . 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  81727 (https://bugs.php.net/bug.php?id=81727)  81726 (https://bugs.php.net/bug.php?id=81726)</t>
+          <t>['Customers are advised to upgrade to the latest version of PHP. (https://www.php.net/downloads.php) For more information please refer to Sec Bug 81726 (https://bugs.php.net/bug.php?id=81726) and Sec Bug 81727 (https://bugs.php.net/bug.php?id=81727) . Patch: Following are links for downloading patches to fix the vulnerabilities: 81727 (https://bugs.php.net/bug.php?id=81727) 81726 (https://bugs.php.net/bug.php?id=81726)']</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability allows a remote attacker to perform a denial of service (DoS) attack or bypass implemented security restrictions.</t>
+          <t>['Successful exploitation of this vulnerability allows a remote attacker to perform a denial of service (DoS) attack or bypass implemented security restrictions.']</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -18434,27 +17060,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>The Apache HTTP Server, commonly referred to as Apache is a freely available Web server.
-Apache is vulnerable to a denial of service due to holding a connection open for partial HTTP requests. 
-Apache Versions 1.x and 2.x are vulnerable.</t>
+          <t>['The Apache HTTP Server, commonly referred to as Apache is a freely available Web server.', 'Apache is vulnerable to a denial of service due to holding a connection open for partial HTTP requests.', 'Apache Versions 1.x and 2.x are vulnerable.']</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Patch - 
-There are no vendor-supplied patches available at this time.
-Workaround: - Server-specific recommendations can be found here (https://community.qualys.com/blogs/securitylabs/2011/11/02/how-to-protect-against-slow-http-attacks). 
-- Countermeasures for Apache are described here (http://httpd.apache.org/docs/trunk/misc/security_tips.htmldos). 
-- Reverse proxies, load balancers and iptables can help to prevent this attack from occurring. 
-- Adjusting the TimeOut Directive (http://httpd.apache.org/docs/2.2/mod/core.htmltimeout) can also prevent this attack from occurring. 
-- A new module mod_reqtimeout (http://httpd.apache.org/docs/2.2/mod/mod_reqtimeout.html) has been introduced since Apache 2.2.15 to provide tools for mitigation against these forms of attack.
-Also refer to Cert Blog (http://www.cert.org/blogs/certcc/2009/07/slowloris_vs_your_webserver.html) and Slowloris and Mitigations for Apache document (http://bedagainstthewall.blogspot.com/2011/01/slowloris-and-mitigations-for-apache.html) for further information.</t>
+          <t>['Patch - There are no vendor-supplied patches available at this time.', 'Workaround: - Server-specific recommendations can be found here (https://community.qualys.com/blogs/securitylabs/2011/11/02/how-to-protect-against-slow-http-attacks). - Countermeasures for Apache are described here (http://httpd.apache.org/docs/trunk/misc/security_tips.htmldos). - Reverse proxies, load balancers and iptables can help to prevent this attack from occurring. - Adjusting the TimeOut Directive (http://httpd.apache.org/docs/2.2/mod/core.htmltimeout) can also prevent this attack from occurring. - A new module mod_reqtimeout (http://httpd.apache.org/docs/2.2/mod/mod_reqtimeout.html) has been introduced since Apache 2.2.15 to provide tools for mitigation against these forms of attack.', 'Also refer to Cert Blog (http://www.cert.org/blogs/certcc/2009/07/slowloris_vs_your_webserver.html) and Slowloris and Mitigations for Apache document (http://bedagainstthewall.blogspot.com/2011/01/slowloris-and-mitigations-for-apache.html) for further information.']</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>A remote attacker can cause a denial of service against the Web server which would prevent legitimate users from accessing the site. 
-Denial of service tools and scripts such as Slowloris takes advantage of this vulnerability.</t>
+          <t>['A remote attacker can cause a denial of service against the Web server which would prevent legitimate users from accessing the site. Denial of service tools and scripts such as Slowloris takes advantage of this vulnerability.']</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -18500,18 +17116,19 @@
           <t>Apache Hypertext Transfer Protocol (HTTP) Server Response Smuggling Vulnerability</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>['HTTP Response Smuggling vulnerability in Apache HTTP Server via mod_proxy_uwsgi. Special characters in the origin response header can truncate/split the response forwarded to the client.', 'Affected Versions: This issue affects Apache HTTP Server: from 2.4.30 through 2.4.55']</t>
+        </is>
+      </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Customers are advised to upgrade to Apache HTTP Server version 2.4.56 or later. For more information please refer to  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56)
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56)</t>
+          <t>['Customers are advised to upgrade to Apache HTTP Server version 2.4.56 or later. For more information please refer to Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html2.4.56)']</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Successful exploitation of the vulnerability may result in integrity impact.</t>
+          <t>['Successful exploitation of the vulnerability may result in integrity impact.']</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -18559,25 +17176,17 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2023-38709: Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. 
-CVE-2024-24795: HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack.  
-Affected Versions: 
-Apache HTTP Server versions prior to 2.4.59 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2023-38709: Faulty input validation in the core of Apache allows malicious or exploitable backend/content generators to split HTTP responses. CVE-2024-24795: HTTP Response splitting in multiple modules in Apache HTTP Server allows an attacker that can inject malicious response headers into backend applications to cause an HTTP desynchronization attack.', 'Affected Versions: Apache HTTP Server versions prior to 2.4.59']</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Customers are advised to update the latest Apache versions respectively. 
-For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update the latest Apache versions respectively. For more information, visit here (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.</t>
+          <t>['Successful exploitation of this vulnerability may result in the breach of Confidentiality, Integrity, and Availability of data.']</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -18625,24 +17234,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-49812:  Apache HTTP Server: mod_ssl TLS upgrade attack 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-49812: Apache HTTP Server: mod_ssl TLS upgrade attack', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -18690,24 +17292,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-53020:  Apache HTTP Server: HTTP/2 DoS by Memory Increase 
-Affected Versions: 
-Apache httpd 2.4.17 through 2.4.63 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-53020: Apache HTTP Server: HTTP/2 DoS by Memory Increase', 'Affected Versions: Apache httpd 2.4.17 through 2.4.63']</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -18755,24 +17350,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2024-43394:  Apache HTTP Server: SSRF on Windows due to UNC paths 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-43394: Apache HTTP Server: SSRF on Windows due to UNC paths', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -18820,24 +17408,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-23048:  Apache HTTP Server: mod_ssl access control bypass with session resumption 
-Affected Versions: 
-Apache httpd 2.4.35 through 2.4.63 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-23048: Apache HTTP Server: mod_ssl access control bypass with session resumption', 'Affected Versions: Apache httpd 2.4.35 through 2.4.63']</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -18885,23 +17466,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-42516: Apache HTTP Server: HTTP response splitting', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -18949,23 +17524,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-59775: Apache HTTP Server: NTLM Leakage on Windows through UNC SSRF', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -19013,23 +17582,17 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-66200: Apache HTTP Server: mod_userdir+suexec bypass via AllowOverride FileInfo', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -19077,23 +17640,17 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-58098: Apache HTTP Server: Server Side Includes adds query string to exec cmd=...', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -19141,23 +17698,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33006: Apache HTTP Server: mod_auth_digest timing attack', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -19205,23 +17756,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-24072: Apache HTTP Server: mod_rewrite elevation of privileges via ap_expr', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -19269,24 +17814,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44119:  escalation of privilege through expressions in .htaccess in multiple modules 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44119: escalation of privilege through expressions in .htaccess in multiple modules', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -19334,24 +17872,17 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44186:  Loop in `proxy_ftp_handler` in mod_proxy_ftp 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44186: Loop in `proxy_ftp_handler` in mod_proxy_ftp', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -19399,24 +17930,17 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-49975:  mod_http2 denial of service 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-49975: mod_http2 denial of service', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -19464,23 +17988,17 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34355: mod_proxy_html buffer overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -19528,23 +18046,17 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-43951: OOB Read in `merge_response_headers` can cause crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -19592,23 +18104,17 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-42535: mod_dav_fs protected directory access', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -19656,23 +18162,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0. 
-A crafted method sent through HTTP/2 will bypass validation and be forwarded by mod_proxy, which can lead to request splitting or cache poisoning. 
-Affected Versions: 
-Apache HTTP Server 2.4.17 to 2.4.48. </t>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'A crafted method sent through HTTP/2 will bypass validation and be forwarded by mod_proxy, which can lead to request splitting or cache poisoning.', 'Affected Versions: Apache HTTP Server 2.4.17 to 2.4.48.']</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  NA (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: NA (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow request splitting or cache poisoning.</t>
+          <t>['Successful exploitation of this vulnerability may allow request splitting or cache poisoning.']</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -19718,18 +18218,19 @@
           <t>Apache Hypertext Transfer Protocol Server (HTTP Server) Denial of Service (DoS) Vulnerability</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>['Apache HTTP Server is a free and open-source cross-platform web server software, released under the terms of Apache License 2.0.', 'A carefully crafted request uri-path can cause mod_proxy_uwsgi to read above the allocated memory and crash (DoS).', 'Affected Versions: Apache HTTP Server versions 2.4.30 to 2.4.48.']</t>
+        </is>
+      </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  NA (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update to Apache HTTP Server 2.4.49 or later. For more information, check Apache Security Advisory (https://httpd.apache.org/security/vulnerabilities_24.html). Patch: Following are links for downloading patches to fix the vulnerabilities: NA (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may cause Denial of Service (DoS)</t>
+          <t>['Successful exploitation of this vulnerability may cause Denial of Service (DoS)']</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -19777,23 +18278,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.64 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2024-43204: Apache HTTP Server: SSRF with mod_headers setting Content-Type header', 'Affected Versions: Apache httpd 2.4.x before 2.4.64']</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -19841,23 +18336,17 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.26 through 2.4.63 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-49630: Apache HTTP Server: mod_proxy_http2 denial of service', 'Affected Versions: Apache httpd 2.4.26 through 2.4.63']</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -19905,24 +18394,17 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2025-65082:  Apache HTTP Server: CGI environment variable override 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-65082: Apache HTTP Server: CGI environment variable override', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -19970,23 +18452,17 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.66 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2025-55753: Apache HTTP Server: mod_md (ACME), unintended retry intervals', 'Affected Versions: Apache httpd 2.4.x before 2.4.66']</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -20034,24 +18510,17 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34032:  Apache HTTP Server: mod_proxy_ajp: Heap Buffer Over-Read Due to Missing Null-Termination Check (ajp_msg_get_string) 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34032: Apache HTTP Server: mod_proxy_ajp: Heap Buffer Over-Read Due to Missing Null-Termination Check (ajp_msg_get_string)', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -20099,24 +18568,17 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33007:  Apache HTTP Server: mod_authn_socache crash 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33007: Apache HTTP Server: mod_authn_socache crash', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -20164,24 +18626,17 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33857:  Apache HTTP Server: Off-by-one OOB reads in AJP getter functions 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33857: Apache HTTP Server: Off-by-one OOB reads in AJP getter functions', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -20229,24 +18684,17 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-33523:  Apache HTTP Server: multiple modules: HTTP response splitting forwarding malicious status line 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-33523: Apache HTTP Server: multiple modules: HTTP response splitting forwarding malicious status line', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -20294,24 +18742,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-28780:  Apache HTTP Server: buffer overflow in mod_proxy_ajp via  ajp_msg_check_header() 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-28780: Apache HTTP Server: buffer overflow in mod_proxy_ajp via ajp_msg_check_header()', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -20359,23 +18800,17 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.67 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29168: Apache HTTP Server: mod_md unrestricted OCSP response', 'Affected Versions: Apache httpd 2.4.x before 2.4.67']</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -20423,23 +18858,17 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29170: mod_proxy_ftp XSS', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -20487,23 +18916,17 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-29167: mod_ldap per-dir use-after-free', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -20551,23 +18974,17 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-42536: mod_xml2enc heap overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -20615,23 +19032,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44185: Stack Buffer Over-Read in mod_ssl OCSP `send_request`', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -20679,24 +19090,17 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-34356:  ProxyPassReverseCookieMap buffer overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-34356: ProxyPassReverseCookieMap buffer overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -20744,24 +19148,17 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apache HTTP Server is an HTTP web server application. 
-CVE-2026-44631:  Heap Underflow in `ap_regname` via Signed Char Overflow 
-Affected Versions: 
-Apache httpd 2.4.x before 2.4.68 </t>
+          <t>['Apache HTTP Server is an HTTP web server application.', 'CVE-2026-44631: Heap Underflow in `ap_regname` via Signed Char Overflow', 'Affected Versions: Apache httpd 2.4.x before 2.4.68']</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Customers are advised to update latest Apache httpd 
-For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) 
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)</t>
+          <t>['Customers are advised to update latest Apache httpd For more information please refer to Apachehttpserver (https://httpd.apache.org/security/vulnerabilities_24.html) Patch: Following are links for downloading patches to fix the vulnerabilities: Apache HTTP Server (https://httpd.apache.org/security/vulnerabilities_24.html)']</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.</t>
+          <t>['Successful exploitation of this vulnerability may compromise the confidentiality, integrity, or availability of the data.']</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -20851,7 +19248,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PHP is a general purpose scripting language that is especially suited for Web development and can be embedded in HTML.</t>
+          <t>['PHP is a general purpose scripting language that is especially suited for Web development and can be embedded in HTML.']</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
@@ -20891,55 +19288,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>The result section of this QID lists web applications and plugins that were detected on the target using web application fingerprinting. This technique compares static files at known locations against precomputed hashes for versions of those files in all available releases. The technique is fast, low-bandwidth, non-invasive, generic, and highly automatable.
- Following open source and free applications are currently supported:
- Joomla!
- MediaWiki
- WordPress
- phpBB
- MovableType
- Drupal
- osCommerce
- PHP-Nuke
- Moodle
- Liferay
- Tikiwiki
- Twiki
- phpmyadmin
- SPIP
- Confluence(free versions)
- Wikka
- Wacko
- Usemod
- e107
- Flyspray
- AppRain
- V-CMS
- AjaxPlorer/Pydio
- eFront Learning Management System
- vTigerCRM (Open source versions)
- MyBB
- WebCalendar
- PivotX WebLog
- DokuWiki
- MODX Revolution
- MODX Evolution
- Collabtive
- Achievo
- Magento 1.x CE
- iCE Hrm (Opensource Version)
- AdaptCMS
- ownCloud
- HumHub
- Redaxscript
- phpwcms
- Wolf CMS
- Pligg CMS
- Zen Cart
- Xoops
- TYPO3
- Microweber
- This QID is based on the Blind Elephant project (http://blindelephant.sourceforge.net/). For a complete list of supported web applications and plugins, please check the following link: DOC-5480 (https://community.qualys.com/docs/DOC-5480).</t>
+          <t>['The result section of this QID lists web applications and plugins that were detected on the target using web application fingerprinting. This technique compares static files at known locations against precomputed hashes for versions of those files in all available releases. The technique is fast, low-bandwidth, non-invasive, generic, and highly automatable. Following open source and free applications are currently supported: Joomla! MediaWiki WordPress phpBB MovableType Drupal osCommerce PHP-Nuke Moodle Liferay Tikiwiki Twiki phpmyadmin SPIP Confluence(free versions) Wikka Wacko Usemod e107 Flyspray AppRain V-CMS AjaxPlorer/Pydio eFront Learning Management System vTigerCRM (Open source versions) MyBB WebCalendar PivotX WebLog DokuWiki MODX Revolution MODX Evolution Collabtive Achievo Magento 1.x CE iCE Hrm (Opensource Version) AdaptCMS ownCloud HumHub Redaxscript phpwcms Wolf CMS Pligg CMS Zen Cart Xoops TYPO3 Microweber', 'This QID is based on the Blind Elephant project (http://blindelephant.sourceforge.net/). For a complete list of supported web applications and plugins, please check the following link: DOC-5480 (https://community.qualys.com/docs/DOC-5480).']</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -20985,7 +19334,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.</t>
+          <t>['This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.']</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
@@ -21031,7 +19380,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
@@ -21071,8 +19420,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
@@ -21112,7 +19460,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
@@ -21152,7 +19500,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards. </t>
+          <t>['The Apache HTTP Server Project is an effort to develop and maintain an open-source HTTP server for modern operating systems including UNIX and Windows. The goal of this project is to provide a secure, efficient and extensible server that provides HTTP services in sync with the current HTTP standards.']</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
@@ -21192,7 +19540,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
@@ -21232,18 +19580,17 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -21281,14 +19628,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -21328,7 +19668,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
@@ -21368,8 +19708,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
@@ -21409,7 +19748,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server.</t>
+          <t>['The Result section displays the default Web page for the Web server.']</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
@@ -21455,7 +19794,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server following HTTP redirections.</t>
+          <t>['The Result section displays the default Web page for the Web server following HTTP redirections.']</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
@@ -21501,9 +19840,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request.  
-QID Detection Logic: 
-This QID returns the HTTP response method and header information returned by a web server.</t>
+          <t>["This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request. QID Detection Logic: This QID returns the HTTP response method and header information returned by a web server."]</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
@@ -21549,27 +19886,17 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 
-1) no-referrer 
-2) no-referrer-when-downgrade 
-3) same-origin 
-4) origin 
-5) origin-when-cross-origin 
-6) strict-origin 
-7) strict-origin-when-cross-origin  </t>
+          <t>['No Referrer Policy is specified for the link. It checks for one of the following Referrer Policy in the response headers: 1) no-referrer 2) no-referrer-when-downgrade 3) same-origin 4) origin 5) origin-when-cross-origin 6) strict-origin 7) strict-origin-when-cross-origin']</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Referrer Policy header improves security by ensuring websites don't leak sensitive information via the referrer header. It's recommended to add secure Referrer Policies as a part of a defense-in-depth approach. 
-References: 
-- https://www.w3.org/TR/referrer-policy/ (https://www.w3.org/TR/referrer-policy/) 
-- https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy)</t>
+          <t>["Referrer Policy header improves security by ensuring websites don't leak sensitive information via the referrer header. It's recommended to add secure Referrer Policies as a part of a defense-in-depth approach.", 'References: - https://www.w3.org/TR/referrer-policy/ (https://www.w3.org/TR/referrer-policy/) - https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy (https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Referrer-Policy)']</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>The Referrer-Policy header controls how much referrer information is sent to a site when navigating to it. Absence of Referrer-Policy header can lead to leakage of sensitive information via the referrer header.</t>
+          <t>['The Referrer-Policy header controls how much referrer information is sent to a site when navigating to it. Absence of Referrer-Policy header can lead to leakage of sensitive information via the referrer header.']</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -21613,7 +19940,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>A web server is server software, or hardware dedicated to running this software, that can satisfy client requests on the World Wide Web.</t>
+          <t>['A web server is server software, or hardware dedicated to running this software, that can satisfy client requests on the World Wide Web.']</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
@@ -21659,7 +19986,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Based largely on the HTTP reply code, the following directories are most likely present on the host.</t>
+          <t>['Based largely on the HTTP reply code, the following directories are most likely present on the host.']</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
@@ -21705,26 +20032,17 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
-phpMyAdmin is prone to following vulnerabilities. 
-CVE-2018-19968:Local file inclusion through transformation feature 
-CVE-2018-19970:XSS vulnerability in navigation tree 
-Affected Versions: 
-phpMyAdmin versions from at least 4.0 through 4.8.3  </t>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.', 'phpMyAdmin is prone to following vulnerabilities. CVE-2018-19968:Local file inclusion through transformation feature CVE-2018-19970:XSS vulnerability in navigation tree', 'Affected Versions: phpMyAdmin versions from at least 4.0 through 4.8.3']</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Users are advised to upgrade to phpMyAdmin 4.8.4 or newer from phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php).
-For more information check PMASA-2018-6 (https://www.phpmyadmin.net/security/PMASA-2018-6/)and PMASA-2018-8 (https://www.phpmyadmin.net/security/PMASA-2018-8/)
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PMASA-2018-6 (https://www.phpmyadmin.net/security/PMASA-2018-6/)  PMASA-2018-8 (https://www.phpmyadmin.net/security/PMASA-2018-8/)</t>
+          <t>['Users are advised to upgrade to phpMyAdmin 4.8.4 or newer from phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php). For more information check PMASA-2018-6 (https://www.phpmyadmin.net/security/PMASA-2018-6/)and PMASA-2018-8 (https://www.phpmyadmin.net/security/PMASA-2018-8/) Patch: Following are links for downloading patches to fix the vulnerabilities: PMASA-2018-6 (https://www.phpmyadmin.net/security/PMASA-2018-6/) PMASA-2018-8 (https://www.phpmyadmin.net/security/PMASA-2018-8/)']</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an attacker to exploit phpMyAdmin to leak the contents of a local file, execute xss attacks.</t>
+          <t>['Successful exploitation of this vulnerability may allow an attacker to exploit phpMyAdmin to leak the contents of a local file, execute xss attacks.']</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -21772,21 +20090,17 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.&lt;/P&gt;  Phpmyadmin through 5.0.2 allows csv injection via export section.  Note: the vendor disputes this because "the csv file is accurately generated based on the database contents.  &lt;/P&gt; Affected versions 
-from 5.0.0.0 before 5.0.3.0 </t>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.&lt;/P&gt; Phpmyadmin through 5.0.2 allows csv injection via export section. Note: the vendor disputes this because "the csv file is accurately generated based on the database contents. &lt;/P&gt; Affected versions from 5.0.0.0 before 5.0.3.0']</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>For more information regarding these vulnerabilities, please refer to  phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php).for  latest versions to remediate this vulnerability.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  CVE-2020-22278 (https://mega.nz/file/ySQnlQSRvXzY46mgf0CE2ysYpWpbE4O6T_g37--rtaL8pqdHcQs)</t>
+          <t>['For more information regarding these vulnerabilities, please refer to phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php).for latest versions to remediate this vulnerability. Patch: Following are links for downloading patches to fix the vulnerabilities: CVE-2020-22278 (https://mega.nz/file/ySQnlQSRvXzY46mgf0CE2ysYpWpbE4O6T_g37--rtaL8pqdHcQs)']</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an authenticated attacker to execute arbitrary JavaScript code on the target system.</t>
+          <t>['Successful exploitation of this vulnerability may allow an authenticated attacker to execute arbitrary JavaScript code on the target system.']</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -21834,21 +20148,19 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
- Affected Versions: 
-phpMyAdmin versions prior to 4.8.2  </t>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.', 'Multiple vulnerabilities were reported in PhpMyAdmin CVE-2018-12581:A Cross-Site Scripting vulnerability has been found where an attacker can use a crafted database name to trigger an XSS attack when that database is referenced from the Designer feature. CVE-2018-12613: An issue was discovered in phpMyAdmin, in which an attacker can include (view and potentially execute) files on the server. The vulnerability comes from a portion of code where pages are redirected and loaded within phpMyAdmin, and an improper test for whitelisted pages. An attacker must be authenticated, except in the "$cfg[\'AllowArbitraryServer\'] = true" case (where an attacker can specify any host he/she is already in control of, and execute arbitrary code on phpMyAdmin) and the "$cfg[\'ServerDefault\'] = 0" case (which bypasses the login requirement and runs the vulnerable code without any authentication).', 'Affected Versions: phpMyAdmin versions prior to 4.8.2']</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Users are advised to upgrade to phpMyAdmin 4.8.2 or newer from phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php).
-For more information check PMASA-2018-3 (https://www.phpmyadmin.net/security/PMASA-2018-3/) and PMASA-2018-4 (https://www.phpmyadmin.net/security/PMASA-2018-4/).
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PMASA-2018-3: PhpMyAdmin (https://www.phpmyadmin.net/security/PMASA-2018-3/)  PMASA-2018-4: PhpMyAdmin (https://www.phpmyadmin.net/security/PMASA-2018-4/)</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
+          <t>['Users are advised to upgrade to phpMyAdmin 4.8.2 or newer from phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php). For more information check PMASA-2018-3 (https://www.phpmyadmin.net/security/PMASA-2018-3/) and PMASA-2018-4 (https://www.phpmyadmin.net/security/PMASA-2018-4/). Patch: Following are links for downloading patches to fix the vulnerabilities: PMASA-2018-3: PhpMyAdmin (https://www.phpmyadmin.net/security/PMASA-2018-3/) PMASA-2018-4: PhpMyAdmin (https://www.phpmyadmin.net/security/PMASA-2018-4/)']</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>['Successful exploitation can result in file inclusion ,remote code execution and cross-site-scripting attack.']</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>['CVE-2018-12581', 'CVE-2018-12613']</t>
@@ -21894,13 +20206,19 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
-Affected Versions: 
-phpMyAdmin versions prior to 4.8.3  </t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr"/>
-      <c r="D384" t="inlineStr"/>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.', 'A Cross-Site Scripting vulnerability was found in the file import feature, where an attacker can deliver a payload to a user through importing a specially-crafted file.', 'Affected Versions: phpMyAdmin versions prior to 4.8.3']</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>['Users are advised to upgrade to phpMyAdmin 4.8.3 or newer from phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php). For more information check PMASA-2018-5 (https://www.phpmyadmin.net/security/PMASA-2018-5/) Patch: Following are links for downloading patches to fix the vulnerabilities: PMASA-2018-5 (https://www.phpmyadmin.net/security/PMASA-2018-5/)']</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>["A remote user can access the target user's cookies (including authentication cookies), if any, associated with the site running the phpMyAdmin software, access data recently submitted by the target user via web form to the site, or take actions on the site acting as the target user."]</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>['CVE-2018-15605']</t>
@@ -21946,24 +20264,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
-The software is exposed to Arbitrary file read vulnerability: 
-CVE-2019-6799
- Affected Versions: 
-phpMyAdmin versions from at least 4.0 through 4.8.4  </t>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.', 'The software is exposed to Arbitrary file read vulnerability: CVE-2019-6799', 'Affected Versions: phpMyAdmin versions from at least 4.0 through 4.8.4']</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Users are advised to upgrade to phpMyAdmin 4.8.5 (http://phpmyadmin.net/home_page/downloads.php) or the latest version.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PMASA-2019-1 (https://www.phpmyadmin.net/security/PMASA-2019-1/)</t>
+          <t>['Users are advised to upgrade to phpMyAdmin 4.8.5 (http://phpmyadmin.net/home_page/downloads.php) or the latest version. Patch: Following are links for downloading patches to fix the vulnerabilities: PMASA-2019-1 (https://www.phpmyadmin.net/security/PMASA-2019-1/)']</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an attacker to read any file on the server that the web server's.</t>
+          <t>["Successful exploitation of this vulnerability may allow an attacker to read any file on the server that the web server's."]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -22011,24 +20322,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
-The software is exposed to SQL injection vulnerability in Designer feature: 
-CVE-2019-6799
- Affected Versions: 
-phpMyAdmin versions from 4.5.0 through 4.8.4  </t>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.', 'The software is exposed to SQL injection vulnerability in Designer feature: CVE-2019-6799', 'Affected Versions: phpMyAdmin versions from 4.5.0 through 4.8.4']</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Users are advised to upgrade to phpMyAdmin 4.8.5 (http://phpmyadmin.net/home_page/downloads.php) or the latest version.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PMASA-2019-2 (https://www.phpmyadmin.net/security/PMASA-2019-2/)</t>
+          <t>['Users are advised to upgrade to phpMyAdmin 4.8.5 (http://phpmyadmin.net/home_page/downloads.php) or the latest version. Patch: Following are links for downloading patches to fix the vulnerabilities: PMASA-2019-2 (https://www.phpmyadmin.net/security/PMASA-2019-2/)']</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Successful exploitation allows remote attackers to inject and execute arbitrary SQL code a targeted server.</t>
+          <t>['Successful exploitation allows remote attackers to inject and execute arbitrary SQL code a targeted server.']</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -22076,33 +20380,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Many Web sites support the idea of user sessions. Each user connecting to the site is issued a unique session ID, which is then used to identify all subsequent requests made by that user, either encoded in the URLs, or as a cookie. The server can then store data for each user session such as the state of a Web shopping cart. Session IDs are also often used to control access to sites requiring a login. Instead of sending the username/password with every request, the site issues a session ID after the user logs on, and the session ID identifies the user for the rest of the session.
-With some server session management systems, it's possible for a user, who can connect to the server and get a session ID, to guess other users' session IDs. If successful, the attacker can then view any page, take any action, post to any form etc. as the real user of that session.
-This attack requires no IP spoofing or session snooping. It works against sites using SSL.
-The following links provide more information about this vulnerability:
- Netcraft Security Advisory 2001-01.1 - Predictable Session IDs (http://news.netcraft.com/archives/2003/01/01/security_advisory_2001011_predictable_session_ids.html)
- Cookie Encyclopedia - Predictable Session IDs (http://www.pdos.lcs.mit.edu/cookies/seq_sessionid.html)
- Brute-Force Exploitation of Web Application Session IDs (http://www.cgisecurity.com/lib/SessionIDs.pdf)</t>
+          <t>['Many Web sites support the idea of user sessions. Each user connecting to the site is issued a unique session ID, which is then used to identify all subsequent requests made by that user, either encoded in the URLs, or as a cookie. The server can then store data for each user session such as the state of a Web shopping cart. Session IDs are also often used to control access to sites requiring a login. Instead of sending the username/password with every request, the site issues a session ID after the user logs on, and the session ID identifies the user for the rest of the session.', "With some server session management systems, it's possible for a user, who can connect to the server and get a session ID, to guess other users' session IDs. If successful, the attacker can then view any page, take any action, post to any form etc. as the real user of that session.", 'This attack requires no IP spoofing or session snooping. It works against sites using SSL.', 'The following links provide more information about this vulnerability:', 'Netcraft Security Advisory 2001-01.1 - Predictable Session IDs (http://news.netcraft.com/archives/2003/01/01/security_advisory_2001011_predictable_session_ids.html) Cookie Encyclopedia - Predictable Session IDs (http://www.pdos.lcs.mit.edu/cookies/seq_sessionid.html) Brute-Force Exploitation of Web Application Session IDs (http://www.cgisecurity.com/lib/SessionIDs.pdf)']</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>This issue may be caused by the Web server, the Web application server or the Web application itself.
- Some software known to be vulnerable are listed below:
- Ipswitch IMail Server Predictable Session ID Vulnerability (http://cve.mitre.org/cgi-bin/cvename.cgi?name=CAN-2001-1284)
-  IBM WebSphere Application Server Predictable Session ID Vulnerability (http://cve.mitre.org/cgi-bin/cvename.cgi?name=CVE-2001-0962)
- For all other software follow the guidelines below or contact your vendor.
- Use strong cryptographic algorithms to generate random session IDS.
- The Web application should not rely on predictable session IDs as the sole means of session tracking and management.
- Any meaningful data being used in session IDs should be one-way encrypted.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PQ47663V302: Websphere Applicaton Server 3.x (http://www-01.ibm.com/support/us/)</t>
+          <t>['This issue may be caused by the Web server, the Web application server or the Web application itself. Some software known to be vulnerable are listed below:', 'Ipswitch IMail Server Predictable Session ID Vulnerability (http://cve.mitre.org/cgi-bin/cvename.cgi?name=CAN-2001-1284) IBM WebSphere Application Server Predictable Session ID Vulnerability (http://cve.mitre.org/cgi-bin/cvename.cgi?name=CVE-2001-0962)', 'For all other software follow the guidelines below or contact your vendor.', 'Use strong cryptographic algorithms to generate random session IDS. The Web application should not rely on predictable session IDs as the sole means of session tracking and management. Any meaningful data being used in session IDs should be one-way encrypted.', 'Patch: Following are links for downloading patches to fix the vulnerabilities: PQ47663V302: Websphere Applicaton Server 3.x (http://www-01.ibm.com/support/us/)']</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>The session ID can be trivially guessed after only a limited number of attempts. If this issue is successfully exploited, then it may be possible for an attacker to obtain the cookie-based authentication credentials for legitimate users, allowing unauthorized access to the vulnerable application.</t>
+          <t>['The session ID can be trivially guessed after only a limited number of attempts. If this issue is successfully exploited, then it may be possible for an attacker to obtain the cookie-based authentication credentials for legitimate users, allowing unauthorized access to the vulnerable application.']</t>
         </is>
       </c>
       <c r="E387" t="inlineStr"/>
@@ -22146,17 +20434,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>The Web server uses plain-text form based authentication. A web page exists on the target host which uses an HTML login form. This data is sent from the client to the server in plain-text.</t>
+          <t>['The Web server uses plain-text form based authentication. A web page exists on the target host which uses an HTML login form. This data is sent from the client to the server in plain-text.']</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Please contact the vendor of the hardware/software for a possible fix for the issue. For custom applications, ensure that data sent via HTML login forms is encrypted before being sent from the client to the host.</t>
+          <t>['Please contact the vendor of the hardware/software for a possible fix for the issue. For custom applications, ensure that data sent via HTML login forms is encrypted before being sent from the client to the host.']</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>An attacker with access to the network traffic to and from the target host may be able to obtain login credentials for other users by sniffing the network traffic.</t>
+          <t>['An attacker with access to the network traffic to and from the target host may be able to obtain login credentials for other users by sniffing the network traffic.']</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
@@ -22200,20 +20488,17 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>The secure cookie flag is an option that can be set by the application server when sending a new cookie to the user within an HTTP Response. The purpose of the secure flag is to prevent cookies from being observed by unauthorized parties due to the transmission of a the cookie in clear text. By setting the secure flag, the browser will prevent the transmission of a cookie over an unencrypted channel. 
-A cookie with the secure attribute was not detected in the scan. 
-QID Detection Logic: 
-This unauthenticated QID checks for the existence of the "secure" cookie flag.</t>
+          <t>['The secure cookie flag is an option that can be set by the application server when sending a new cookie to the user within an HTTP Response. The purpose of the secure flag is to prevent cookies from being observed by unauthorized parties due to the transmission of a the cookie in clear text. By setting the secure flag, the browser will prevent the transmission of a cookie over an unencrypted channel. A cookie with the secure attribute was not detected in the scan. QID Detection Logic: This unauthenticated QID checks for the existence of the "secure" cookie flag.']</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Apply the "secure" attribute to session cookies to ensure that they are sent via HTTPS only. More information about this flag can be found here: https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Set-Cookie.</t>
+          <t>['Apply the "secure" attribute to session cookies to ensure that they are sent via HTTPS only. More information about this flag can be found here: https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Set-Cookie.']</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Session cookies sent via HTTP expose users to sniffing attacks that could lead to user impersonation or account compromise.</t>
+          <t>['Session cookies sent via HTTP expose users to sniffing attacks that could lead to user impersonation or account compromise.']</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
@@ -22257,23 +20542,17 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>The Web server allows form based authentication without disabling the AutoComplete feature for the password field. 
-Autocomplete should be turned off for any input that takes sensitive information such as credit card number, CVV2/CVC code, U.S. social security number, etc.</t>
+          <t>['The Web server allows form based authentication without disabling the AutoComplete feature for the password field. Autocomplete should be turned off for any input that takes sensitive information such as credit card number, CVV2/CVC code, U.S. social security number, etc.']</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Contact the vendor to have the AutoComplete attribute disabled for the password field in all forms. The AutoComplete attribute should also be disabled for the user ID field.  
-Developers can add the following attribute to the form or input element: autocomplete="off"  
-This attribute prevents the browser from prompting the user to save the populated form values for later reuse.   
-Most browsers no longer honor autocomplete="off" for password input fields. These browsers include  Chrome, Firefox, Microsoft Edge, IE, Opera 
-However, there is still an ability to turn off autocomplete through the browser and that is recommended for a shared computing environment. 
-Since the ability to turn autocomplete off for password inputs fields is controlled by the user it is highly recommended for application to enforce strong password rules.</t>
+          <t>['Contact the vendor to have the AutoComplete attribute disabled for the password field in all forms. The AutoComplete attribute should also be disabled for the user ID field. Developers can add the following attribute to the form or input element: autocomplete="off" This attribute prevents the browser from prompting the user to save the populated form values for later reuse. Most browsers no longer honor autocomplete="off" for password input fields. These browsers include Chrome, Firefox, Microsoft Edge, IE, Opera However, there is still an ability to turn off autocomplete through the browser and that is recommended for a shared computing environment. Since the ability to turn autocomplete off for password inputs fields is controlled by the user it is highly recommended for application to enforce strong password rules.']</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>If the browser is used in a shared computing environment where more than one person may use the browser, then "autocomplete" values may be retrieved or submitted by an unauthorized user.</t>
+          <t>['If the browser is used in a shared computing environment where more than one person may use the browser, then "autocomplete" values may be retrieved or submitted by an unauthorized user.']</t>
         </is>
       </c>
       <c r="E390" t="inlineStr"/>
@@ -22317,24 +20596,17 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
-CVE-2020-5504: A malicious user could inject custom SQL in place of their own username when creating queries to this page. 
- Affected Versions: 
-phpMyAdmin versions from 4.0.x prior to 4.9.4. 
-phpMyAdmin versions from 5.0.x prior to 5.0.1. </t>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.', 'CVE-2020-5504: A malicious user could inject custom SQL in place of their own username when creating queries to this page.', 'Affected Versions: phpMyAdmin versions from 4.0.x prior to 4.9.4. phpMyAdmin versions from 5.0.x prior to 5.0.1.']</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Users are advised to upgrade to phpMyAdmin 4.9.4 or 5.0.1 (http://phpmyadmin.net/home_page/downloads.php) or the latest version.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PMASA-2020-1 (https://www.phpmyadmin.net/security/PMASA-2020-1/)</t>
+          <t>['Users are advised to upgrade to phpMyAdmin 4.9.4 or 5.0.1 (http://phpmyadmin.net/home_page/downloads.php) or the latest version.', 'Patch: Following are links for downloading patches to fix the vulnerabilities: PMASA-2020-1 (https://www.phpmyadmin.net/security/PMASA-2020-1/)']</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Successful exploitation of these vulnerabilities may allows remote attackers to inject and execute arbitrary SQL code on the targeted server.</t>
+          <t>['Successful exploitation of these vulnerabilities may allows remote attackers to inject and execute arbitrary SQL code on the targeted server.']</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -22382,19 +20654,19 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
-The software is exposed to the XSRF/CSRF vulnerability: 
-CVE-2019-12922
-Affected Versions: 
-phpMyAdmin versions prior to 4.9.1  </t>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.', 'The software is exposed to the XSRF/CSRF vulnerability: CVE-2019-12922 Affected Versions: phpMyAdmin versions prior to 4.9.1']</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Users are advised to upgrade to phpMyAdmin 4.8.4 or newer from phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php).</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr"/>
+          <t>['Users are advised to upgrade to phpMyAdmin 4.8.4 or newer from phpMyAdmin (http://phpmyadmin.net/home_page/downloads.php).', 'Patch: Following are links for downloading patches to fix the vulnerabilities: phpMyAdmin (https://seclists.org/fulldisclosure/2019/Sep/23)']</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>['By deceiving a user to click on a crafted URL, it is possible for an attacker to execute arbitrary SQL commands.']</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>['CVE-2019-12922']</t>
@@ -22440,23 +20712,17 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
-CVE-2019-12616: A vulnerability was found that allows an attacker to trigger a CSRF attack against a phpMyAdmin user. 
- Affected Versions: 
-phpMyAdmin versions prior to 4.9.0. </t>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.', 'CVE-2019-12616: A vulnerability was found that allows an attacker to trigger a CSRF attack against a phpMyAdmin user.', 'Affected Versions: phpMyAdmin versions prior to 4.9.0.']</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Users are advised to upgrade to phpMyAdmin 4.9.0 (http://phpmyadmin.net/home_page/downloads.php) or the latest version.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PMASA-2019-4 (https://www.phpmyadmin.net/security/PMASA-2019-4/)</t>
+          <t>['Users are advised to upgrade to phpMyAdmin 4.9.0 (http://phpmyadmin.net/home_page/downloads.php) or the latest version. Patch: Following are links for downloading patches to fix the vulnerabilities: PMASA-2019-4 (https://www.phpmyadmin.net/security/PMASA-2019-4/)']</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allows remote attackers to trick user to perform unintended actions on attackers behalf.</t>
+          <t>['Successful exploitation of this vulnerability may allows remote attackers to trick user to perform unintended actions on attackers behalf.']</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -22504,23 +20770,17 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
-CVE-2022-0813: PhpMyAdmin 5.1.1 and before allows an attacker to retrieve potentially sensitive information by creating invalid requests. This affects the lang parameter, the pma_parameter, and the cookie section. 
- Affected Versions: 
-PhpMyAdmin version 5.1.1 and before. </t>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.', 'CVE-2022-0813: PhpMyAdmin 5.1.1 and before allows an attacker to retrieve potentially sensitive information by creating invalid requests. This affects the lang parameter, the pma_parameter, and the cookie section.', 'Affected Versions: PhpMyAdmin version 5.1.1 and before.']</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Users are advised to upgrade to phpMyAdmin 5.1.3 (http://phpmyadmin.net/home_page/downloads.php) or the latest version.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  phpMyAdmin Release Note (https://www.phpmyadmin.net/news/2022/2/11/phpmyadmin-4910-and-513-are-released/)</t>
+          <t>['Users are advised to upgrade to phpMyAdmin 5.1.3 (http://phpmyadmin.net/home_page/downloads.php) or the latest version. Patch: Following are links for downloading patches to fix the vulnerabilities: phpMyAdmin Release Note (https://www.phpmyadmin.net/news/2022/2/11/phpmyadmin-4910-and-513-are-released/)']</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an attacker to retrieve potentially sensitive information by creating invalid requests.</t>
+          <t>['Successful exploitation of this vulnerability may allow an attacker to retrieve potentially sensitive information by creating invalid requests.']</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -22568,24 +20828,17 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t xml:space="preserve">PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet. 
-An XSS vulnerability has been discovered where an authenticated user can trigger an XSS attack by uploading a specially-crafted .sql file through the drag-and-drop interface. 
- Affected Versions: 
-phpMyAdmin versions from 4.3.0 prior to 4.9.1 
-phpMyAdmin versions from 5.0 prior to 5.2.1 </t>
+          <t>['PhpMyAdmin is a free software tool written in PHP and intended to handle the administration of MySQL over the Internet.', 'An XSS vulnerability has been discovered where an authenticated user can trigger an XSS attack by uploading a specially-crafted .sql file through the drag-and-drop interface.', 'Affected Versions: phpMyAdmin versions from 4.3.0 prior to 4.9.1 phpMyAdmin versions from 5.0 prior to 5.2.1']</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Users are advised to upgrade to phpMyAdmin 5.2.1 or 4.9.11 (http://phpmyadmin.net/home_page/downloads.php) or the latest version.Workaround: Disable the configuration directive `$cfg['enable_drag_drop_import']`, users will be unable to use the drag and drop upload which would protect against the vulnerability.
- Patch: 
-Following are links for downloading patches to fix the vulnerabilities:
-  PMASA-2023-1 (https://www.phpmyadmin.net/security/PMASA-2023-1/)</t>
+          <t>["Users are advised to upgrade to phpMyAdmin 5.2.1 or 4.9.11 (http://phpmyadmin.net/home_page/downloads.php) or the latest version.Workaround: Disable the configuration directive `$cfg['enable_drag_drop_import']`, users will be unable to use the drag and drop upload which would protect against the vulnerability. Patch: Following are links for downloading patches to fix the vulnerabilities: PMASA-2023-1 (https://www.phpmyadmin.net/security/PMASA-2023-1/)"]</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Successful exploitation of this vulnerability may allow an authenticated attacker to execute arbitrary JavaScript code on the target system.</t>
+          <t>['Successful exploitation of this vulnerability may allow an authenticated attacker to execute arbitrary JavaScript code on the target system.']</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -22633,55 +20886,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>The result section of this QID lists web applications and plugins that were detected on the target using web application fingerprinting. This technique compares static files at known locations against precomputed hashes for versions of those files in all available releases. The technique is fast, low-bandwidth, non-invasive, generic, and highly automatable.
- Following open source and free applications are currently supported:
- Joomla!
- MediaWiki
- WordPress
- phpBB
- MovableType
- Drupal
- osCommerce
- PHP-Nuke
- Moodle
- Liferay
- Tikiwiki
- Twiki
- phpmyadmin
- SPIP
- Confluence(free versions)
- Wikka
- Wacko
- Usemod
- e107
- Flyspray
- AppRain
- V-CMS
- AjaxPlorer/Pydio
- eFront Learning Management System
- vTigerCRM (Open source versions)
- MyBB
- WebCalendar
- PivotX WebLog
- DokuWiki
- MODX Revolution
- MODX Evolution
- Collabtive
- Achievo
- Magento 1.x CE
- iCE Hrm (Opensource Version)
- AdaptCMS
- ownCloud
- HumHub
- Redaxscript
- phpwcms
- Wolf CMS
- Pligg CMS
- Zen Cart
- Xoops
- TYPO3
- Microweber
- This QID is based on the Blind Elephant project (http://blindelephant.sourceforge.net/). For a complete list of supported web applications and plugins, please check the following link: DOC-5480 (https://community.qualys.com/docs/DOC-5480).</t>
+          <t>['The result section of this QID lists web applications and plugins that were detected on the target using web application fingerprinting. This technique compares static files at known locations against precomputed hashes for versions of those files in all available releases. The technique is fast, low-bandwidth, non-invasive, generic, and highly automatable. Following open source and free applications are currently supported: Joomla! MediaWiki WordPress phpBB MovableType Drupal osCommerce PHP-Nuke Moodle Liferay Tikiwiki Twiki phpmyadmin SPIP Confluence(free versions) Wikka Wacko Usemod e107 Flyspray AppRain V-CMS AjaxPlorer/Pydio eFront Learning Management System vTigerCRM (Open source versions) MyBB WebCalendar PivotX WebLog DokuWiki MODX Revolution MODX Evolution Collabtive Achievo Magento 1.x CE iCE Hrm (Opensource Version) AdaptCMS ownCloud HumHub Redaxscript phpwcms Wolf CMS Pligg CMS Zen Cart Xoops TYPO3 Microweber', 'This QID is based on the Blind Elephant project (http://blindelephant.sourceforge.net/). For a complete list of supported web applications and plugins, please check the following link: DOC-5480 (https://community.qualys.com/docs/DOC-5480).']</t>
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
@@ -22727,7 +20932,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.</t>
+          <t>['This QID lists supported HTTP protocol (HTTP 1.x or HTTP 2) from remote web server.']</t>
         </is>
       </c>
       <c r="C397" t="inlineStr"/>
@@ -22773,7 +20978,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
@@ -22813,8 +21018,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
@@ -22854,7 +21058,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -22894,7 +21098,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -22932,11 +21136,19 @@
           <t>Open TCP Services List</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr"/>
-      <c r="C402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
+        </is>
+      </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E402" t="inlineStr"/>
@@ -22974,14 +21186,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -23021,7 +21226,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -23061,8 +21266,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -23144,7 +21348,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server.</t>
+          <t>['The Result section displays the default Web page for the Web server.']</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -23190,7 +21394,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>The Result section displays the default Web page for the Web server following HTTP redirections.</t>
+          <t>['The Result section displays the default Web page for the Web server following HTTP redirections.']</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
@@ -23236,7 +21440,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nginx is a web server which can also be used as a reverse proxy, load balancer , mail proxy and HTTP cache. </t>
+          <t>['Nginx is a web server which can also be used as a reverse proxy, load balancer , mail proxy and HTTP cache.']</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
@@ -23282,9 +21486,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request.  
-QID Detection Logic: 
-This QID returns the HTTP response method and header information returned by a web server.</t>
+          <t>["This QID prints the information, in the form of a text record, that a web server sends back to a client's browser in response to receiving a single HTTP GET request. QID Detection Logic: This QID returns the HTTP response method and header information returned by a web server."]</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
@@ -23330,14 +21532,13 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.
-The target Web server was found to support this functionality of the HTTP 1.1 protocol.</t>
+          <t>['Version 1.1 of the HTTP protocol supports URL-Request Pipelining. This means that instead of using the "Keep-Alive" method to keep the TCP connection alive over multiple requests, the protocol allows multiple HTTP URL requests to be made in the same TCP packet. Any Web server which is HTTP 1.1 compliant should then process all the URLs requested in the single TCP packet and respond as usual.', 'The target Web server was found to support this functionality of the HTTP 1.1 protocol.']</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.</t>
+          <t>['Support for URL-Request Pipelining has interesting consequences. For example, as explained in this paper by Daniel Roelker (http://www.defcon.org/images/defcon-11/dc-11-presentations/dc-11-Roelker/dc-11-roelker-paper.pdf), it can be used for evading detection by Intrusion Detection Systems. Also, it can be used in HTTP Response-Spliting style attacks.']</t>
         </is>
       </c>
       <c r="E411" t="inlineStr"/>
@@ -23381,7 +21582,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Based largely on the HTTP reply code, the following directories are most likely present on the host.</t>
+          <t>['Based largely on the HTTP reply code, the following directories are most likely present on the host.']</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
@@ -23427,7 +21628,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.</t>
+          <t>['The fully qualified domain name of this host, if it was obtained from a DNS server, is displayed in the RESULT section.']</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
@@ -23467,8 +21668,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below. 
-The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners.</t>
+          <t>['The Host Scan Time is the period of time it takes the scanning engine to perform the vulnerability assessment of a single target host. The Host Scan Time for this host is reported in the Result section below.', "The Host Scan Time does not have a direct correlation to the Duration time as displayed in the Report Summary section of a scan results report. The Duration is the period of time it takes the service to perform a scan task. The Duration includes the time it takes the service to scan all hosts, which may involve parallel scanning. It also includes the time it takes for a scanner appliance to pick up the scan task and transfer the results back to the service's Secure Operating Center. Further, when a scan task is distributed across multiple scanners, the Duration includes the time it takes to perform parallel host scanning on all scanners."]</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -23508,7 +21708,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.</t>
+          <t>['The following host names were discovered for this computer using various methods such as DNS look up, NetBIOS query, and SQL server name query.']</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -23548,7 +21748,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.</t>
+          <t>['Scan activity per port is an estimate of the amount of internal process time the scanner engine spent scanning a particular TCP or UDP port. This information can be useful to determine the reason for long scan times. The individual time values represent internal process time, not elapsed time, and can be longer than the total scan time because of internal parallelism. High values are often caused by slowly responding services or services on which requests time out.']</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -23588,18 +21788,17 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet.  The test was carried out with a "stealth" port scanner so that the server does not log real connections.
-The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).</t>
+          <t>['The port scanner enables unauthorized users with the appropriate tools to draw a map of all services on this host that can be accessed from the Internet. The test was carried out with a "stealth" port scanner so that the server does not log real connections.', 'The Results section displays the port number (Port), the default service listening on the port (IANA Assigned Ports/Services), the description of the service (Description) and the service that the scanner detected using service discovery (Service Detected).']</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Shut down any unknown or unused service on the list.  If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team.  For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org).</t>
+          <t>["Shut down any unknown or unused service on the list. If you have difficulty figuring out which service is provided by which process or program, contact your provider's support team. For more information about commercial and open-source Intrusion Detection Systems available for detecting port scanners of this kind, visit the CERT Web site (http://www.cert.org)."]</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Unauthorized users can exploit this information to test vulnerabilities in each of the open services.</t>
+          <t>['Unauthorized users can exploit this information to test vulnerabilities in each of the open services.']</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
@@ -23637,14 +21836,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts. 
-We have sent the following types of packets to trigger the host to send us ICMP replies: 
-Echo Request (to trigger Echo Reply) 
-Timestamp Request (to trigger Timestamp Reply) 
-Address Mask Request (to trigger Address Mask Reply) 
-UDP Packet (to trigger Port Unreachable Reply) 
-IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)
-Listed in the "Result" section are the ICMP replies that we have received.</t>
+          <t>["ICMP (Internet Control and Error Message Protocol) is a protocol encapsulated in IP packets. ICMP's principal purpose is to provide a protocol layer that informs gateways of the inter-connectivity and accessibility of other gateways or hosts.", 'We have sent the following types of packets to trigger the host to send us ICMP replies:', 'Echo Request (to trigger Echo Reply) Timestamp Request (to trigger Timestamp Reply) Address Mask Request (to trigger Address Mask Reply) UDP Packet (to trigger Port Unreachable Reply) IP Packet with Protocol &gt;= 250 (to trigger Protocol Unreachable Reply)', 'Listed in the "Result" section are the ICMP replies that we have received.']</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -23684,7 +21876,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.</t>
+          <t>['TCP Initial Sequence Numbers (ISNs) obtained in the SYNACK replies from the host are analyzed to determine how random they are. The average change between subsequent ISNs and the standard deviation from the average are displayed in the RESULT section. Also included is the degree of difficulty for exploitation of the TCP ISN generation scheme used by the host.']</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -23724,8 +21916,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.
-Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.</t>
+          <t>['The values for the identification (ID) field in IP headers in IP packets from the host are analyzed to determine how random they are. The changes between subsequent ID values for either the network byte ordering or the host byte ordering, whichever is smaller, are displayed in the RESULT section along with the duration taken to send the probes. When incremental values are used, as is the case for TCP/IP implementation in many operating systems, these changes reflect the network load of the host at the time this test was conducted.', 'Please note that for reliability reasons only the network traffic from open TCP ports is analyzed.']</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
